--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2288,8 +2288,1742 @@
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>646f4fbfd5504bbb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69681</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0.616241</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>-0.0741614767801857</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:57.846727Z</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>e2876712547f4c3b</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69263</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.680308</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>-0.01939169969969967</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:58.340278Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1a9ea8e40b784a15</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69682</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.684201</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.04391323021582727</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:14:58.893489Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>5a4eb97ea6bb4c1f</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69679</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.632201</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>-0.06749869969969968</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:00.014811Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>60b8d65daf374321</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.510807</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.11080699999999999</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:01.130828Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>6737dcd9b1d24020</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.57955</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.13902136563876655</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:01.749745Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ac427b0e0fdc4676</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.526936</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.08243900000000004</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:02.236713Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>cd5f2bf39c264b72</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>68288</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.704235</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.3545846503496504</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:03.660648Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>4b06f5a4c0804d78</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.599195</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.01936306722689085</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:04.678326Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>30facd89be8a4b48</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.563014</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>-0.12738847678018572</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:05.206115Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ec5ca370ba0546ef</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.628883</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.051628182108626186</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:07.681014Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>d7c3181ca9674fe9</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.527254</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.082121</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:08.249635Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>b34b3708459c411b</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.526936</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>-0.07306400000000013</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:08.773065Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2de5a7d0deb34a1b</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.526283</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.18614694557823125</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:09.305570Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>5fa69921c97849f4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.613848</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>-0.02643976978417273</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:09.759475Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>a5b01fe302794e12</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.662883</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.022595230215827322</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:10.799851Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>145fcb8310264bd8</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.569642</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.11919154954954947</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:14.474993Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ17"/>
+  <autoFilter ref="A1:AJ34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4022,8 +4022,3170 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>f965f48b044b47e1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>69682</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.684201</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.07482599999999995</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:19.690950Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>3f7399c57a3b4170</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>69681</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.616241</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>-0.06427018210862612</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:20.150236Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ea04e37873db469c</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>69263</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.680308</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>-0.01939169969969967</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:21.192488Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2a878495b4ac4ffb</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.510807</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.11080699999999999</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:21.746211Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>6f4da11c6df84d88</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.57955</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.13902136563876655</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:22.246071Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>03e5a0f81ada4139</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.526936</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>-0.08243900000000004</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:22.807301Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>8b531bfe1ad24c94</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>68288</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.704235</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0.3545846503496504</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:24.893665Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>94a8174a0733410b</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.563014</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>-0.12738847678018572</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:26.331109Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>95cf40a401c541e6</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.599195</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.01936306722689085</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:26.813178Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>1c3f54eb07ba4f3e</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.526936</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>-0.07306400000000013</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:28.293364Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>029da089e96d49c1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.527254</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>-0.082121</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:28.786986Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>3d4aa7bf11804668</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.628883</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>-0.051628182108626186</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:29.267249Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>a4685704f9e14450</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.526283</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.18614694557823125</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:29.725154Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ecf65f35fb954115</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.613848</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>-0.03650165034965036</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:30.182750Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>e41d5fc13f274a11</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.662883</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.022595230215827322</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:30.646895Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>fbee74e8232242bb</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>6bae46bd2680c84ce698cde5e863cadf17cf096c2af52ab6ded3ff7320578e1f</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.569642</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.11919154954954947</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:46:34.632788Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>f1ba0c15e6674983</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>69682</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.684208</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.07483300000000004</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:18.155145Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2e594a4bc98d4299</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>69263</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.68024</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.020376054421768597</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:19.829844Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>1a3314d3a7424d8b</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.510848</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.11084799999999995</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:20.304048Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>a921733b5e0d4263</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.579552</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.1390233656387665</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:20.814282Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>e81d3e73b2bc403a</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>-0.08243699999999998</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:21.312852Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>555c006db5ac42a7</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>68288</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.704234</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.3545836503496504</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:23.458560Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>5955b2ea26484211</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.563046</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>-0.1273564767801857</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:24.972799Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>f2ab73db274e4630</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.599198</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.019366067226890826</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:25.545768Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>1ede631c4d584d55</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>-0.07306200000000007</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:27.133627Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>f1f15a8356fc4d33</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.527203</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>-0.08217200000000002</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:27.628665Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>bf51ed4a32784bbc</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.628889</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>-0.051622182108626125</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:28.112728Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>f7fe276ead4d4f45</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.526281</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>0.1861449455782313</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:28.608319Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>625f23ccbb01457e</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.613947</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>-0.026340769784172657</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:29.071469Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>188ce65117914d31</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.663025</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.022737230215827298</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:29.527479Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>e58e43d6e4de458c</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.569644</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0.11919354954954953</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:53:33.675629Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ34"/>
+  <autoFilter ref="A1:AJ65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ65"/>
+  <dimension ref="A1:AJ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7184,8 +7184,1334 @@
       <c r="AI65" s="2" t="inlineStr"/>
       <c r="AJ65" s="2" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>05fa5aa4b21d4bac</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.510882</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.11088199999999993</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:28.086385Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>3fc1907dd134478e</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.579552</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.1390233656387665</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:28.594679Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>8d160e6523dd4cdd</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>-0.08243699999999998</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:29.080231Z</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="2" t="inlineStr"/>
+      <c r="AI68" s="2" t="inlineStr"/>
+      <c r="AJ68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>92eba755d08e4aab</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>68288</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>0.704209</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>0.34965034965034963</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0.35455865034965034</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:30.555681Z</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="2" t="inlineStr"/>
+      <c r="AJ69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>71f788159739438d</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>0.599199</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0.019367067226890855</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:31.821007Z</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="2" t="inlineStr"/>
+      <c r="AH70" s="2" t="inlineStr"/>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>e47a6ab5619b417f</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>0.563071</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>-0.12733147678018575</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:33.313201Z</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>d2a46881bd0b4d12</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>0.527201</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>-0.09257086311787066</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:34.765803Z</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="2" t="inlineStr"/>
+      <c r="AH72" s="2" t="inlineStr"/>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>269e6b1c00644dad</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>0.628836</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>-0.051675182108626205</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:35.281516Z</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="2" t="inlineStr"/>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>f5ac8ff70ff04bae</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>-0.07306200000000007</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:35.963959Z</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="2" t="inlineStr"/>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>0cb9d3531d384b58</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>0.526281</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>0.1861449455782313</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:36.441729Z</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>9459506a0e824091</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>0.663041</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>0.022753230215827314</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:36.924167Z</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ee75c30a1e384add</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>0.613913</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>-0.026374769784172636</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:37.460336Z</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2260ecf16e124af6</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>0.569636</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>0.11918554954954952</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.504632Z</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ65"/>
+  <autoFilter ref="A1:AJ78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ78"/>
+  <dimension ref="A1:AJ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8510,8 +8510,1538 @@
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>3cd1c371ca5348a1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>0.579552</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>0.1390233656387665</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:43.326707Z</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>06423e22b7a2431a</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>-0.08243699999999998</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:43.920209Z</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="2" t="inlineStr"/>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="2" t="inlineStr"/>
+      <c r="AJ80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>f0e4931673f242ff</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>0.599199</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>0.019367067226890855</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:46.352076Z</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="2" t="inlineStr"/>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="2" t="inlineStr"/>
+      <c r="AJ81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>cd56e4e3a1ca4421</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>0.563071</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>-0.12733147678018575</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:47.796652Z</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="2" t="inlineStr"/>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="2" t="inlineStr"/>
+      <c r="AJ82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>54d678843a4b42c7</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.639896</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.02012413688212933</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:48.789246Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>84c8c2b3408d4d5f</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.527201</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>-0.09257086311787066</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:49.284497Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>d7964634a4eb424a</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.628836</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>-0.051675182108626205</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:49.833473Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>4cef676cd1494cb8</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.526938</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>-0.07306200000000007</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:50.485383Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>7116a6138bca4841</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.526281</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.1861449455782313</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:50.962336Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>554e436430c8460e</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.663041</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.022753230215827314</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:51.418739Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>d47c9fdbccfe4639</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.613913</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>-0.026374769784172636</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:51.886373Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>3d62a92101654f9e</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.569636</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.11918554954954952</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:55.995920Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>a797bd12b2584bb0</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.57961</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>0.1390813656387665</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:36.926594Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>59f80bd3163147b6</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.52695</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>-0.08242499999999997</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:37.417895Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>f6b41f52c0094e48</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.599274</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>0.01944206722689079</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:12:39.986059Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ78"/>
+  <autoFilter ref="A1:AJ93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ93"/>
+  <dimension ref="A1:AJ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10040,8 +10040,1232 @@
       <c r="AI93" s="2" t="inlineStr"/>
       <c r="AJ93" s="2" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>b3840ef561054809</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.57961</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>0.1390813656387665</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:31.889837Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>27da5ba5ca654e76</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.52695</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>-0.08242499999999997</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:32.462110Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>3909876fd1864ff8</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.599274</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>0.01944206722689079</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:35.118991Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>1c3f848380bf46af</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.563115</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>-0.1272874767801857</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:36.680077Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>3d197149dcb94c3f</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.640004</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.020232136882129326</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:37.624827Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>5bd578a0af6e4311</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.628935</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>-0.051576182108626134</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:38.106265Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>6eb8483dcada4976</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.52695</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>-0.07305000000000006</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:38.641492Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>6531c9bcbbd64752</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.527213</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>-0.1024166296296295</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:39.222086Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>6f148626a0a34506</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.526317</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>0.18618094557823134</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:39.764070Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>271755c53cd34b87</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.663166</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>0.022878230215827355</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.237935Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>39f0b08982d94260</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.614</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>-0.026287769784172688</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.707211Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>499edd7f210446e2</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.569685</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.11923454954954948</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.989547Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ93"/>
+  <autoFilter ref="A1:AJ105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$498</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ438"/>
+  <dimension ref="A1:AJ498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -45590,8 +45590,6128 @@
       <c r="AI438" s="2" t="inlineStr"/>
       <c r="AJ438" s="2" t="inlineStr"/>
     </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>b899631f408e4879</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>71316</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K439" s="2" t="inlineStr"/>
+      <c r="L439" s="2" t="inlineStr">
+        <is>
+          <t>0.52736</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="inlineStr"/>
+      <c r="N439" s="2" t="inlineStr"/>
+      <c r="O439" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P439" s="2" t="inlineStr"/>
+      <c r="Q439" s="2" t="inlineStr">
+        <is>
+          <t>-0.022189549549549437</t>
+        </is>
+      </c>
+      <c r="R439" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:19.586314Z</t>
+        </is>
+      </c>
+      <c r="S439" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T439" s="2" t="inlineStr"/>
+      <c r="U439" s="2" t="inlineStr"/>
+      <c r="V439" s="2" t="inlineStr"/>
+      <c r="W439" s="2" t="inlineStr"/>
+      <c r="X439" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y439" s="2" t="inlineStr"/>
+      <c r="Z439" s="2" t="inlineStr"/>
+      <c r="AA439" s="2" t="inlineStr"/>
+      <c r="AB439" s="2" t="inlineStr"/>
+      <c r="AC439" s="2" t="inlineStr"/>
+      <c r="AD439" s="2" t="inlineStr"/>
+      <c r="AE439" s="2" t="inlineStr"/>
+      <c r="AF439" s="2" t="inlineStr"/>
+      <c r="AG439" s="2" t="inlineStr"/>
+      <c r="AH439" s="2" t="inlineStr"/>
+      <c r="AI439" s="2" t="inlineStr"/>
+      <c r="AJ439" s="2" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>0b544dd668f642fa</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>68471</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K440" s="2" t="inlineStr"/>
+      <c r="L440" s="2" t="inlineStr">
+        <is>
+          <t>0.571054</t>
+        </is>
+      </c>
+      <c r="M440" s="2" t="inlineStr"/>
+      <c r="N440" s="2" t="inlineStr"/>
+      <c r="O440" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P440" s="2" t="inlineStr"/>
+      <c r="Q440" s="2" t="inlineStr">
+        <is>
+          <t>-0.11934847678018579</t>
+        </is>
+      </c>
+      <c r="R440" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:20.827862Z</t>
+        </is>
+      </c>
+      <c r="S440" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T440" s="2" t="inlineStr"/>
+      <c r="U440" s="2" t="inlineStr"/>
+      <c r="V440" s="2" t="inlineStr"/>
+      <c r="W440" s="2" t="inlineStr"/>
+      <c r="X440" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y440" s="2" t="inlineStr"/>
+      <c r="Z440" s="2" t="inlineStr"/>
+      <c r="AA440" s="2" t="inlineStr"/>
+      <c r="AB440" s="2" t="inlineStr"/>
+      <c r="AC440" s="2" t="inlineStr"/>
+      <c r="AD440" s="2" t="inlineStr"/>
+      <c r="AE440" s="2" t="inlineStr"/>
+      <c r="AF440" s="2" t="inlineStr"/>
+      <c r="AG440" s="2" t="inlineStr"/>
+      <c r="AH440" s="2" t="inlineStr"/>
+      <c r="AI440" s="2" t="inlineStr"/>
+      <c r="AJ440" s="2" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>270c690a602a47a5</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>68472</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K441" s="2" t="inlineStr"/>
+      <c r="L441" s="2" t="inlineStr">
+        <is>
+          <t>0.513199</t>
+        </is>
+      </c>
+      <c r="M441" s="2" t="inlineStr"/>
+      <c r="N441" s="2" t="inlineStr"/>
+      <c r="O441" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P441" s="2" t="inlineStr"/>
+      <c r="Q441" s="2" t="inlineStr">
+        <is>
+          <t>-0.017317431924882665</t>
+        </is>
+      </c>
+      <c r="R441" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:23.236348Z</t>
+        </is>
+      </c>
+      <c r="S441" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T441" s="2" t="inlineStr"/>
+      <c r="U441" s="2" t="inlineStr"/>
+      <c r="V441" s="2" t="inlineStr"/>
+      <c r="W441" s="2" t="inlineStr"/>
+      <c r="X441" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y441" s="2" t="inlineStr"/>
+      <c r="Z441" s="2" t="inlineStr"/>
+      <c r="AA441" s="2" t="inlineStr"/>
+      <c r="AB441" s="2" t="inlineStr"/>
+      <c r="AC441" s="2" t="inlineStr"/>
+      <c r="AD441" s="2" t="inlineStr"/>
+      <c r="AE441" s="2" t="inlineStr"/>
+      <c r="AF441" s="2" t="inlineStr"/>
+      <c r="AG441" s="2" t="inlineStr"/>
+      <c r="AH441" s="2" t="inlineStr"/>
+      <c r="AI441" s="2" t="inlineStr"/>
+      <c r="AJ441" s="2" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>a06ac53512db440f</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K442" s="2" t="inlineStr"/>
+      <c r="L442" s="2" t="inlineStr">
+        <is>
+          <t>0.551011</t>
+        </is>
+      </c>
+      <c r="M442" s="2" t="inlineStr"/>
+      <c r="N442" s="2" t="inlineStr"/>
+      <c r="O442" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P442" s="2" t="inlineStr"/>
+      <c r="Q442" s="2" t="inlineStr">
+        <is>
+          <t>0.0608149215686275</t>
+        </is>
+      </c>
+      <c r="R442" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:23.843519Z</t>
+        </is>
+      </c>
+      <c r="S442" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T442" s="2" t="inlineStr"/>
+      <c r="U442" s="2" t="inlineStr"/>
+      <c r="V442" s="2" t="inlineStr"/>
+      <c r="W442" s="2" t="inlineStr"/>
+      <c r="X442" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y442" s="2" t="inlineStr"/>
+      <c r="Z442" s="2" t="inlineStr"/>
+      <c r="AA442" s="2" t="inlineStr"/>
+      <c r="AB442" s="2" t="inlineStr"/>
+      <c r="AC442" s="2" t="inlineStr"/>
+      <c r="AD442" s="2" t="inlineStr"/>
+      <c r="AE442" s="2" t="inlineStr"/>
+      <c r="AF442" s="2" t="inlineStr"/>
+      <c r="AG442" s="2" t="inlineStr"/>
+      <c r="AH442" s="2" t="inlineStr"/>
+      <c r="AI442" s="2" t="inlineStr"/>
+      <c r="AJ442" s="2" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>3c90ba545d264bf7</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>68301</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K443" s="2" t="inlineStr"/>
+      <c r="L443" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M443" s="2" t="inlineStr"/>
+      <c r="N443" s="2" t="inlineStr"/>
+      <c r="O443" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P443" s="2" t="inlineStr"/>
+      <c r="Q443" s="2" t="inlineStr">
+        <is>
+          <t>-0.02249254954954949</t>
+        </is>
+      </c>
+      <c r="R443" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:24.375948Z</t>
+        </is>
+      </c>
+      <c r="S443" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T443" s="2" t="inlineStr"/>
+      <c r="U443" s="2" t="inlineStr"/>
+      <c r="V443" s="2" t="inlineStr"/>
+      <c r="W443" s="2" t="inlineStr"/>
+      <c r="X443" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y443" s="2" t="inlineStr"/>
+      <c r="Z443" s="2" t="inlineStr"/>
+      <c r="AA443" s="2" t="inlineStr"/>
+      <c r="AB443" s="2" t="inlineStr"/>
+      <c r="AC443" s="2" t="inlineStr"/>
+      <c r="AD443" s="2" t="inlineStr"/>
+      <c r="AE443" s="2" t="inlineStr"/>
+      <c r="AF443" s="2" t="inlineStr"/>
+      <c r="AG443" s="2" t="inlineStr"/>
+      <c r="AH443" s="2" t="inlineStr"/>
+      <c r="AI443" s="2" t="inlineStr"/>
+      <c r="AJ443" s="2" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>bc202ec13cdd444c</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K444" s="2" t="inlineStr"/>
+      <c r="L444" s="2" t="inlineStr">
+        <is>
+          <t>0.691594</t>
+        </is>
+      </c>
+      <c r="M444" s="2" t="inlineStr"/>
+      <c r="N444" s="2" t="inlineStr"/>
+      <c r="O444" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P444" s="2" t="inlineStr"/>
+      <c r="Q444" s="2" t="inlineStr">
+        <is>
+          <t>0.11176206722689086</t>
+        </is>
+      </c>
+      <c r="R444" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:24.962601Z</t>
+        </is>
+      </c>
+      <c r="S444" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T444" s="2" t="inlineStr"/>
+      <c r="U444" s="2" t="inlineStr"/>
+      <c r="V444" s="2" t="inlineStr"/>
+      <c r="W444" s="2" t="inlineStr"/>
+      <c r="X444" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y444" s="2" t="inlineStr"/>
+      <c r="Z444" s="2" t="inlineStr"/>
+      <c r="AA444" s="2" t="inlineStr"/>
+      <c r="AB444" s="2" t="inlineStr"/>
+      <c r="AC444" s="2" t="inlineStr"/>
+      <c r="AD444" s="2" t="inlineStr"/>
+      <c r="AE444" s="2" t="inlineStr"/>
+      <c r="AF444" s="2" t="inlineStr"/>
+      <c r="AG444" s="2" t="inlineStr"/>
+      <c r="AH444" s="2" t="inlineStr"/>
+      <c r="AI444" s="2" t="inlineStr"/>
+      <c r="AJ444" s="2" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>b755e18ce8844506</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>71213</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J445" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K445" s="2" t="inlineStr"/>
+      <c r="L445" s="2" t="inlineStr">
+        <is>
+          <t>0.719577</t>
+        </is>
+      </c>
+      <c r="M445" s="2" t="inlineStr"/>
+      <c r="N445" s="2" t="inlineStr"/>
+      <c r="O445" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P445" s="2" t="inlineStr"/>
+      <c r="Q445" s="2" t="inlineStr">
+        <is>
+          <t>0.2388077692307693</t>
+        </is>
+      </c>
+      <c r="R445" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:26.016387Z</t>
+        </is>
+      </c>
+      <c r="S445" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="T445" s="2" t="inlineStr"/>
+      <c r="U445" s="2" t="inlineStr"/>
+      <c r="V445" s="2" t="inlineStr"/>
+      <c r="W445" s="2" t="inlineStr"/>
+      <c r="X445" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y445" s="2" t="inlineStr"/>
+      <c r="Z445" s="2" t="inlineStr"/>
+      <c r="AA445" s="2" t="inlineStr"/>
+      <c r="AB445" s="2" t="inlineStr"/>
+      <c r="AC445" s="2" t="inlineStr"/>
+      <c r="AD445" s="2" t="inlineStr"/>
+      <c r="AE445" s="2" t="inlineStr"/>
+      <c r="AF445" s="2" t="inlineStr"/>
+      <c r="AG445" s="2" t="inlineStr"/>
+      <c r="AH445" s="2" t="inlineStr"/>
+      <c r="AI445" s="2" t="inlineStr"/>
+      <c r="AJ445" s="2" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>00d0b1e0274540b7</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>68435</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K446" s="2" t="inlineStr"/>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="inlineStr"/>
+      <c r="N446" s="2" t="inlineStr"/>
+      <c r="O446" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P446" s="2" t="inlineStr"/>
+      <c r="Q446" s="2" t="inlineStr">
+        <is>
+          <t>0.136432</t>
+        </is>
+      </c>
+      <c r="R446" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:27.346075Z</t>
+        </is>
+      </c>
+      <c r="S446" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T446" s="2" t="inlineStr"/>
+      <c r="U446" s="2" t="inlineStr"/>
+      <c r="V446" s="2" t="inlineStr"/>
+      <c r="W446" s="2" t="inlineStr"/>
+      <c r="X446" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y446" s="2" t="inlineStr"/>
+      <c r="Z446" s="2" t="inlineStr"/>
+      <c r="AA446" s="2" t="inlineStr"/>
+      <c r="AB446" s="2" t="inlineStr"/>
+      <c r="AC446" s="2" t="inlineStr"/>
+      <c r="AD446" s="2" t="inlineStr"/>
+      <c r="AE446" s="2" t="inlineStr"/>
+      <c r="AF446" s="2" t="inlineStr"/>
+      <c r="AG446" s="2" t="inlineStr"/>
+      <c r="AH446" s="2" t="inlineStr"/>
+      <c r="AI446" s="2" t="inlineStr"/>
+      <c r="AJ446" s="2" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>a6a967a07fa04cc2</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>68437</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K447" s="2" t="inlineStr"/>
+      <c r="L447" s="2" t="inlineStr">
+        <is>
+          <t>0.518066</t>
+        </is>
+      </c>
+      <c r="M447" s="2" t="inlineStr"/>
+      <c r="N447" s="2" t="inlineStr"/>
+      <c r="O447" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P447" s="2" t="inlineStr"/>
+      <c r="Q447" s="2" t="inlineStr">
+        <is>
+          <t>-0.10170586311787067</t>
+        </is>
+      </c>
+      <c r="R447" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:28.977370Z</t>
+        </is>
+      </c>
+      <c r="S447" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T447" s="2" t="inlineStr"/>
+      <c r="U447" s="2" t="inlineStr"/>
+      <c r="V447" s="2" t="inlineStr"/>
+      <c r="W447" s="2" t="inlineStr"/>
+      <c r="X447" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y447" s="2" t="inlineStr"/>
+      <c r="Z447" s="2" t="inlineStr"/>
+      <c r="AA447" s="2" t="inlineStr"/>
+      <c r="AB447" s="2" t="inlineStr"/>
+      <c r="AC447" s="2" t="inlineStr"/>
+      <c r="AD447" s="2" t="inlineStr"/>
+      <c r="AE447" s="2" t="inlineStr"/>
+      <c r="AF447" s="2" t="inlineStr"/>
+      <c r="AG447" s="2" t="inlineStr"/>
+      <c r="AH447" s="2" t="inlineStr"/>
+      <c r="AI447" s="2" t="inlineStr"/>
+      <c r="AJ447" s="2" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>7502cbd4d6cb4683</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>71319</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K448" s="2" t="inlineStr"/>
+      <c r="L448" s="2" t="inlineStr">
+        <is>
+          <t>0.505173</t>
+        </is>
+      </c>
+      <c r="M448" s="2" t="inlineStr"/>
+      <c r="N448" s="2" t="inlineStr"/>
+      <c r="O448" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P448" s="2" t="inlineStr"/>
+      <c r="Q448" s="2" t="inlineStr">
+        <is>
+          <t>-0.12445662962962956</t>
+        </is>
+      </c>
+      <c r="R448" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:29.636509Z</t>
+        </is>
+      </c>
+      <c r="S448" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T448" s="2" t="inlineStr"/>
+      <c r="U448" s="2" t="inlineStr"/>
+      <c r="V448" s="2" t="inlineStr"/>
+      <c r="W448" s="2" t="inlineStr"/>
+      <c r="X448" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y448" s="2" t="inlineStr"/>
+      <c r="Z448" s="2" t="inlineStr"/>
+      <c r="AA448" s="2" t="inlineStr"/>
+      <c r="AB448" s="2" t="inlineStr"/>
+      <c r="AC448" s="2" t="inlineStr"/>
+      <c r="AD448" s="2" t="inlineStr"/>
+      <c r="AE448" s="2" t="inlineStr"/>
+      <c r="AF448" s="2" t="inlineStr"/>
+      <c r="AG448" s="2" t="inlineStr"/>
+      <c r="AH448" s="2" t="inlineStr"/>
+      <c r="AI448" s="2" t="inlineStr"/>
+      <c r="AJ448" s="2" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>1daa3e2377174bbf</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>68562</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K449" s="2" t="inlineStr"/>
+      <c r="L449" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M449" s="2" t="inlineStr"/>
+      <c r="N449" s="2" t="inlineStr"/>
+      <c r="O449" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P449" s="2" t="inlineStr"/>
+      <c r="Q449" s="2" t="inlineStr">
+        <is>
+          <t>-0.0927148631178707</t>
+        </is>
+      </c>
+      <c r="R449" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:30.200409Z</t>
+        </is>
+      </c>
+      <c r="S449" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T449" s="2" t="inlineStr"/>
+      <c r="U449" s="2" t="inlineStr"/>
+      <c r="V449" s="2" t="inlineStr"/>
+      <c r="W449" s="2" t="inlineStr"/>
+      <c r="X449" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y449" s="2" t="inlineStr"/>
+      <c r="Z449" s="2" t="inlineStr"/>
+      <c r="AA449" s="2" t="inlineStr"/>
+      <c r="AB449" s="2" t="inlineStr"/>
+      <c r="AC449" s="2" t="inlineStr"/>
+      <c r="AD449" s="2" t="inlineStr"/>
+      <c r="AE449" s="2" t="inlineStr"/>
+      <c r="AF449" s="2" t="inlineStr"/>
+      <c r="AG449" s="2" t="inlineStr"/>
+      <c r="AH449" s="2" t="inlineStr"/>
+      <c r="AI449" s="2" t="inlineStr"/>
+      <c r="AJ449" s="2" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>89283a53de954e6f</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>68563</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K450" s="2" t="inlineStr"/>
+      <c r="L450" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M450" s="2" t="inlineStr"/>
+      <c r="N450" s="2" t="inlineStr"/>
+      <c r="O450" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P450" s="2" t="inlineStr"/>
+      <c r="Q450" s="2" t="inlineStr">
+        <is>
+          <t>-0.043758450643776814</t>
+        </is>
+      </c>
+      <c r="R450" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:30.876302Z</t>
+        </is>
+      </c>
+      <c r="S450" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T450" s="2" t="inlineStr"/>
+      <c r="U450" s="2" t="inlineStr"/>
+      <c r="V450" s="2" t="inlineStr"/>
+      <c r="W450" s="2" t="inlineStr"/>
+      <c r="X450" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y450" s="2" t="inlineStr"/>
+      <c r="Z450" s="2" t="inlineStr"/>
+      <c r="AA450" s="2" t="inlineStr"/>
+      <c r="AB450" s="2" t="inlineStr"/>
+      <c r="AC450" s="2" t="inlineStr"/>
+      <c r="AD450" s="2" t="inlineStr"/>
+      <c r="AE450" s="2" t="inlineStr"/>
+      <c r="AF450" s="2" t="inlineStr"/>
+      <c r="AG450" s="2" t="inlineStr"/>
+      <c r="AH450" s="2" t="inlineStr"/>
+      <c r="AI450" s="2" t="inlineStr"/>
+      <c r="AJ450" s="2" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>b6ea2935c35449fb</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>68565</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K451" s="2" t="inlineStr"/>
+      <c r="L451" s="2" t="inlineStr">
+        <is>
+          <t>0.589593</t>
+        </is>
+      </c>
+      <c r="M451" s="2" t="inlineStr"/>
+      <c r="N451" s="2" t="inlineStr"/>
+      <c r="O451" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P451" s="2" t="inlineStr"/>
+      <c r="Q451" s="2" t="inlineStr">
+        <is>
+          <t>-0.09091818210862612</t>
+        </is>
+      </c>
+      <c r="R451" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:32.741667Z</t>
+        </is>
+      </c>
+      <c r="S451" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T451" s="2" t="inlineStr"/>
+      <c r="U451" s="2" t="inlineStr"/>
+      <c r="V451" s="2" t="inlineStr"/>
+      <c r="W451" s="2" t="inlineStr"/>
+      <c r="X451" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y451" s="2" t="inlineStr"/>
+      <c r="Z451" s="2" t="inlineStr"/>
+      <c r="AA451" s="2" t="inlineStr"/>
+      <c r="AB451" s="2" t="inlineStr"/>
+      <c r="AC451" s="2" t="inlineStr"/>
+      <c r="AD451" s="2" t="inlineStr"/>
+      <c r="AE451" s="2" t="inlineStr"/>
+      <c r="AF451" s="2" t="inlineStr"/>
+      <c r="AG451" s="2" t="inlineStr"/>
+      <c r="AH451" s="2" t="inlineStr"/>
+      <c r="AI451" s="2" t="inlineStr"/>
+      <c r="AJ451" s="2" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>ffe11112fd844026</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>68567</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K452" s="2" t="inlineStr"/>
+      <c r="L452" s="2" t="inlineStr">
+        <is>
+          <t>0.516525</t>
+        </is>
+      </c>
+      <c r="M452" s="2" t="inlineStr"/>
+      <c r="N452" s="2" t="inlineStr"/>
+      <c r="O452" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P452" s="2" t="inlineStr"/>
+      <c r="Q452" s="2" t="inlineStr">
+        <is>
+          <t>-0.07363893442622949</t>
+        </is>
+      </c>
+      <c r="R452" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:33.236212Z</t>
+        </is>
+      </c>
+      <c r="S452" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T452" s="2" t="inlineStr"/>
+      <c r="U452" s="2" t="inlineStr"/>
+      <c r="V452" s="2" t="inlineStr"/>
+      <c r="W452" s="2" t="inlineStr"/>
+      <c r="X452" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y452" s="2" t="inlineStr"/>
+      <c r="Z452" s="2" t="inlineStr"/>
+      <c r="AA452" s="2" t="inlineStr"/>
+      <c r="AB452" s="2" t="inlineStr"/>
+      <c r="AC452" s="2" t="inlineStr"/>
+      <c r="AD452" s="2" t="inlineStr"/>
+      <c r="AE452" s="2" t="inlineStr"/>
+      <c r="AF452" s="2" t="inlineStr"/>
+      <c r="AG452" s="2" t="inlineStr"/>
+      <c r="AH452" s="2" t="inlineStr"/>
+      <c r="AI452" s="2" t="inlineStr"/>
+      <c r="AJ452" s="2" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>ad31bbb186aa407d</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J453" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K453" s="2" t="inlineStr"/>
+      <c r="L453" s="2" t="inlineStr">
+        <is>
+          <t>0.500399</t>
+        </is>
+      </c>
+      <c r="M453" s="2" t="inlineStr"/>
+      <c r="N453" s="2" t="inlineStr"/>
+      <c r="O453" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P453" s="2" t="inlineStr"/>
+      <c r="Q453" s="2" t="inlineStr">
+        <is>
+          <t>-0.07041645064377677</t>
+        </is>
+      </c>
+      <c r="R453" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:33.976053Z</t>
+        </is>
+      </c>
+      <c r="S453" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T453" s="2" t="inlineStr"/>
+      <c r="U453" s="2" t="inlineStr"/>
+      <c r="V453" s="2" t="inlineStr"/>
+      <c r="W453" s="2" t="inlineStr"/>
+      <c r="X453" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y453" s="2" t="inlineStr"/>
+      <c r="Z453" s="2" t="inlineStr"/>
+      <c r="AA453" s="2" t="inlineStr"/>
+      <c r="AB453" s="2" t="inlineStr"/>
+      <c r="AC453" s="2" t="inlineStr"/>
+      <c r="AD453" s="2" t="inlineStr"/>
+      <c r="AE453" s="2" t="inlineStr"/>
+      <c r="AF453" s="2" t="inlineStr"/>
+      <c r="AG453" s="2" t="inlineStr"/>
+      <c r="AH453" s="2" t="inlineStr"/>
+      <c r="AI453" s="2" t="inlineStr"/>
+      <c r="AJ453" s="2" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>d243b878375547a4</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>70533</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K454" s="2" t="inlineStr"/>
+      <c r="L454" s="2" t="inlineStr">
+        <is>
+          <t>0.509301</t>
+        </is>
+      </c>
+      <c r="M454" s="2" t="inlineStr"/>
+      <c r="N454" s="2" t="inlineStr"/>
+      <c r="O454" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P454" s="2" t="inlineStr"/>
+      <c r="Q454" s="2" t="inlineStr">
+        <is>
+          <t>-0.11047086311787069</t>
+        </is>
+      </c>
+      <c r="R454" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:35.206941Z</t>
+        </is>
+      </c>
+      <c r="S454" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T454" s="2" t="inlineStr"/>
+      <c r="U454" s="2" t="inlineStr"/>
+      <c r="V454" s="2" t="inlineStr"/>
+      <c r="W454" s="2" t="inlineStr"/>
+      <c r="X454" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y454" s="2" t="inlineStr"/>
+      <c r="Z454" s="2" t="inlineStr"/>
+      <c r="AA454" s="2" t="inlineStr"/>
+      <c r="AB454" s="2" t="inlineStr"/>
+      <c r="AC454" s="2" t="inlineStr"/>
+      <c r="AD454" s="2" t="inlineStr"/>
+      <c r="AE454" s="2" t="inlineStr"/>
+      <c r="AF454" s="2" t="inlineStr"/>
+      <c r="AG454" s="2" t="inlineStr"/>
+      <c r="AH454" s="2" t="inlineStr"/>
+      <c r="AI454" s="2" t="inlineStr"/>
+      <c r="AJ454" s="2" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>d3aff28604c244df</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K455" s="2" t="inlineStr"/>
+      <c r="L455" s="2" t="inlineStr">
+        <is>
+          <t>0.576417</t>
+        </is>
+      </c>
+      <c r="M455" s="2" t="inlineStr"/>
+      <c r="N455" s="2" t="inlineStr"/>
+      <c r="O455" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P455" s="2" t="inlineStr"/>
+      <c r="Q455" s="2" t="inlineStr">
+        <is>
+          <t>0.0056015493562231455</t>
+        </is>
+      </c>
+      <c r="R455" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:36.461414Z</t>
+        </is>
+      </c>
+      <c r="S455" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T455" s="2" t="inlineStr"/>
+      <c r="U455" s="2" t="inlineStr"/>
+      <c r="V455" s="2" t="inlineStr"/>
+      <c r="W455" s="2" t="inlineStr"/>
+      <c r="X455" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y455" s="2" t="inlineStr"/>
+      <c r="Z455" s="2" t="inlineStr"/>
+      <c r="AA455" s="2" t="inlineStr"/>
+      <c r="AB455" s="2" t="inlineStr"/>
+      <c r="AC455" s="2" t="inlineStr"/>
+      <c r="AD455" s="2" t="inlineStr"/>
+      <c r="AE455" s="2" t="inlineStr"/>
+      <c r="AF455" s="2" t="inlineStr"/>
+      <c r="AG455" s="2" t="inlineStr"/>
+      <c r="AH455" s="2" t="inlineStr"/>
+      <c r="AI455" s="2" t="inlineStr"/>
+      <c r="AJ455" s="2" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>f8385502a19f4e79</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K456" s="2" t="inlineStr"/>
+      <c r="L456" s="2" t="inlineStr">
+        <is>
+          <t>0.698419</t>
+        </is>
+      </c>
+      <c r="M456" s="2" t="inlineStr"/>
+      <c r="N456" s="2" t="inlineStr"/>
+      <c r="O456" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P456" s="2" t="inlineStr"/>
+      <c r="Q456" s="2" t="inlineStr">
+        <is>
+          <t>0.1679025680751174</t>
+        </is>
+      </c>
+      <c r="R456" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:39.377337Z</t>
+        </is>
+      </c>
+      <c r="S456" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T456" s="2" t="inlineStr"/>
+      <c r="U456" s="2" t="inlineStr"/>
+      <c r="V456" s="2" t="inlineStr"/>
+      <c r="W456" s="2" t="inlineStr"/>
+      <c r="X456" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y456" s="2" t="inlineStr"/>
+      <c r="Z456" s="2" t="inlineStr"/>
+      <c r="AA456" s="2" t="inlineStr"/>
+      <c r="AB456" s="2" t="inlineStr"/>
+      <c r="AC456" s="2" t="inlineStr"/>
+      <c r="AD456" s="2" t="inlineStr"/>
+      <c r="AE456" s="2" t="inlineStr"/>
+      <c r="AF456" s="2" t="inlineStr"/>
+      <c r="AG456" s="2" t="inlineStr"/>
+      <c r="AH456" s="2" t="inlineStr"/>
+      <c r="AI456" s="2" t="inlineStr"/>
+      <c r="AJ456" s="2" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>a18216c095c946b2</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K457" s="2" t="inlineStr"/>
+      <c r="L457" s="2" t="inlineStr">
+        <is>
+          <t>0.556222</t>
+        </is>
+      </c>
+      <c r="M457" s="2" t="inlineStr"/>
+      <c r="N457" s="2" t="inlineStr"/>
+      <c r="O457" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P457" s="2" t="inlineStr"/>
+      <c r="Q457" s="2" t="inlineStr">
+        <is>
+          <t>0.03699123076923083</t>
+        </is>
+      </c>
+      <c r="R457" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:39.880431Z</t>
+        </is>
+      </c>
+      <c r="S457" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T457" s="2" t="inlineStr"/>
+      <c r="U457" s="2" t="inlineStr"/>
+      <c r="V457" s="2" t="inlineStr"/>
+      <c r="W457" s="2" t="inlineStr"/>
+      <c r="X457" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y457" s="2" t="inlineStr"/>
+      <c r="Z457" s="2" t="inlineStr"/>
+      <c r="AA457" s="2" t="inlineStr"/>
+      <c r="AB457" s="2" t="inlineStr"/>
+      <c r="AC457" s="2" t="inlineStr"/>
+      <c r="AD457" s="2" t="inlineStr"/>
+      <c r="AE457" s="2" t="inlineStr"/>
+      <c r="AF457" s="2" t="inlineStr"/>
+      <c r="AG457" s="2" t="inlineStr"/>
+      <c r="AH457" s="2" t="inlineStr"/>
+      <c r="AI457" s="2" t="inlineStr"/>
+      <c r="AJ457" s="2" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>9edb99cd2a6c4126</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K458" s="2" t="inlineStr"/>
+      <c r="L458" s="2" t="inlineStr">
+        <is>
+          <t>0.6138</t>
+        </is>
+      </c>
+      <c r="M458" s="2" t="inlineStr"/>
+      <c r="N458" s="2" t="inlineStr"/>
+      <c r="O458" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P458" s="2" t="inlineStr"/>
+      <c r="Q458" s="2" t="inlineStr">
+        <is>
+          <t>0.0429845493562232</t>
+        </is>
+      </c>
+      <c r="R458" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:40.547769Z</t>
+        </is>
+      </c>
+      <c r="S458" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T458" s="2" t="inlineStr"/>
+      <c r="U458" s="2" t="inlineStr"/>
+      <c r="V458" s="2" t="inlineStr"/>
+      <c r="W458" s="2" t="inlineStr"/>
+      <c r="X458" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y458" s="2" t="inlineStr"/>
+      <c r="Z458" s="2" t="inlineStr"/>
+      <c r="AA458" s="2" t="inlineStr"/>
+      <c r="AB458" s="2" t="inlineStr"/>
+      <c r="AC458" s="2" t="inlineStr"/>
+      <c r="AD458" s="2" t="inlineStr"/>
+      <c r="AE458" s="2" t="inlineStr"/>
+      <c r="AF458" s="2" t="inlineStr"/>
+      <c r="AG458" s="2" t="inlineStr"/>
+      <c r="AH458" s="2" t="inlineStr"/>
+      <c r="AI458" s="2" t="inlineStr"/>
+      <c r="AJ458" s="2" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>7ec9d2eace6f4e87</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K459" s="2" t="inlineStr"/>
+      <c r="L459" s="2" t="inlineStr">
+        <is>
+          <t>0.67501</t>
+        </is>
+      </c>
+      <c r="M459" s="2" t="inlineStr"/>
+      <c r="N459" s="2" t="inlineStr"/>
+      <c r="O459" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P459" s="2" t="inlineStr"/>
+      <c r="Q459" s="2" t="inlineStr">
+        <is>
+          <t>0.07500999999999991</t>
+        </is>
+      </c>
+      <c r="R459" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:41.093797Z</t>
+        </is>
+      </c>
+      <c r="S459" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T459" s="2" t="inlineStr"/>
+      <c r="U459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr"/>
+      <c r="W459" s="2" t="inlineStr"/>
+      <c r="X459" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y459" s="2" t="inlineStr"/>
+      <c r="Z459" s="2" t="inlineStr"/>
+      <c r="AA459" s="2" t="inlineStr"/>
+      <c r="AB459" s="2" t="inlineStr"/>
+      <c r="AC459" s="2" t="inlineStr"/>
+      <c r="AD459" s="2" t="inlineStr"/>
+      <c r="AE459" s="2" t="inlineStr"/>
+      <c r="AF459" s="2" t="inlineStr"/>
+      <c r="AG459" s="2" t="inlineStr"/>
+      <c r="AH459" s="2" t="inlineStr"/>
+      <c r="AI459" s="2" t="inlineStr"/>
+      <c r="AJ459" s="2" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>6496c090d38d4995</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>69537</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K460" s="2" t="inlineStr"/>
+      <c r="L460" s="2" t="inlineStr">
+        <is>
+          <t>0.536892</t>
+        </is>
+      </c>
+      <c r="M460" s="2" t="inlineStr"/>
+      <c r="N460" s="2" t="inlineStr"/>
+      <c r="O460" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P460" s="2" t="inlineStr"/>
+      <c r="Q460" s="2" t="inlineStr">
+        <is>
+          <t>0.10770745064377685</t>
+        </is>
+      </c>
+      <c r="R460" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:45.110727Z</t>
+        </is>
+      </c>
+      <c r="S460" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T460" s="2" t="inlineStr"/>
+      <c r="U460" s="2" t="inlineStr"/>
+      <c r="V460" s="2" t="inlineStr"/>
+      <c r="W460" s="2" t="inlineStr"/>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="inlineStr"/>
+      <c r="Z460" s="2" t="inlineStr"/>
+      <c r="AA460" s="2" t="inlineStr"/>
+      <c r="AB460" s="2" t="inlineStr"/>
+      <c r="AC460" s="2" t="inlineStr"/>
+      <c r="AD460" s="2" t="inlineStr"/>
+      <c r="AE460" s="2" t="inlineStr"/>
+      <c r="AF460" s="2" t="inlineStr"/>
+      <c r="AG460" s="2" t="inlineStr"/>
+      <c r="AH460" s="2" t="inlineStr"/>
+      <c r="AI460" s="2" t="inlineStr"/>
+      <c r="AJ460" s="2" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>0f75d567feef4604</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>71199</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K461" s="2" t="inlineStr"/>
+      <c r="L461" s="2" t="inlineStr">
+        <is>
+          <t>0.505972</t>
+        </is>
+      </c>
+      <c r="M461" s="2" t="inlineStr"/>
+      <c r="N461" s="2" t="inlineStr"/>
+      <c r="O461" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P461" s="2" t="inlineStr"/>
+      <c r="Q461" s="2" t="inlineStr">
+        <is>
+          <t>0.0364884319248826</t>
+        </is>
+      </c>
+      <c r="R461" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:47.291214Z</t>
+        </is>
+      </c>
+      <c r="S461" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T461" s="2" t="inlineStr"/>
+      <c r="U461" s="2" t="inlineStr"/>
+      <c r="V461" s="2" t="inlineStr"/>
+      <c r="W461" s="2" t="inlineStr"/>
+      <c r="X461" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y461" s="2" t="inlineStr"/>
+      <c r="Z461" s="2" t="inlineStr"/>
+      <c r="AA461" s="2" t="inlineStr"/>
+      <c r="AB461" s="2" t="inlineStr"/>
+      <c r="AC461" s="2" t="inlineStr"/>
+      <c r="AD461" s="2" t="inlineStr"/>
+      <c r="AE461" s="2" t="inlineStr"/>
+      <c r="AF461" s="2" t="inlineStr"/>
+      <c r="AG461" s="2" t="inlineStr"/>
+      <c r="AH461" s="2" t="inlineStr"/>
+      <c r="AI461" s="2" t="inlineStr"/>
+      <c r="AJ461" s="2" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>f840ed211b4545a7</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>69553</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K462" s="2" t="inlineStr"/>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>0.585819</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr"/>
+      <c r="N462" s="2" t="inlineStr"/>
+      <c r="O462" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P462" s="2" t="inlineStr"/>
+      <c r="Q462" s="2" t="inlineStr">
+        <is>
+          <t>-0.09469218210862618</t>
+        </is>
+      </c>
+      <c r="R462" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:48.296318Z</t>
+        </is>
+      </c>
+      <c r="S462" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr"/>
+      <c r="U462" s="2" t="inlineStr"/>
+      <c r="V462" s="2" t="inlineStr"/>
+      <c r="W462" s="2" t="inlineStr"/>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="inlineStr"/>
+      <c r="Z462" s="2" t="inlineStr"/>
+      <c r="AA462" s="2" t="inlineStr"/>
+      <c r="AB462" s="2" t="inlineStr"/>
+      <c r="AC462" s="2" t="inlineStr"/>
+      <c r="AD462" s="2" t="inlineStr"/>
+      <c r="AE462" s="2" t="inlineStr"/>
+      <c r="AF462" s="2" t="inlineStr"/>
+      <c r="AG462" s="2" t="inlineStr"/>
+      <c r="AH462" s="2" t="inlineStr"/>
+      <c r="AI462" s="2" t="inlineStr"/>
+      <c r="AJ462" s="2" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>7c7ca0d09e9249a2</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K463" s="2" t="inlineStr"/>
+      <c r="L463" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M463" s="2" t="inlineStr"/>
+      <c r="N463" s="2" t="inlineStr"/>
+      <c r="O463" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P463" s="2" t="inlineStr"/>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>-0.03241436563876654</t>
+        </is>
+      </c>
+      <c r="R463" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:48.811628Z</t>
+        </is>
+      </c>
+      <c r="S463" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T463" s="2" t="inlineStr"/>
+      <c r="U463" s="2" t="inlineStr"/>
+      <c r="V463" s="2" t="inlineStr"/>
+      <c r="W463" s="2" t="inlineStr"/>
+      <c r="X463" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y463" s="2" t="inlineStr"/>
+      <c r="Z463" s="2" t="inlineStr"/>
+      <c r="AA463" s="2" t="inlineStr"/>
+      <c r="AB463" s="2" t="inlineStr"/>
+      <c r="AC463" s="2" t="inlineStr"/>
+      <c r="AD463" s="2" t="inlineStr"/>
+      <c r="AE463" s="2" t="inlineStr"/>
+      <c r="AF463" s="2" t="inlineStr"/>
+      <c r="AG463" s="2" t="inlineStr"/>
+      <c r="AH463" s="2" t="inlineStr"/>
+      <c r="AI463" s="2" t="inlineStr"/>
+      <c r="AJ463" s="2" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>13d3deb382f543ff</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>69615</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K464" s="2" t="inlineStr"/>
+      <c r="L464" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M464" s="2" t="inlineStr"/>
+      <c r="N464" s="2" t="inlineStr"/>
+      <c r="O464" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="inlineStr"/>
+      <c r="Q464" s="2" t="inlineStr">
+        <is>
+          <t>0.05757343192488262</t>
+        </is>
+      </c>
+      <c r="R464" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:49.329396Z</t>
+        </is>
+      </c>
+      <c r="S464" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T464" s="2" t="inlineStr"/>
+      <c r="U464" s="2" t="inlineStr"/>
+      <c r="V464" s="2" t="inlineStr"/>
+      <c r="W464" s="2" t="inlineStr"/>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="inlineStr"/>
+      <c r="Z464" s="2" t="inlineStr"/>
+      <c r="AA464" s="2" t="inlineStr"/>
+      <c r="AB464" s="2" t="inlineStr"/>
+      <c r="AC464" s="2" t="inlineStr"/>
+      <c r="AD464" s="2" t="inlineStr"/>
+      <c r="AE464" s="2" t="inlineStr"/>
+      <c r="AF464" s="2" t="inlineStr"/>
+      <c r="AG464" s="2" t="inlineStr"/>
+      <c r="AH464" s="2" t="inlineStr"/>
+      <c r="AI464" s="2" t="inlineStr"/>
+      <c r="AJ464" s="2" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>ac0b785f475a4469</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K465" s="2" t="inlineStr"/>
+      <c r="L465" s="2" t="inlineStr">
+        <is>
+          <t>0.537618</t>
+        </is>
+      </c>
+      <c r="M465" s="2" t="inlineStr"/>
+      <c r="N465" s="2" t="inlineStr"/>
+      <c r="O465" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P465" s="2" t="inlineStr"/>
+      <c r="Q465" s="2" t="inlineStr">
+        <is>
+          <t>-0.04221393277310914</t>
+        </is>
+      </c>
+      <c r="R465" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:50.421327Z</t>
+        </is>
+      </c>
+      <c r="S465" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T465" s="2" t="inlineStr"/>
+      <c r="U465" s="2" t="inlineStr"/>
+      <c r="V465" s="2" t="inlineStr"/>
+      <c r="W465" s="2" t="inlineStr"/>
+      <c r="X465" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y465" s="2" t="inlineStr"/>
+      <c r="Z465" s="2" t="inlineStr"/>
+      <c r="AA465" s="2" t="inlineStr"/>
+      <c r="AB465" s="2" t="inlineStr"/>
+      <c r="AC465" s="2" t="inlineStr"/>
+      <c r="AD465" s="2" t="inlineStr"/>
+      <c r="AE465" s="2" t="inlineStr"/>
+      <c r="AF465" s="2" t="inlineStr"/>
+      <c r="AG465" s="2" t="inlineStr"/>
+      <c r="AH465" s="2" t="inlineStr"/>
+      <c r="AI465" s="2" t="inlineStr"/>
+      <c r="AJ465" s="2" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>5be186953be14011</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>69617</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K466" s="2" t="inlineStr"/>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>0.626886</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr"/>
+      <c r="N466" s="2" t="inlineStr"/>
+      <c r="O466" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P466" s="2" t="inlineStr"/>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>0.017511000000000054</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:50.955785Z</t>
+        </is>
+      </c>
+      <c r="S466" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr"/>
+      <c r="U466" s="2" t="inlineStr"/>
+      <c r="V466" s="2" t="inlineStr"/>
+      <c r="W466" s="2" t="inlineStr"/>
+      <c r="X466" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y466" s="2" t="inlineStr"/>
+      <c r="Z466" s="2" t="inlineStr"/>
+      <c r="AA466" s="2" t="inlineStr"/>
+      <c r="AB466" s="2" t="inlineStr"/>
+      <c r="AC466" s="2" t="inlineStr"/>
+      <c r="AD466" s="2" t="inlineStr"/>
+      <c r="AE466" s="2" t="inlineStr"/>
+      <c r="AF466" s="2" t="inlineStr"/>
+      <c r="AG466" s="2" t="inlineStr"/>
+      <c r="AH466" s="2" t="inlineStr"/>
+      <c r="AI466" s="2" t="inlineStr"/>
+      <c r="AJ466" s="2" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>66ed6d204d284ea6</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>69845</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K467" s="2" t="inlineStr"/>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr"/>
+      <c r="N467" s="2" t="inlineStr"/>
+      <c r="O467" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P467" s="2" t="inlineStr"/>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>0.007826230769230835</t>
+        </is>
+      </c>
+      <c r="R467" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:51.479255Z</t>
+        </is>
+      </c>
+      <c r="S467" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr"/>
+      <c r="U467" s="2" t="inlineStr"/>
+      <c r="V467" s="2" t="inlineStr"/>
+      <c r="W467" s="2" t="inlineStr"/>
+      <c r="X467" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y467" s="2" t="inlineStr"/>
+      <c r="Z467" s="2" t="inlineStr"/>
+      <c r="AA467" s="2" t="inlineStr"/>
+      <c r="AB467" s="2" t="inlineStr"/>
+      <c r="AC467" s="2" t="inlineStr"/>
+      <c r="AD467" s="2" t="inlineStr"/>
+      <c r="AE467" s="2" t="inlineStr"/>
+      <c r="AF467" s="2" t="inlineStr"/>
+      <c r="AG467" s="2" t="inlineStr"/>
+      <c r="AH467" s="2" t="inlineStr"/>
+      <c r="AI467" s="2" t="inlineStr"/>
+      <c r="AJ467" s="2" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>52a98a471aeb4535</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>69866</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K468" s="2" t="inlineStr"/>
+      <c r="L468" s="2" t="inlineStr">
+        <is>
+          <t>0.588155</t>
+        </is>
+      </c>
+      <c r="M468" s="2" t="inlineStr"/>
+      <c r="N468" s="2" t="inlineStr"/>
+      <c r="O468" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P468" s="2" t="inlineStr"/>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>0.20792686311787067</t>
+        </is>
+      </c>
+      <c r="R468" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:51.969876Z</t>
+        </is>
+      </c>
+      <c r="S468" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T468" s="2" t="inlineStr"/>
+      <c r="U468" s="2" t="inlineStr"/>
+      <c r="V468" s="2" t="inlineStr"/>
+      <c r="W468" s="2" t="inlineStr"/>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="inlineStr"/>
+      <c r="Z468" s="2" t="inlineStr"/>
+      <c r="AA468" s="2" t="inlineStr"/>
+      <c r="AB468" s="2" t="inlineStr"/>
+      <c r="AC468" s="2" t="inlineStr"/>
+      <c r="AD468" s="2" t="inlineStr"/>
+      <c r="AE468" s="2" t="inlineStr"/>
+      <c r="AF468" s="2" t="inlineStr"/>
+      <c r="AG468" s="2" t="inlineStr"/>
+      <c r="AH468" s="2" t="inlineStr"/>
+      <c r="AI468" s="2" t="inlineStr"/>
+      <c r="AJ468" s="2" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>c0247001486b45ba</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>69868</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K469" s="2" t="inlineStr"/>
+      <c r="L469" s="2" t="inlineStr">
+        <is>
+          <t>0.556407</t>
+        </is>
+      </c>
+      <c r="M469" s="2" t="inlineStr"/>
+      <c r="N469" s="2" t="inlineStr"/>
+      <c r="O469" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P469" s="2" t="inlineStr"/>
+      <c r="Q469" s="2" t="inlineStr">
+        <is>
+          <t>-0.09394265034965033</t>
+        </is>
+      </c>
+      <c r="R469" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:52.462475Z</t>
+        </is>
+      </c>
+      <c r="S469" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T469" s="2" t="inlineStr"/>
+      <c r="U469" s="2" t="inlineStr"/>
+      <c r="V469" s="2" t="inlineStr"/>
+      <c r="W469" s="2" t="inlineStr"/>
+      <c r="X469" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y469" s="2" t="inlineStr"/>
+      <c r="Z469" s="2" t="inlineStr"/>
+      <c r="AA469" s="2" t="inlineStr"/>
+      <c r="AB469" s="2" t="inlineStr"/>
+      <c r="AC469" s="2" t="inlineStr"/>
+      <c r="AD469" s="2" t="inlineStr"/>
+      <c r="AE469" s="2" t="inlineStr"/>
+      <c r="AF469" s="2" t="inlineStr"/>
+      <c r="AG469" s="2" t="inlineStr"/>
+      <c r="AH469" s="2" t="inlineStr"/>
+      <c r="AI469" s="2" t="inlineStr"/>
+      <c r="AJ469" s="2" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>d206199ba0f14cf8</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>70104</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K470" s="2" t="inlineStr"/>
+      <c r="L470" s="2" t="inlineStr">
+        <is>
+          <t>0.525997</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="inlineStr"/>
+      <c r="N470" s="2" t="inlineStr"/>
+      <c r="O470" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P470" s="2" t="inlineStr"/>
+      <c r="Q470" s="2" t="inlineStr">
+        <is>
+          <t>0.025997000000000048</t>
+        </is>
+      </c>
+      <c r="R470" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:18:52.998625Z</t>
+        </is>
+      </c>
+      <c r="S470" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T470" s="2" t="inlineStr"/>
+      <c r="U470" s="2" t="inlineStr"/>
+      <c r="V470" s="2" t="inlineStr"/>
+      <c r="W470" s="2" t="inlineStr"/>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="inlineStr"/>
+      <c r="Z470" s="2" t="inlineStr"/>
+      <c r="AA470" s="2" t="inlineStr"/>
+      <c r="AB470" s="2" t="inlineStr"/>
+      <c r="AC470" s="2" t="inlineStr"/>
+      <c r="AD470" s="2" t="inlineStr"/>
+      <c r="AE470" s="2" t="inlineStr"/>
+      <c r="AF470" s="2" t="inlineStr"/>
+      <c r="AG470" s="2" t="inlineStr"/>
+      <c r="AH470" s="2" t="inlineStr"/>
+      <c r="AI470" s="2" t="inlineStr"/>
+      <c r="AJ470" s="2" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>6b11a2939d9c46e4</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>68472</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K471" s="2" t="inlineStr"/>
+      <c r="L471" s="2" t="inlineStr">
+        <is>
+          <t>0.513199</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="inlineStr"/>
+      <c r="N471" s="2" t="inlineStr"/>
+      <c r="O471" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P471" s="2" t="inlineStr"/>
+      <c r="Q471" s="2" t="inlineStr">
+        <is>
+          <t>-0.04627236563876658</t>
+        </is>
+      </c>
+      <c r="R471" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.175897Z</t>
+        </is>
+      </c>
+      <c r="S471" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="T471" s="2" t="inlineStr"/>
+      <c r="U471" s="2" t="inlineStr"/>
+      <c r="V471" s="2" t="inlineStr"/>
+      <c r="W471" s="2" t="inlineStr"/>
+      <c r="X471" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y471" s="2" t="inlineStr"/>
+      <c r="Z471" s="2" t="inlineStr"/>
+      <c r="AA471" s="2" t="inlineStr"/>
+      <c r="AB471" s="2" t="inlineStr"/>
+      <c r="AC471" s="2" t="inlineStr"/>
+      <c r="AD471" s="2" t="inlineStr"/>
+      <c r="AE471" s="2" t="inlineStr"/>
+      <c r="AF471" s="2" t="inlineStr"/>
+      <c r="AG471" s="2" t="inlineStr"/>
+      <c r="AH471" s="2" t="inlineStr"/>
+      <c r="AI471" s="2" t="inlineStr"/>
+      <c r="AJ471" s="2" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>178759b2872a4fa0</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>68302</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K472" s="2" t="inlineStr"/>
+      <c r="L472" s="2" t="inlineStr">
+        <is>
+          <t>0.551011</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="inlineStr"/>
+      <c r="N472" s="2" t="inlineStr"/>
+      <c r="O472" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P472" s="2" t="inlineStr"/>
+      <c r="Q472" s="2" t="inlineStr">
+        <is>
+          <t>0.0608149215686275</t>
+        </is>
+      </c>
+      <c r="R472" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.737438Z</t>
+        </is>
+      </c>
+      <c r="S472" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T472" s="2" t="inlineStr"/>
+      <c r="U472" s="2" t="inlineStr"/>
+      <c r="V472" s="2" t="inlineStr"/>
+      <c r="W472" s="2" t="inlineStr"/>
+      <c r="X472" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="inlineStr"/>
+      <c r="Z472" s="2" t="inlineStr"/>
+      <c r="AA472" s="2" t="inlineStr"/>
+      <c r="AB472" s="2" t="inlineStr"/>
+      <c r="AC472" s="2" t="inlineStr"/>
+      <c r="AD472" s="2" t="inlineStr"/>
+      <c r="AE472" s="2" t="inlineStr"/>
+      <c r="AF472" s="2" t="inlineStr"/>
+      <c r="AG472" s="2" t="inlineStr"/>
+      <c r="AH472" s="2" t="inlineStr"/>
+      <c r="AI472" s="2" t="inlineStr"/>
+      <c r="AJ472" s="2" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>ba3238f89c554e7b</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>68301</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K473" s="2" t="inlineStr"/>
+      <c r="L473" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="inlineStr"/>
+      <c r="N473" s="2" t="inlineStr"/>
+      <c r="O473" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P473" s="2" t="inlineStr"/>
+      <c r="Q473" s="2" t="inlineStr">
+        <is>
+          <t>-0.0034594319248826277</t>
+        </is>
+      </c>
+      <c r="R473" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:25.426369Z</t>
+        </is>
+      </c>
+      <c r="S473" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T473" s="2" t="inlineStr"/>
+      <c r="U473" s="2" t="inlineStr"/>
+      <c r="V473" s="2" t="inlineStr"/>
+      <c r="W473" s="2" t="inlineStr"/>
+      <c r="X473" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y473" s="2" t="inlineStr"/>
+      <c r="Z473" s="2" t="inlineStr"/>
+      <c r="AA473" s="2" t="inlineStr"/>
+      <c r="AB473" s="2" t="inlineStr"/>
+      <c r="AC473" s="2" t="inlineStr"/>
+      <c r="AD473" s="2" t="inlineStr"/>
+      <c r="AE473" s="2" t="inlineStr"/>
+      <c r="AF473" s="2" t="inlineStr"/>
+      <c r="AG473" s="2" t="inlineStr"/>
+      <c r="AH473" s="2" t="inlineStr"/>
+      <c r="AI473" s="2" t="inlineStr"/>
+      <c r="AJ473" s="2" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2a3773534d97440d</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K474" s="2" t="inlineStr"/>
+      <c r="L474" s="2" t="inlineStr">
+        <is>
+          <t>0.691594</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="inlineStr"/>
+      <c r="N474" s="2" t="inlineStr"/>
+      <c r="O474" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P474" s="2" t="inlineStr"/>
+      <c r="Q474" s="2" t="inlineStr">
+        <is>
+          <t>0.11176206722689086</t>
+        </is>
+      </c>
+      <c r="R474" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:25.971824Z</t>
+        </is>
+      </c>
+      <c r="S474" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T474" s="2" t="inlineStr"/>
+      <c r="U474" s="2" t="inlineStr"/>
+      <c r="V474" s="2" t="inlineStr"/>
+      <c r="W474" s="2" t="inlineStr"/>
+      <c r="X474" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y474" s="2" t="inlineStr"/>
+      <c r="Z474" s="2" t="inlineStr"/>
+      <c r="AA474" s="2" t="inlineStr"/>
+      <c r="AB474" s="2" t="inlineStr"/>
+      <c r="AC474" s="2" t="inlineStr"/>
+      <c r="AD474" s="2" t="inlineStr"/>
+      <c r="AE474" s="2" t="inlineStr"/>
+      <c r="AF474" s="2" t="inlineStr"/>
+      <c r="AG474" s="2" t="inlineStr"/>
+      <c r="AH474" s="2" t="inlineStr"/>
+      <c r="AI474" s="2" t="inlineStr"/>
+      <c r="AJ474" s="2" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>3f3b6e2c066c44a1</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>71213</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K475" s="2" t="inlineStr"/>
+      <c r="L475" s="2" t="inlineStr">
+        <is>
+          <t>0.719577</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="inlineStr"/>
+      <c r="N475" s="2" t="inlineStr"/>
+      <c r="O475" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P475" s="2" t="inlineStr"/>
+      <c r="Q475" s="2" t="inlineStr">
+        <is>
+          <t>0.2293809215686275</t>
+        </is>
+      </c>
+      <c r="R475" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:27.119976Z</t>
+        </is>
+      </c>
+      <c r="S475" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="T475" s="2" t="inlineStr"/>
+      <c r="U475" s="2" t="inlineStr"/>
+      <c r="V475" s="2" t="inlineStr"/>
+      <c r="W475" s="2" t="inlineStr"/>
+      <c r="X475" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y475" s="2" t="inlineStr"/>
+      <c r="Z475" s="2" t="inlineStr"/>
+      <c r="AA475" s="2" t="inlineStr"/>
+      <c r="AB475" s="2" t="inlineStr"/>
+      <c r="AC475" s="2" t="inlineStr"/>
+      <c r="AD475" s="2" t="inlineStr"/>
+      <c r="AE475" s="2" t="inlineStr"/>
+      <c r="AF475" s="2" t="inlineStr"/>
+      <c r="AG475" s="2" t="inlineStr"/>
+      <c r="AH475" s="2" t="inlineStr"/>
+      <c r="AI475" s="2" t="inlineStr"/>
+      <c r="AJ475" s="2" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>63cf563532054698</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>71280</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K476" s="2" t="inlineStr"/>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>0.640948</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr"/>
+      <c r="N476" s="2" t="inlineStr"/>
+      <c r="O476" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P476" s="2" t="inlineStr"/>
+      <c r="Q476" s="2" t="inlineStr">
+        <is>
+          <t>-0.029018996699670008</t>
+        </is>
+      </c>
+      <c r="R476" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:27.768400Z</t>
+        </is>
+      </c>
+      <c r="S476" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="T476" s="2" t="inlineStr"/>
+      <c r="U476" s="2" t="inlineStr"/>
+      <c r="V476" s="2" t="inlineStr"/>
+      <c r="W476" s="2" t="inlineStr"/>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="inlineStr"/>
+      <c r="Z476" s="2" t="inlineStr"/>
+      <c r="AA476" s="2" t="inlineStr"/>
+      <c r="AB476" s="2" t="inlineStr"/>
+      <c r="AC476" s="2" t="inlineStr"/>
+      <c r="AD476" s="2" t="inlineStr"/>
+      <c r="AE476" s="2" t="inlineStr"/>
+      <c r="AF476" s="2" t="inlineStr"/>
+      <c r="AG476" s="2" t="inlineStr"/>
+      <c r="AH476" s="2" t="inlineStr"/>
+      <c r="AI476" s="2" t="inlineStr"/>
+      <c r="AJ476" s="2" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2d0977a26b2e43d6</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>68435</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K477" s="2" t="inlineStr"/>
+      <c r="L477" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="inlineStr"/>
+      <c r="N477" s="2" t="inlineStr"/>
+      <c r="O477" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P477" s="2" t="inlineStr"/>
+      <c r="Q477" s="2" t="inlineStr">
+        <is>
+          <t>0.136432</t>
+        </is>
+      </c>
+      <c r="R477" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:28.310332Z</t>
+        </is>
+      </c>
+      <c r="S477" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr"/>
+      <c r="U477" s="2" t="inlineStr"/>
+      <c r="V477" s="2" t="inlineStr"/>
+      <c r="W477" s="2" t="inlineStr"/>
+      <c r="X477" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y477" s="2" t="inlineStr"/>
+      <c r="Z477" s="2" t="inlineStr"/>
+      <c r="AA477" s="2" t="inlineStr"/>
+      <c r="AB477" s="2" t="inlineStr"/>
+      <c r="AC477" s="2" t="inlineStr"/>
+      <c r="AD477" s="2" t="inlineStr"/>
+      <c r="AE477" s="2" t="inlineStr"/>
+      <c r="AF477" s="2" t="inlineStr"/>
+      <c r="AG477" s="2" t="inlineStr"/>
+      <c r="AH477" s="2" t="inlineStr"/>
+      <c r="AI477" s="2" t="inlineStr"/>
+      <c r="AJ477" s="2" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>572530ce05374a51</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>71318</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K478" s="2" t="inlineStr"/>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>0.689596</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr"/>
+      <c r="N478" s="2" t="inlineStr"/>
+      <c r="O478" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P478" s="2" t="inlineStr"/>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>-0.010103699699699709</t>
+        </is>
+      </c>
+      <c r="R478" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:29.177358Z</t>
+        </is>
+      </c>
+      <c r="S478" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T478" s="2" t="inlineStr"/>
+      <c r="U478" s="2" t="inlineStr"/>
+      <c r="V478" s="2" t="inlineStr"/>
+      <c r="W478" s="2" t="inlineStr"/>
+      <c r="X478" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y478" s="2" t="inlineStr"/>
+      <c r="Z478" s="2" t="inlineStr"/>
+      <c r="AA478" s="2" t="inlineStr"/>
+      <c r="AB478" s="2" t="inlineStr"/>
+      <c r="AC478" s="2" t="inlineStr"/>
+      <c r="AD478" s="2" t="inlineStr"/>
+      <c r="AE478" s="2" t="inlineStr"/>
+      <c r="AF478" s="2" t="inlineStr"/>
+      <c r="AG478" s="2" t="inlineStr"/>
+      <c r="AH478" s="2" t="inlineStr"/>
+      <c r="AI478" s="2" t="inlineStr"/>
+      <c r="AJ478" s="2" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>a59fe830e1da4035</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>68437</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K479" s="2" t="inlineStr"/>
+      <c r="L479" s="2" t="inlineStr">
+        <is>
+          <t>0.518066</t>
+        </is>
+      </c>
+      <c r="M479" s="2" t="inlineStr"/>
+      <c r="N479" s="2" t="inlineStr"/>
+      <c r="O479" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P479" s="2" t="inlineStr"/>
+      <c r="Q479" s="2" t="inlineStr">
+        <is>
+          <t>-0.10170586311787067</t>
+        </is>
+      </c>
+      <c r="R479" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:30.455227Z</t>
+        </is>
+      </c>
+      <c r="S479" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T479" s="2" t="inlineStr"/>
+      <c r="U479" s="2" t="inlineStr"/>
+      <c r="V479" s="2" t="inlineStr"/>
+      <c r="W479" s="2" t="inlineStr"/>
+      <c r="X479" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y479" s="2" t="inlineStr"/>
+      <c r="Z479" s="2" t="inlineStr"/>
+      <c r="AA479" s="2" t="inlineStr"/>
+      <c r="AB479" s="2" t="inlineStr"/>
+      <c r="AC479" s="2" t="inlineStr"/>
+      <c r="AD479" s="2" t="inlineStr"/>
+      <c r="AE479" s="2" t="inlineStr"/>
+      <c r="AF479" s="2" t="inlineStr"/>
+      <c r="AG479" s="2" t="inlineStr"/>
+      <c r="AH479" s="2" t="inlineStr"/>
+      <c r="AI479" s="2" t="inlineStr"/>
+      <c r="AJ479" s="2" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>5ac0bfbb17f04c5c</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>71319</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K480" s="2" t="inlineStr"/>
+      <c r="L480" s="2" t="inlineStr">
+        <is>
+          <t>0.505173</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="inlineStr"/>
+      <c r="N480" s="2" t="inlineStr"/>
+      <c r="O480" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P480" s="2" t="inlineStr"/>
+      <c r="Q480" s="2" t="inlineStr">
+        <is>
+          <t>-0.12445662962962956</t>
+        </is>
+      </c>
+      <c r="R480" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:31.204261Z</t>
+        </is>
+      </c>
+      <c r="S480" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T480" s="2" t="inlineStr"/>
+      <c r="U480" s="2" t="inlineStr"/>
+      <c r="V480" s="2" t="inlineStr"/>
+      <c r="W480" s="2" t="inlineStr"/>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="inlineStr"/>
+      <c r="Z480" s="2" t="inlineStr"/>
+      <c r="AA480" s="2" t="inlineStr"/>
+      <c r="AB480" s="2" t="inlineStr"/>
+      <c r="AC480" s="2" t="inlineStr"/>
+      <c r="AD480" s="2" t="inlineStr"/>
+      <c r="AE480" s="2" t="inlineStr"/>
+      <c r="AF480" s="2" t="inlineStr"/>
+      <c r="AG480" s="2" t="inlineStr"/>
+      <c r="AH480" s="2" t="inlineStr"/>
+      <c r="AI480" s="2" t="inlineStr"/>
+      <c r="AJ480" s="2" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>a4d7901fa13f49d9</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>68562</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J481" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K481" s="2" t="inlineStr"/>
+      <c r="L481" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M481" s="2" t="inlineStr"/>
+      <c r="N481" s="2" t="inlineStr"/>
+      <c r="O481" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P481" s="2" t="inlineStr"/>
+      <c r="Q481" s="2" t="inlineStr">
+        <is>
+          <t>-0.10257262962962954</t>
+        </is>
+      </c>
+      <c r="R481" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:31.835843Z</t>
+        </is>
+      </c>
+      <c r="S481" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T481" s="2" t="inlineStr"/>
+      <c r="U481" s="2" t="inlineStr"/>
+      <c r="V481" s="2" t="inlineStr"/>
+      <c r="W481" s="2" t="inlineStr"/>
+      <c r="X481" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y481" s="2" t="inlineStr"/>
+      <c r="Z481" s="2" t="inlineStr"/>
+      <c r="AA481" s="2" t="inlineStr"/>
+      <c r="AB481" s="2" t="inlineStr"/>
+      <c r="AC481" s="2" t="inlineStr"/>
+      <c r="AD481" s="2" t="inlineStr"/>
+      <c r="AE481" s="2" t="inlineStr"/>
+      <c r="AF481" s="2" t="inlineStr"/>
+      <c r="AG481" s="2" t="inlineStr"/>
+      <c r="AH481" s="2" t="inlineStr"/>
+      <c r="AI481" s="2" t="inlineStr"/>
+      <c r="AJ481" s="2" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>366eceae499646d5</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>68563</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J482" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K482" s="2" t="inlineStr"/>
+      <c r="L482" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="inlineStr"/>
+      <c r="N482" s="2" t="inlineStr"/>
+      <c r="O482" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P482" s="2" t="inlineStr"/>
+      <c r="Q482" s="2" t="inlineStr">
+        <is>
+          <t>-0.043758450643776814</t>
+        </is>
+      </c>
+      <c r="R482" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:32.634716Z</t>
+        </is>
+      </c>
+      <c r="S482" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T482" s="2" t="inlineStr"/>
+      <c r="U482" s="2" t="inlineStr"/>
+      <c r="V482" s="2" t="inlineStr"/>
+      <c r="W482" s="2" t="inlineStr"/>
+      <c r="X482" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y482" s="2" t="inlineStr"/>
+      <c r="Z482" s="2" t="inlineStr"/>
+      <c r="AA482" s="2" t="inlineStr"/>
+      <c r="AB482" s="2" t="inlineStr"/>
+      <c r="AC482" s="2" t="inlineStr"/>
+      <c r="AD482" s="2" t="inlineStr"/>
+      <c r="AE482" s="2" t="inlineStr"/>
+      <c r="AF482" s="2" t="inlineStr"/>
+      <c r="AG482" s="2" t="inlineStr"/>
+      <c r="AH482" s="2" t="inlineStr"/>
+      <c r="AI482" s="2" t="inlineStr"/>
+      <c r="AJ482" s="2" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>11436c95f74547b5</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>68565</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K483" s="2" t="inlineStr"/>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>0.589593</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="inlineStr"/>
+      <c r="N483" s="2" t="inlineStr"/>
+      <c r="O483" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P483" s="2" t="inlineStr"/>
+      <c r="Q483" s="2" t="inlineStr">
+        <is>
+          <t>-0.09091818210862612</t>
+        </is>
+      </c>
+      <c r="R483" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:34.585574Z</t>
+        </is>
+      </c>
+      <c r="S483" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T483" s="2" t="inlineStr"/>
+      <c r="U483" s="2" t="inlineStr"/>
+      <c r="V483" s="2" t="inlineStr"/>
+      <c r="W483" s="2" t="inlineStr"/>
+      <c r="X483" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y483" s="2" t="inlineStr"/>
+      <c r="Z483" s="2" t="inlineStr"/>
+      <c r="AA483" s="2" t="inlineStr"/>
+      <c r="AB483" s="2" t="inlineStr"/>
+      <c r="AC483" s="2" t="inlineStr"/>
+      <c r="AD483" s="2" t="inlineStr"/>
+      <c r="AE483" s="2" t="inlineStr"/>
+      <c r="AF483" s="2" t="inlineStr"/>
+      <c r="AG483" s="2" t="inlineStr"/>
+      <c r="AH483" s="2" t="inlineStr"/>
+      <c r="AI483" s="2" t="inlineStr"/>
+      <c r="AJ483" s="2" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>923e630afac64263</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>68567</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K484" s="2" t="inlineStr"/>
+      <c r="L484" s="2" t="inlineStr">
+        <is>
+          <t>0.516525</t>
+        </is>
+      </c>
+      <c r="M484" s="2" t="inlineStr"/>
+      <c r="N484" s="2" t="inlineStr"/>
+      <c r="O484" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P484" s="2" t="inlineStr"/>
+      <c r="Q484" s="2" t="inlineStr">
+        <is>
+          <t>-0.0542904506437768</t>
+        </is>
+      </c>
+      <c r="R484" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:35.266965Z</t>
+        </is>
+      </c>
+      <c r="S484" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T484" s="2" t="inlineStr"/>
+      <c r="U484" s="2" t="inlineStr"/>
+      <c r="V484" s="2" t="inlineStr"/>
+      <c r="W484" s="2" t="inlineStr"/>
+      <c r="X484" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y484" s="2" t="inlineStr"/>
+      <c r="Z484" s="2" t="inlineStr"/>
+      <c r="AA484" s="2" t="inlineStr"/>
+      <c r="AB484" s="2" t="inlineStr"/>
+      <c r="AC484" s="2" t="inlineStr"/>
+      <c r="AD484" s="2" t="inlineStr"/>
+      <c r="AE484" s="2" t="inlineStr"/>
+      <c r="AF484" s="2" t="inlineStr"/>
+      <c r="AG484" s="2" t="inlineStr"/>
+      <c r="AH484" s="2" t="inlineStr"/>
+      <c r="AI484" s="2" t="inlineStr"/>
+      <c r="AJ484" s="2" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>e84f2dc03ed84a00</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J485" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K485" s="2" t="inlineStr"/>
+      <c r="L485" s="2" t="inlineStr">
+        <is>
+          <t>0.500399</t>
+        </is>
+      </c>
+      <c r="M485" s="2" t="inlineStr"/>
+      <c r="N485" s="2" t="inlineStr"/>
+      <c r="O485" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P485" s="2" t="inlineStr"/>
+      <c r="Q485" s="2" t="inlineStr">
+        <is>
+          <t>-0.009404921568627378</t>
+        </is>
+      </c>
+      <c r="R485" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:35.801312Z</t>
+        </is>
+      </c>
+      <c r="S485" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T485" s="2" t="inlineStr"/>
+      <c r="U485" s="2" t="inlineStr"/>
+      <c r="V485" s="2" t="inlineStr"/>
+      <c r="W485" s="2" t="inlineStr"/>
+      <c r="X485" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y485" s="2" t="inlineStr"/>
+      <c r="Z485" s="2" t="inlineStr"/>
+      <c r="AA485" s="2" t="inlineStr"/>
+      <c r="AB485" s="2" t="inlineStr"/>
+      <c r="AC485" s="2" t="inlineStr"/>
+      <c r="AD485" s="2" t="inlineStr"/>
+      <c r="AE485" s="2" t="inlineStr"/>
+      <c r="AF485" s="2" t="inlineStr"/>
+      <c r="AG485" s="2" t="inlineStr"/>
+      <c r="AH485" s="2" t="inlineStr"/>
+      <c r="AI485" s="2" t="inlineStr"/>
+      <c r="AJ485" s="2" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>a5cc72a254af45d4</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>70533</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K486" s="2" t="inlineStr"/>
+      <c r="L486" s="2" t="inlineStr">
+        <is>
+          <t>0.509301</t>
+        </is>
+      </c>
+      <c r="M486" s="2" t="inlineStr"/>
+      <c r="N486" s="2" t="inlineStr"/>
+      <c r="O486" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P486" s="2" t="inlineStr"/>
+      <c r="Q486" s="2" t="inlineStr">
+        <is>
+          <t>-0.11047086311787069</t>
+        </is>
+      </c>
+      <c r="R486" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:37.172008Z</t>
+        </is>
+      </c>
+      <c r="S486" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T486" s="2" t="inlineStr"/>
+      <c r="U486" s="2" t="inlineStr"/>
+      <c r="V486" s="2" t="inlineStr"/>
+      <c r="W486" s="2" t="inlineStr"/>
+      <c r="X486" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y486" s="2" t="inlineStr"/>
+      <c r="Z486" s="2" t="inlineStr"/>
+      <c r="AA486" s="2" t="inlineStr"/>
+      <c r="AB486" s="2" t="inlineStr"/>
+      <c r="AC486" s="2" t="inlineStr"/>
+      <c r="AD486" s="2" t="inlineStr"/>
+      <c r="AE486" s="2" t="inlineStr"/>
+      <c r="AF486" s="2" t="inlineStr"/>
+      <c r="AG486" s="2" t="inlineStr"/>
+      <c r="AH486" s="2" t="inlineStr"/>
+      <c r="AI486" s="2" t="inlineStr"/>
+      <c r="AJ486" s="2" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>eccb22f536cf4db0</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J487" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K487" s="2" t="inlineStr"/>
+      <c r="L487" s="2" t="inlineStr">
+        <is>
+          <t>0.576417</t>
+        </is>
+      </c>
+      <c r="M487" s="2" t="inlineStr"/>
+      <c r="N487" s="2" t="inlineStr"/>
+      <c r="O487" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P487" s="2" t="inlineStr"/>
+      <c r="Q487" s="2" t="inlineStr">
+        <is>
+          <t>-0.05321262962962958</t>
+        </is>
+      </c>
+      <c r="R487" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:38.676055Z</t>
+        </is>
+      </c>
+      <c r="S487" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T487" s="2" t="inlineStr"/>
+      <c r="U487" s="2" t="inlineStr"/>
+      <c r="V487" s="2" t="inlineStr"/>
+      <c r="W487" s="2" t="inlineStr"/>
+      <c r="X487" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y487" s="2" t="inlineStr"/>
+      <c r="Z487" s="2" t="inlineStr"/>
+      <c r="AA487" s="2" t="inlineStr"/>
+      <c r="AB487" s="2" t="inlineStr"/>
+      <c r="AC487" s="2" t="inlineStr"/>
+      <c r="AD487" s="2" t="inlineStr"/>
+      <c r="AE487" s="2" t="inlineStr"/>
+      <c r="AF487" s="2" t="inlineStr"/>
+      <c r="AG487" s="2" t="inlineStr"/>
+      <c r="AH487" s="2" t="inlineStr"/>
+      <c r="AI487" s="2" t="inlineStr"/>
+      <c r="AJ487" s="2" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>8d653d1edc974196</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K488" s="2" t="inlineStr"/>
+      <c r="L488" s="2" t="inlineStr">
+        <is>
+          <t>0.598949</t>
+        </is>
+      </c>
+      <c r="M488" s="2" t="inlineStr"/>
+      <c r="N488" s="2" t="inlineStr"/>
+      <c r="O488" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P488" s="2" t="inlineStr"/>
+      <c r="Q488" s="2" t="inlineStr">
+        <is>
+          <t>-0.020822863117870738</t>
+        </is>
+      </c>
+      <c r="R488" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:40.911181Z</t>
+        </is>
+      </c>
+      <c r="S488" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T488" s="2" t="inlineStr"/>
+      <c r="U488" s="2" t="inlineStr"/>
+      <c r="V488" s="2" t="inlineStr"/>
+      <c r="W488" s="2" t="inlineStr"/>
+      <c r="X488" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y488" s="2" t="inlineStr"/>
+      <c r="Z488" s="2" t="inlineStr"/>
+      <c r="AA488" s="2" t="inlineStr"/>
+      <c r="AB488" s="2" t="inlineStr"/>
+      <c r="AC488" s="2" t="inlineStr"/>
+      <c r="AD488" s="2" t="inlineStr"/>
+      <c r="AE488" s="2" t="inlineStr"/>
+      <c r="AF488" s="2" t="inlineStr"/>
+      <c r="AG488" s="2" t="inlineStr"/>
+      <c r="AH488" s="2" t="inlineStr"/>
+      <c r="AI488" s="2" t="inlineStr"/>
+      <c r="AJ488" s="2" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>a5e146ecd7424c59</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K489" s="2" t="inlineStr"/>
+      <c r="L489" s="2" t="inlineStr">
+        <is>
+          <t>0.698419</t>
+        </is>
+      </c>
+      <c r="M489" s="2" t="inlineStr"/>
+      <c r="N489" s="2" t="inlineStr"/>
+      <c r="O489" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P489" s="2" t="inlineStr"/>
+      <c r="Q489" s="2" t="inlineStr">
+        <is>
+          <t>0.1886150784313726</t>
+        </is>
+      </c>
+      <c r="R489" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:41.500495Z</t>
+        </is>
+      </c>
+      <c r="S489" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T489" s="2" t="inlineStr"/>
+      <c r="U489" s="2" t="inlineStr"/>
+      <c r="V489" s="2" t="inlineStr"/>
+      <c r="W489" s="2" t="inlineStr"/>
+      <c r="X489" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y489" s="2" t="inlineStr"/>
+      <c r="Z489" s="2" t="inlineStr"/>
+      <c r="AA489" s="2" t="inlineStr"/>
+      <c r="AB489" s="2" t="inlineStr"/>
+      <c r="AC489" s="2" t="inlineStr"/>
+      <c r="AD489" s="2" t="inlineStr"/>
+      <c r="AE489" s="2" t="inlineStr"/>
+      <c r="AF489" s="2" t="inlineStr"/>
+      <c r="AG489" s="2" t="inlineStr"/>
+      <c r="AH489" s="2" t="inlineStr"/>
+      <c r="AI489" s="2" t="inlineStr"/>
+      <c r="AJ489" s="2" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>307f7eaf28b2452f</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K490" s="2" t="inlineStr"/>
+      <c r="L490" s="2" t="inlineStr">
+        <is>
+          <t>0.556222</t>
+        </is>
+      </c>
+      <c r="M490" s="2" t="inlineStr"/>
+      <c r="N490" s="2" t="inlineStr"/>
+      <c r="O490" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P490" s="2" t="inlineStr"/>
+      <c r="Q490" s="2" t="inlineStr">
+        <is>
+          <t>0.02570556807511737</t>
+        </is>
+      </c>
+      <c r="R490" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:42.051951Z</t>
+        </is>
+      </c>
+      <c r="S490" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T490" s="2" t="inlineStr"/>
+      <c r="U490" s="2" t="inlineStr"/>
+      <c r="V490" s="2" t="inlineStr"/>
+      <c r="W490" s="2" t="inlineStr"/>
+      <c r="X490" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y490" s="2" t="inlineStr"/>
+      <c r="Z490" s="2" t="inlineStr"/>
+      <c r="AA490" s="2" t="inlineStr"/>
+      <c r="AB490" s="2" t="inlineStr"/>
+      <c r="AC490" s="2" t="inlineStr"/>
+      <c r="AD490" s="2" t="inlineStr"/>
+      <c r="AE490" s="2" t="inlineStr"/>
+      <c r="AF490" s="2" t="inlineStr"/>
+      <c r="AG490" s="2" t="inlineStr"/>
+      <c r="AH490" s="2" t="inlineStr"/>
+      <c r="AI490" s="2" t="inlineStr"/>
+      <c r="AJ490" s="2" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>bc1fb564ced74c32</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K491" s="2" t="inlineStr"/>
+      <c r="L491" s="2" t="inlineStr">
+        <is>
+          <t>0.6138</t>
+        </is>
+      </c>
+      <c r="M491" s="2" t="inlineStr"/>
+      <c r="N491" s="2" t="inlineStr"/>
+      <c r="O491" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P491" s="2" t="inlineStr"/>
+      <c r="Q491" s="2" t="inlineStr">
+        <is>
+          <t>0.023636065573770515</t>
+        </is>
+      </c>
+      <c r="R491" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:42.609865Z</t>
+        </is>
+      </c>
+      <c r="S491" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T491" s="2" t="inlineStr"/>
+      <c r="U491" s="2" t="inlineStr"/>
+      <c r="V491" s="2" t="inlineStr"/>
+      <c r="W491" s="2" t="inlineStr"/>
+      <c r="X491" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y491" s="2" t="inlineStr"/>
+      <c r="Z491" s="2" t="inlineStr"/>
+      <c r="AA491" s="2" t="inlineStr"/>
+      <c r="AB491" s="2" t="inlineStr"/>
+      <c r="AC491" s="2" t="inlineStr"/>
+      <c r="AD491" s="2" t="inlineStr"/>
+      <c r="AE491" s="2" t="inlineStr"/>
+      <c r="AF491" s="2" t="inlineStr"/>
+      <c r="AG491" s="2" t="inlineStr"/>
+      <c r="AH491" s="2" t="inlineStr"/>
+      <c r="AI491" s="2" t="inlineStr"/>
+      <c r="AJ491" s="2" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>37c4cea6f2b244b0</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K492" s="2" t="inlineStr"/>
+      <c r="L492" s="2" t="inlineStr">
+        <is>
+          <t>0.67501</t>
+        </is>
+      </c>
+      <c r="M492" s="2" t="inlineStr"/>
+      <c r="N492" s="2" t="inlineStr"/>
+      <c r="O492" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P492" s="2" t="inlineStr"/>
+      <c r="Q492" s="2" t="inlineStr">
+        <is>
+          <t>0.0848460655737705</t>
+        </is>
+      </c>
+      <c r="R492" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:43.095313Z</t>
+        </is>
+      </c>
+      <c r="S492" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T492" s="2" t="inlineStr"/>
+      <c r="U492" s="2" t="inlineStr"/>
+      <c r="V492" s="2" t="inlineStr"/>
+      <c r="W492" s="2" t="inlineStr"/>
+      <c r="X492" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y492" s="2" t="inlineStr"/>
+      <c r="Z492" s="2" t="inlineStr"/>
+      <c r="AA492" s="2" t="inlineStr"/>
+      <c r="AB492" s="2" t="inlineStr"/>
+      <c r="AC492" s="2" t="inlineStr"/>
+      <c r="AD492" s="2" t="inlineStr"/>
+      <c r="AE492" s="2" t="inlineStr"/>
+      <c r="AF492" s="2" t="inlineStr"/>
+      <c r="AG492" s="2" t="inlineStr"/>
+      <c r="AH492" s="2" t="inlineStr"/>
+      <c r="AI492" s="2" t="inlineStr"/>
+      <c r="AJ492" s="2" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>52fe8cd9beb4469c</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>69510</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J493" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K493" s="2" t="inlineStr"/>
+      <c r="L493" s="2" t="inlineStr">
+        <is>
+          <t>0.512967</t>
+        </is>
+      </c>
+      <c r="M493" s="2" t="inlineStr"/>
+      <c r="N493" s="2" t="inlineStr"/>
+      <c r="O493" s="2" t="inlineStr">
+        <is>
+          <t>0.30959752321981426</t>
+        </is>
+      </c>
+      <c r="P493" s="2" t="inlineStr"/>
+      <c r="Q493" s="2" t="inlineStr">
+        <is>
+          <t>0.2033694767801857</t>
+        </is>
+      </c>
+      <c r="R493" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.237997Z</t>
+        </is>
+      </c>
+      <c r="S493" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T493" s="2" t="inlineStr"/>
+      <c r="U493" s="2" t="inlineStr"/>
+      <c r="V493" s="2" t="inlineStr"/>
+      <c r="W493" s="2" t="inlineStr"/>
+      <c r="X493" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y493" s="2" t="inlineStr"/>
+      <c r="Z493" s="2" t="inlineStr"/>
+      <c r="AA493" s="2" t="inlineStr"/>
+      <c r="AB493" s="2" t="inlineStr"/>
+      <c r="AC493" s="2" t="inlineStr"/>
+      <c r="AD493" s="2" t="inlineStr"/>
+      <c r="AE493" s="2" t="inlineStr"/>
+      <c r="AF493" s="2" t="inlineStr"/>
+      <c r="AG493" s="2" t="inlineStr"/>
+      <c r="AH493" s="2" t="inlineStr"/>
+      <c r="AI493" s="2" t="inlineStr"/>
+      <c r="AJ493" s="2" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>0ba0713bdec249f6</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>69537</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J494" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K494" s="2" t="inlineStr"/>
+      <c r="L494" s="2" t="inlineStr">
+        <is>
+          <t>0.536892</t>
+        </is>
+      </c>
+      <c r="M494" s="2" t="inlineStr"/>
+      <c r="N494" s="2" t="inlineStr"/>
+      <c r="O494" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P494" s="2" t="inlineStr"/>
+      <c r="Q494" s="2" t="inlineStr">
+        <is>
+          <t>0.10770745064377685</t>
+        </is>
+      </c>
+      <c r="R494" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.758046Z</t>
+        </is>
+      </c>
+      <c r="S494" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T494" s="2" t="inlineStr"/>
+      <c r="U494" s="2" t="inlineStr"/>
+      <c r="V494" s="2" t="inlineStr"/>
+      <c r="W494" s="2" t="inlineStr"/>
+      <c r="X494" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y494" s="2" t="inlineStr"/>
+      <c r="Z494" s="2" t="inlineStr"/>
+      <c r="AA494" s="2" t="inlineStr"/>
+      <c r="AB494" s="2" t="inlineStr"/>
+      <c r="AC494" s="2" t="inlineStr"/>
+      <c r="AD494" s="2" t="inlineStr"/>
+      <c r="AE494" s="2" t="inlineStr"/>
+      <c r="AF494" s="2" t="inlineStr"/>
+      <c r="AG494" s="2" t="inlineStr"/>
+      <c r="AH494" s="2" t="inlineStr"/>
+      <c r="AI494" s="2" t="inlineStr"/>
+      <c r="AJ494" s="2" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>3332773f65aa49aa</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>71199</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J495" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K495" s="2" t="inlineStr"/>
+      <c r="L495" s="2" t="inlineStr">
+        <is>
+          <t>0.505972</t>
+        </is>
+      </c>
+      <c r="M495" s="2" t="inlineStr"/>
+      <c r="N495" s="2" t="inlineStr"/>
+      <c r="O495" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P495" s="2" t="inlineStr"/>
+      <c r="Q495" s="2" t="inlineStr">
+        <is>
+          <t>0.06544336563876652</t>
+        </is>
+      </c>
+      <c r="R495" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:48.910262Z</t>
+        </is>
+      </c>
+      <c r="S495" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T495" s="2" t="inlineStr"/>
+      <c r="U495" s="2" t="inlineStr"/>
+      <c r="V495" s="2" t="inlineStr"/>
+      <c r="W495" s="2" t="inlineStr"/>
+      <c r="X495" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y495" s="2" t="inlineStr"/>
+      <c r="Z495" s="2" t="inlineStr"/>
+      <c r="AA495" s="2" t="inlineStr"/>
+      <c r="AB495" s="2" t="inlineStr"/>
+      <c r="AC495" s="2" t="inlineStr"/>
+      <c r="AD495" s="2" t="inlineStr"/>
+      <c r="AE495" s="2" t="inlineStr"/>
+      <c r="AF495" s="2" t="inlineStr"/>
+      <c r="AG495" s="2" t="inlineStr"/>
+      <c r="AH495" s="2" t="inlineStr"/>
+      <c r="AI495" s="2" t="inlineStr"/>
+      <c r="AJ495" s="2" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>9643fa39a32d4f5b</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K496" s="2" t="inlineStr"/>
+      <c r="L496" s="2" t="inlineStr">
+        <is>
+          <t>0.527057</t>
+        </is>
+      </c>
+      <c r="M496" s="2" t="inlineStr"/>
+      <c r="N496" s="2" t="inlineStr"/>
+      <c r="O496" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P496" s="2" t="inlineStr"/>
+      <c r="Q496" s="2" t="inlineStr">
+        <is>
+          <t>-0.03241436563876654</t>
+        </is>
+      </c>
+      <c r="R496" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:50.632049Z</t>
+        </is>
+      </c>
+      <c r="S496" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T496" s="2" t="inlineStr"/>
+      <c r="U496" s="2" t="inlineStr"/>
+      <c r="V496" s="2" t="inlineStr"/>
+      <c r="W496" s="2" t="inlineStr"/>
+      <c r="X496" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y496" s="2" t="inlineStr"/>
+      <c r="Z496" s="2" t="inlineStr"/>
+      <c r="AA496" s="2" t="inlineStr"/>
+      <c r="AB496" s="2" t="inlineStr"/>
+      <c r="AC496" s="2" t="inlineStr"/>
+      <c r="AD496" s="2" t="inlineStr"/>
+      <c r="AE496" s="2" t="inlineStr"/>
+      <c r="AF496" s="2" t="inlineStr"/>
+      <c r="AG496" s="2" t="inlineStr"/>
+      <c r="AH496" s="2" t="inlineStr"/>
+      <c r="AI496" s="2" t="inlineStr"/>
+      <c r="AJ496" s="2" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>979c0e6d7d664c76</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J497" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K497" s="2" t="inlineStr"/>
+      <c r="L497" s="2" t="inlineStr">
+        <is>
+          <t>0.537618</t>
+        </is>
+      </c>
+      <c r="M497" s="2" t="inlineStr"/>
+      <c r="N497" s="2" t="inlineStr"/>
+      <c r="O497" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P497" s="2" t="inlineStr"/>
+      <c r="Q497" s="2" t="inlineStr">
+        <is>
+          <t>-0.03319745064377677</t>
+        </is>
+      </c>
+      <c r="R497" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.334320Z</t>
+        </is>
+      </c>
+      <c r="S497" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T497" s="2" t="inlineStr"/>
+      <c r="U497" s="2" t="inlineStr"/>
+      <c r="V497" s="2" t="inlineStr"/>
+      <c r="W497" s="2" t="inlineStr"/>
+      <c r="X497" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y497" s="2" t="inlineStr"/>
+      <c r="Z497" s="2" t="inlineStr"/>
+      <c r="AA497" s="2" t="inlineStr"/>
+      <c r="AB497" s="2" t="inlineStr"/>
+      <c r="AC497" s="2" t="inlineStr"/>
+      <c r="AD497" s="2" t="inlineStr"/>
+      <c r="AE497" s="2" t="inlineStr"/>
+      <c r="AF497" s="2" t="inlineStr"/>
+      <c r="AG497" s="2" t="inlineStr"/>
+      <c r="AH497" s="2" t="inlineStr"/>
+      <c r="AI497" s="2" t="inlineStr"/>
+      <c r="AJ497" s="2" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>4ab4340e733542c5</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>69617</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J498" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K498" s="2" t="inlineStr"/>
+      <c r="L498" s="2" t="inlineStr">
+        <is>
+          <t>0.626886</t>
+        </is>
+      </c>
+      <c r="M498" s="2" t="inlineStr"/>
+      <c r="N498" s="2" t="inlineStr"/>
+      <c r="O498" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P498" s="2" t="inlineStr"/>
+      <c r="Q498" s="2" t="inlineStr">
+        <is>
+          <t>0.017511000000000054</t>
+        </is>
+      </c>
+      <c r="R498" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.829078Z</t>
+        </is>
+      </c>
+      <c r="S498" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T498" s="2" t="inlineStr"/>
+      <c r="U498" s="2" t="inlineStr"/>
+      <c r="V498" s="2" t="inlineStr"/>
+      <c r="W498" s="2" t="inlineStr"/>
+      <c r="X498" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y498" s="2" t="inlineStr"/>
+      <c r="Z498" s="2" t="inlineStr"/>
+      <c r="AA498" s="2" t="inlineStr"/>
+      <c r="AB498" s="2" t="inlineStr"/>
+      <c r="AC498" s="2" t="inlineStr"/>
+      <c r="AD498" s="2" t="inlineStr"/>
+      <c r="AE498" s="2" t="inlineStr"/>
+      <c r="AF498" s="2" t="inlineStr"/>
+      <c r="AG498" s="2" t="inlineStr"/>
+      <c r="AH498" s="2" t="inlineStr"/>
+      <c r="AI498" s="2" t="inlineStr"/>
+      <c r="AJ498" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ438"/>
+  <autoFilter ref="A1:AJ498"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/research/model_ledgers/cs2-tiered-elo.xlsx
+++ b/data/research/model_ledgers/cs2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$570</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ498"/>
+  <dimension ref="A1:AJ570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -45676,14 +45676,34 @@
       <c r="W439" s="2" t="inlineStr"/>
       <c r="X439" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y439" s="2" t="inlineStr"/>
-      <c r="Z439" s="2" t="inlineStr"/>
-      <c r="AA439" s="2" t="inlineStr"/>
-      <c r="AB439" s="2" t="inlineStr"/>
-      <c r="AC439" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y439" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z439" s="2" t="inlineStr">
+        <is>
+          <t>0.550000</t>
+        </is>
+      </c>
+      <c r="AA439" s="2" t="inlineStr">
+        <is>
+          <t>0.000450</t>
+        </is>
+      </c>
+      <c r="AB439" s="2" t="inlineStr">
+        <is>
+          <t>0.8197</t>
+        </is>
+      </c>
+      <c r="AC439" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:38.920286Z</t>
+        </is>
+      </c>
       <c r="AD439" s="2" t="inlineStr"/>
       <c r="AE439" s="2" t="inlineStr"/>
       <c r="AF439" s="2" t="inlineStr"/>
@@ -45778,14 +45798,34 @@
       <c r="W440" s="2" t="inlineStr"/>
       <c r="X440" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y440" s="2" t="inlineStr"/>
-      <c r="Z440" s="2" t="inlineStr"/>
-      <c r="AA440" s="2" t="inlineStr"/>
-      <c r="AB440" s="2" t="inlineStr"/>
-      <c r="AC440" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y440" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z440" s="2" t="inlineStr">
+        <is>
+          <t>0.690000</t>
+        </is>
+      </c>
+      <c r="AA440" s="2" t="inlineStr">
+        <is>
+          <t>-0.000402</t>
+        </is>
+      </c>
+      <c r="AB440" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC440" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:40.523377Z</t>
+        </is>
+      </c>
       <c r="AD440" s="2" t="inlineStr"/>
       <c r="AE440" s="2" t="inlineStr"/>
       <c r="AF440" s="2" t="inlineStr"/>
@@ -48940,14 +48980,34 @@
       <c r="W471" s="2" t="inlineStr"/>
       <c r="X471" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y471" s="2" t="inlineStr"/>
-      <c r="Z471" s="2" t="inlineStr"/>
-      <c r="AA471" s="2" t="inlineStr"/>
-      <c r="AB471" s="2" t="inlineStr"/>
-      <c r="AC471" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y471" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z471" s="2" t="inlineStr">
+        <is>
+          <t>0.560000</t>
+        </is>
+      </c>
+      <c r="AA471" s="2" t="inlineStr">
+        <is>
+          <t>0.000529</t>
+        </is>
+      </c>
+      <c r="AB471" s="2" t="inlineStr">
+        <is>
+          <t>0.7874</t>
+        </is>
+      </c>
+      <c r="AC471" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:06.773956Z</t>
+        </is>
+      </c>
       <c r="AD471" s="2" t="inlineStr"/>
       <c r="AE471" s="2" t="inlineStr"/>
       <c r="AF471" s="2" t="inlineStr"/>
@@ -49042,14 +49102,34 @@
       <c r="W472" s="2" t="inlineStr"/>
       <c r="X472" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y472" s="2" t="inlineStr"/>
-      <c r="Z472" s="2" t="inlineStr"/>
-      <c r="AA472" s="2" t="inlineStr"/>
-      <c r="AB472" s="2" t="inlineStr"/>
-      <c r="AC472" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z472" s="2" t="inlineStr">
+        <is>
+          <t>0.490000</t>
+        </is>
+      </c>
+      <c r="AA472" s="2" t="inlineStr">
+        <is>
+          <t>-0.000196</t>
+        </is>
+      </c>
+      <c r="AB472" s="2" t="inlineStr">
+        <is>
+          <t>1.0400</t>
+        </is>
+      </c>
+      <c r="AC472" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:08.432944Z</t>
+        </is>
+      </c>
       <c r="AD472" s="2" t="inlineStr"/>
       <c r="AE472" s="2" t="inlineStr"/>
       <c r="AF472" s="2" t="inlineStr"/>
@@ -49144,14 +49224,34 @@
       <c r="W473" s="2" t="inlineStr"/>
       <c r="X473" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y473" s="2" t="inlineStr"/>
-      <c r="Z473" s="2" t="inlineStr"/>
-      <c r="AA473" s="2" t="inlineStr"/>
-      <c r="AB473" s="2" t="inlineStr"/>
-      <c r="AC473" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y473" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z473" s="2" t="inlineStr">
+        <is>
+          <t>0.530000</t>
+        </is>
+      </c>
+      <c r="AA473" s="2" t="inlineStr">
+        <is>
+          <t>-0.000516</t>
+        </is>
+      </c>
+      <c r="AB473" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC473" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:10.004840Z</t>
+        </is>
+      </c>
       <c r="AD473" s="2" t="inlineStr"/>
       <c r="AE473" s="2" t="inlineStr"/>
       <c r="AF473" s="2" t="inlineStr"/>
@@ -49246,14 +49346,34 @@
       <c r="W474" s="2" t="inlineStr"/>
       <c r="X474" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y474" s="2" t="inlineStr"/>
-      <c r="Z474" s="2" t="inlineStr"/>
-      <c r="AA474" s="2" t="inlineStr"/>
-      <c r="AB474" s="2" t="inlineStr"/>
-      <c r="AC474" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y474" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z474" s="2" t="inlineStr">
+        <is>
+          <t>0.580000</t>
+        </is>
+      </c>
+      <c r="AA474" s="2" t="inlineStr">
+        <is>
+          <t>0.000168</t>
+        </is>
+      </c>
+      <c r="AB474" s="2" t="inlineStr">
+        <is>
+          <t>-2.0000</t>
+        </is>
+      </c>
+      <c r="AC474" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:11.644443Z</t>
+        </is>
+      </c>
       <c r="AD474" s="2" t="inlineStr"/>
       <c r="AE474" s="2" t="inlineStr"/>
       <c r="AF474" s="2" t="inlineStr"/>
@@ -51710,8 +51830,7352 @@
       <c r="AI498" s="2" t="inlineStr"/>
       <c r="AJ498" s="2" t="inlineStr"/>
     </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>a72ef8820e4243b9</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>71280</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J499" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K499" s="2" t="inlineStr"/>
+      <c r="L499" s="2" t="inlineStr">
+        <is>
+          <t>0.640787</t>
+        </is>
+      </c>
+      <c r="M499" s="2" t="inlineStr"/>
+      <c r="N499" s="2" t="inlineStr"/>
+      <c r="O499" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P499" s="2" t="inlineStr"/>
+      <c r="Q499" s="2" t="inlineStr">
+        <is>
+          <t>-0.029179996699669974</t>
+        </is>
+      </c>
+      <c r="R499" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:37.143655Z</t>
+        </is>
+      </c>
+      <c r="S499" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="T499" s="2" t="inlineStr"/>
+      <c r="U499" s="2" t="inlineStr"/>
+      <c r="V499" s="2" t="inlineStr"/>
+      <c r="W499" s="2" t="inlineStr"/>
+      <c r="X499" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y499" s="2" t="inlineStr"/>
+      <c r="Z499" s="2" t="inlineStr"/>
+      <c r="AA499" s="2" t="inlineStr"/>
+      <c r="AB499" s="2" t="inlineStr"/>
+      <c r="AC499" s="2" t="inlineStr"/>
+      <c r="AD499" s="2" t="inlineStr"/>
+      <c r="AE499" s="2" t="inlineStr"/>
+      <c r="AF499" s="2" t="inlineStr"/>
+      <c r="AG499" s="2" t="inlineStr"/>
+      <c r="AH499" s="2" t="inlineStr"/>
+      <c r="AI499" s="2" t="inlineStr"/>
+      <c r="AJ499" s="2" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>15686bdb5d0544e5</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>71213</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J500" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K500" s="2" t="inlineStr"/>
+      <c r="L500" s="2" t="inlineStr">
+        <is>
+          <t>0.719395</t>
+        </is>
+      </c>
+      <c r="M500" s="2" t="inlineStr"/>
+      <c r="N500" s="2" t="inlineStr"/>
+      <c r="O500" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P500" s="2" t="inlineStr"/>
+      <c r="Q500" s="2" t="inlineStr">
+        <is>
+          <t>0.2095910784313726</t>
+        </is>
+      </c>
+      <c r="R500" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:38.137077Z</t>
+        </is>
+      </c>
+      <c r="S500" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="T500" s="2" t="inlineStr"/>
+      <c r="U500" s="2" t="inlineStr"/>
+      <c r="V500" s="2" t="inlineStr"/>
+      <c r="W500" s="2" t="inlineStr"/>
+      <c r="X500" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y500" s="2" t="inlineStr"/>
+      <c r="Z500" s="2" t="inlineStr"/>
+      <c r="AA500" s="2" t="inlineStr"/>
+      <c r="AB500" s="2" t="inlineStr"/>
+      <c r="AC500" s="2" t="inlineStr"/>
+      <c r="AD500" s="2" t="inlineStr"/>
+      <c r="AE500" s="2" t="inlineStr"/>
+      <c r="AF500" s="2" t="inlineStr"/>
+      <c r="AG500" s="2" t="inlineStr"/>
+      <c r="AH500" s="2" t="inlineStr"/>
+      <c r="AI500" s="2" t="inlineStr"/>
+      <c r="AJ500" s="2" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>d6f41cac595c4310</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>68435</t>
+        </is>
+      </c>
+      <c r="I501" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J501" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K501" s="2" t="inlineStr"/>
+      <c r="L501" s="2" t="inlineStr">
+        <is>
+          <t>0.526874</t>
+        </is>
+      </c>
+      <c r="M501" s="2" t="inlineStr"/>
+      <c r="N501" s="2" t="inlineStr"/>
+      <c r="O501" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P501" s="2" t="inlineStr"/>
+      <c r="Q501" s="2" t="inlineStr">
+        <is>
+          <t>0.14664586311787065</t>
+        </is>
+      </c>
+      <c r="R501" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:39.296037Z</t>
+        </is>
+      </c>
+      <c r="S501" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="T501" s="2" t="inlineStr"/>
+      <c r="U501" s="2" t="inlineStr"/>
+      <c r="V501" s="2" t="inlineStr"/>
+      <c r="W501" s="2" t="inlineStr"/>
+      <c r="X501" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y501" s="2" t="inlineStr"/>
+      <c r="Z501" s="2" t="inlineStr"/>
+      <c r="AA501" s="2" t="inlineStr"/>
+      <c r="AB501" s="2" t="inlineStr"/>
+      <c r="AC501" s="2" t="inlineStr"/>
+      <c r="AD501" s="2" t="inlineStr"/>
+      <c r="AE501" s="2" t="inlineStr"/>
+      <c r="AF501" s="2" t="inlineStr"/>
+      <c r="AG501" s="2" t="inlineStr"/>
+      <c r="AH501" s="2" t="inlineStr"/>
+      <c r="AI501" s="2" t="inlineStr"/>
+      <c r="AJ501" s="2" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>e6d214bac2df4781</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>68437</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K502" s="2" t="inlineStr"/>
+      <c r="L502" s="2" t="inlineStr">
+        <is>
+          <t>0.5179</t>
+        </is>
+      </c>
+      <c r="M502" s="2" t="inlineStr"/>
+      <c r="N502" s="2" t="inlineStr"/>
+      <c r="O502" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P502" s="2" t="inlineStr"/>
+      <c r="Q502" s="2" t="inlineStr">
+        <is>
+          <t>-0.10187186311787066</t>
+        </is>
+      </c>
+      <c r="R502" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:41.460173Z</t>
+        </is>
+      </c>
+      <c r="S502" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T502" s="2" t="inlineStr"/>
+      <c r="U502" s="2" t="inlineStr"/>
+      <c r="V502" s="2" t="inlineStr"/>
+      <c r="W502" s="2" t="inlineStr"/>
+      <c r="X502" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y502" s="2" t="inlineStr"/>
+      <c r="Z502" s="2" t="inlineStr"/>
+      <c r="AA502" s="2" t="inlineStr"/>
+      <c r="AB502" s="2" t="inlineStr"/>
+      <c r="AC502" s="2" t="inlineStr"/>
+      <c r="AD502" s="2" t="inlineStr"/>
+      <c r="AE502" s="2" t="inlineStr"/>
+      <c r="AF502" s="2" t="inlineStr"/>
+      <c r="AG502" s="2" t="inlineStr"/>
+      <c r="AH502" s="2" t="inlineStr"/>
+      <c r="AI502" s="2" t="inlineStr"/>
+      <c r="AJ502" s="2" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>bfe1aaa0f4eb43d4</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>71319</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K503" s="2" t="inlineStr"/>
+      <c r="L503" s="2" t="inlineStr">
+        <is>
+          <t>0.509432</t>
+        </is>
+      </c>
+      <c r="M503" s="2" t="inlineStr"/>
+      <c r="N503" s="2" t="inlineStr"/>
+      <c r="O503" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P503" s="2" t="inlineStr"/>
+      <c r="Q503" s="2" t="inlineStr">
+        <is>
+          <t>0.1292038631178707</t>
+        </is>
+      </c>
+      <c r="R503" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:42.547114Z</t>
+        </is>
+      </c>
+      <c r="S503" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T503" s="2" t="inlineStr"/>
+      <c r="U503" s="2" t="inlineStr"/>
+      <c r="V503" s="2" t="inlineStr"/>
+      <c r="W503" s="2" t="inlineStr"/>
+      <c r="X503" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y503" s="2" t="inlineStr"/>
+      <c r="Z503" s="2" t="inlineStr"/>
+      <c r="AA503" s="2" t="inlineStr"/>
+      <c r="AB503" s="2" t="inlineStr"/>
+      <c r="AC503" s="2" t="inlineStr"/>
+      <c r="AD503" s="2" t="inlineStr"/>
+      <c r="AE503" s="2" t="inlineStr"/>
+      <c r="AF503" s="2" t="inlineStr"/>
+      <c r="AG503" s="2" t="inlineStr"/>
+      <c r="AH503" s="2" t="inlineStr"/>
+      <c r="AI503" s="2" t="inlineStr"/>
+      <c r="AJ503" s="2" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>e1477b729f4a4703</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>71318</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K504" s="2" t="inlineStr"/>
+      <c r="L504" s="2" t="inlineStr">
+        <is>
+          <t>0.689352</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="inlineStr"/>
+      <c r="N504" s="2" t="inlineStr"/>
+      <c r="O504" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P504" s="2" t="inlineStr"/>
+      <c r="Q504" s="2" t="inlineStr">
+        <is>
+          <t>-0.01034769969969973</t>
+        </is>
+      </c>
+      <c r="R504" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:43.680044Z</t>
+        </is>
+      </c>
+      <c r="S504" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T504" s="2" t="inlineStr"/>
+      <c r="U504" s="2" t="inlineStr"/>
+      <c r="V504" s="2" t="inlineStr"/>
+      <c r="W504" s="2" t="inlineStr"/>
+      <c r="X504" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y504" s="2" t="inlineStr"/>
+      <c r="Z504" s="2" t="inlineStr"/>
+      <c r="AA504" s="2" t="inlineStr"/>
+      <c r="AB504" s="2" t="inlineStr"/>
+      <c r="AC504" s="2" t="inlineStr"/>
+      <c r="AD504" s="2" t="inlineStr"/>
+      <c r="AE504" s="2" t="inlineStr"/>
+      <c r="AF504" s="2" t="inlineStr"/>
+      <c r="AG504" s="2" t="inlineStr"/>
+      <c r="AH504" s="2" t="inlineStr"/>
+      <c r="AI504" s="2" t="inlineStr"/>
+      <c r="AJ504" s="2" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>886ee6cedc1e4672</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>68563</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K505" s="2" t="inlineStr"/>
+      <c r="L505" s="2" t="inlineStr">
+        <is>
+          <t>0.526874</t>
+        </is>
+      </c>
+      <c r="M505" s="2" t="inlineStr"/>
+      <c r="N505" s="2" t="inlineStr"/>
+      <c r="O505" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P505" s="2" t="inlineStr"/>
+      <c r="Q505" s="2" t="inlineStr">
+        <is>
+          <t>-0.04394145064377686</t>
+        </is>
+      </c>
+      <c r="R505" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:44.902160Z</t>
+        </is>
+      </c>
+      <c r="S505" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T505" s="2" t="inlineStr"/>
+      <c r="U505" s="2" t="inlineStr"/>
+      <c r="V505" s="2" t="inlineStr"/>
+      <c r="W505" s="2" t="inlineStr"/>
+      <c r="X505" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y505" s="2" t="inlineStr"/>
+      <c r="Z505" s="2" t="inlineStr"/>
+      <c r="AA505" s="2" t="inlineStr"/>
+      <c r="AB505" s="2" t="inlineStr"/>
+      <c r="AC505" s="2" t="inlineStr"/>
+      <c r="AD505" s="2" t="inlineStr"/>
+      <c r="AE505" s="2" t="inlineStr"/>
+      <c r="AF505" s="2" t="inlineStr"/>
+      <c r="AG505" s="2" t="inlineStr"/>
+      <c r="AH505" s="2" t="inlineStr"/>
+      <c r="AI505" s="2" t="inlineStr"/>
+      <c r="AJ505" s="2" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>31273f06ef654e6d</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>68562</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K506" s="2" t="inlineStr"/>
+      <c r="L506" s="2" t="inlineStr">
+        <is>
+          <t>0.526874</t>
+        </is>
+      </c>
+      <c r="M506" s="2" t="inlineStr"/>
+      <c r="N506" s="2" t="inlineStr"/>
+      <c r="O506" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P506" s="2" t="inlineStr"/>
+      <c r="Q506" s="2" t="inlineStr">
+        <is>
+          <t>-0.10275562962962959</t>
+        </is>
+      </c>
+      <c r="R506" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:46.077763Z</t>
+        </is>
+      </c>
+      <c r="S506" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T506" s="2" t="inlineStr"/>
+      <c r="U506" s="2" t="inlineStr"/>
+      <c r="V506" s="2" t="inlineStr"/>
+      <c r="W506" s="2" t="inlineStr"/>
+      <c r="X506" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y506" s="2" t="inlineStr"/>
+      <c r="Z506" s="2" t="inlineStr"/>
+      <c r="AA506" s="2" t="inlineStr"/>
+      <c r="AB506" s="2" t="inlineStr"/>
+      <c r="AC506" s="2" t="inlineStr"/>
+      <c r="AD506" s="2" t="inlineStr"/>
+      <c r="AE506" s="2" t="inlineStr"/>
+      <c r="AF506" s="2" t="inlineStr"/>
+      <c r="AG506" s="2" t="inlineStr"/>
+      <c r="AH506" s="2" t="inlineStr"/>
+      <c r="AI506" s="2" t="inlineStr"/>
+      <c r="AJ506" s="2" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>bef5d0801760472f</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K507" s="2" t="inlineStr"/>
+      <c r="L507" s="2" t="inlineStr">
+        <is>
+          <t>0.500607</t>
+        </is>
+      </c>
+      <c r="M507" s="2" t="inlineStr"/>
+      <c r="N507" s="2" t="inlineStr"/>
+      <c r="O507" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P507" s="2" t="inlineStr"/>
+      <c r="Q507" s="2" t="inlineStr">
+        <is>
+          <t>0.0006070000000000242</t>
+        </is>
+      </c>
+      <c r="R507" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:47.035803Z</t>
+        </is>
+      </c>
+      <c r="S507" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T507" s="2" t="inlineStr"/>
+      <c r="U507" s="2" t="inlineStr"/>
+      <c r="V507" s="2" t="inlineStr"/>
+      <c r="W507" s="2" t="inlineStr"/>
+      <c r="X507" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y507" s="2" t="inlineStr"/>
+      <c r="Z507" s="2" t="inlineStr"/>
+      <c r="AA507" s="2" t="inlineStr"/>
+      <c r="AB507" s="2" t="inlineStr"/>
+      <c r="AC507" s="2" t="inlineStr"/>
+      <c r="AD507" s="2" t="inlineStr"/>
+      <c r="AE507" s="2" t="inlineStr"/>
+      <c r="AF507" s="2" t="inlineStr"/>
+      <c r="AG507" s="2" t="inlineStr"/>
+      <c r="AH507" s="2" t="inlineStr"/>
+      <c r="AI507" s="2" t="inlineStr"/>
+      <c r="AJ507" s="2" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>39a3eca650cc441d</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>68567</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K508" s="2" t="inlineStr"/>
+      <c r="L508" s="2" t="inlineStr">
+        <is>
+          <t>0.516308</t>
+        </is>
+      </c>
+      <c r="M508" s="2" t="inlineStr"/>
+      <c r="N508" s="2" t="inlineStr"/>
+      <c r="O508" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P508" s="2" t="inlineStr"/>
+      <c r="Q508" s="2" t="inlineStr">
+        <is>
+          <t>-0.04316336563876655</t>
+        </is>
+      </c>
+      <c r="R508" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:49.016499Z</t>
+        </is>
+      </c>
+      <c r="S508" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T508" s="2" t="inlineStr"/>
+      <c r="U508" s="2" t="inlineStr"/>
+      <c r="V508" s="2" t="inlineStr"/>
+      <c r="W508" s="2" t="inlineStr"/>
+      <c r="X508" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y508" s="2" t="inlineStr"/>
+      <c r="Z508" s="2" t="inlineStr"/>
+      <c r="AA508" s="2" t="inlineStr"/>
+      <c r="AB508" s="2" t="inlineStr"/>
+      <c r="AC508" s="2" t="inlineStr"/>
+      <c r="AD508" s="2" t="inlineStr"/>
+      <c r="AE508" s="2" t="inlineStr"/>
+      <c r="AF508" s="2" t="inlineStr"/>
+      <c r="AG508" s="2" t="inlineStr"/>
+      <c r="AH508" s="2" t="inlineStr"/>
+      <c r="AI508" s="2" t="inlineStr"/>
+      <c r="AJ508" s="2" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>91f6fbbe4b6c481b</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>68565</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K509" s="2" t="inlineStr"/>
+      <c r="L509" s="2" t="inlineStr">
+        <is>
+          <t>0.589419</t>
+        </is>
+      </c>
+      <c r="M509" s="2" t="inlineStr"/>
+      <c r="N509" s="2" t="inlineStr"/>
+      <c r="O509" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P509" s="2" t="inlineStr"/>
+      <c r="Q509" s="2" t="inlineStr">
+        <is>
+          <t>-0.09109218210862613</t>
+        </is>
+      </c>
+      <c r="R509" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:50.038289Z</t>
+        </is>
+      </c>
+      <c r="S509" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T509" s="2" t="inlineStr"/>
+      <c r="U509" s="2" t="inlineStr"/>
+      <c r="V509" s="2" t="inlineStr"/>
+      <c r="W509" s="2" t="inlineStr"/>
+      <c r="X509" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y509" s="2" t="inlineStr"/>
+      <c r="Z509" s="2" t="inlineStr"/>
+      <c r="AA509" s="2" t="inlineStr"/>
+      <c r="AB509" s="2" t="inlineStr"/>
+      <c r="AC509" s="2" t="inlineStr"/>
+      <c r="AD509" s="2" t="inlineStr"/>
+      <c r="AE509" s="2" t="inlineStr"/>
+      <c r="AF509" s="2" t="inlineStr"/>
+      <c r="AG509" s="2" t="inlineStr"/>
+      <c r="AH509" s="2" t="inlineStr"/>
+      <c r="AI509" s="2" t="inlineStr"/>
+      <c r="AJ509" s="2" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>ecd91c482b824a60</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J510" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K510" s="2" t="inlineStr"/>
+      <c r="L510" s="2" t="inlineStr">
+        <is>
+          <t>0.571516</t>
+        </is>
+      </c>
+      <c r="M510" s="2" t="inlineStr"/>
+      <c r="N510" s="2" t="inlineStr"/>
+      <c r="O510" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P510" s="2" t="inlineStr"/>
+      <c r="Q510" s="2" t="inlineStr">
+        <is>
+          <t>0.021966450450450536</t>
+        </is>
+      </c>
+      <c r="R510" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:51.128646Z</t>
+        </is>
+      </c>
+      <c r="S510" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T510" s="2" t="inlineStr"/>
+      <c r="U510" s="2" t="inlineStr"/>
+      <c r="V510" s="2" t="inlineStr"/>
+      <c r="W510" s="2" t="inlineStr"/>
+      <c r="X510" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y510" s="2" t="inlineStr"/>
+      <c r="Z510" s="2" t="inlineStr"/>
+      <c r="AA510" s="2" t="inlineStr"/>
+      <c r="AB510" s="2" t="inlineStr"/>
+      <c r="AC510" s="2" t="inlineStr"/>
+      <c r="AD510" s="2" t="inlineStr"/>
+      <c r="AE510" s="2" t="inlineStr"/>
+      <c r="AF510" s="2" t="inlineStr"/>
+      <c r="AG510" s="2" t="inlineStr"/>
+      <c r="AH510" s="2" t="inlineStr"/>
+      <c r="AI510" s="2" t="inlineStr"/>
+      <c r="AJ510" s="2" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>42b6137f443f4bff</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K511" s="2" t="inlineStr"/>
+      <c r="L511" s="2" t="inlineStr">
+        <is>
+          <t>0.681712</t>
+        </is>
+      </c>
+      <c r="M511" s="2" t="inlineStr"/>
+      <c r="N511" s="2" t="inlineStr"/>
+      <c r="O511" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P511" s="2" t="inlineStr"/>
+      <c r="Q511" s="2" t="inlineStr">
+        <is>
+          <t>0.011745003300330015</t>
+        </is>
+      </c>
+      <c r="R511" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:52.174169Z</t>
+        </is>
+      </c>
+      <c r="S511" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T511" s="2" t="inlineStr"/>
+      <c r="U511" s="2" t="inlineStr"/>
+      <c r="V511" s="2" t="inlineStr"/>
+      <c r="W511" s="2" t="inlineStr"/>
+      <c r="X511" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y511" s="2" t="inlineStr"/>
+      <c r="Z511" s="2" t="inlineStr"/>
+      <c r="AA511" s="2" t="inlineStr"/>
+      <c r="AB511" s="2" t="inlineStr"/>
+      <c r="AC511" s="2" t="inlineStr"/>
+      <c r="AD511" s="2" t="inlineStr"/>
+      <c r="AE511" s="2" t="inlineStr"/>
+      <c r="AF511" s="2" t="inlineStr"/>
+      <c r="AG511" s="2" t="inlineStr"/>
+      <c r="AH511" s="2" t="inlineStr"/>
+      <c r="AI511" s="2" t="inlineStr"/>
+      <c r="AJ511" s="2" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>e26365bb50644bb9</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K512" s="2" t="inlineStr"/>
+      <c r="L512" s="2" t="inlineStr">
+        <is>
+          <t>0.576218</t>
+        </is>
+      </c>
+      <c r="M512" s="2" t="inlineStr"/>
+      <c r="N512" s="2" t="inlineStr"/>
+      <c r="O512" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P512" s="2" t="inlineStr"/>
+      <c r="Q512" s="2" t="inlineStr">
+        <is>
+          <t>-0.02378200000000008</t>
+        </is>
+      </c>
+      <c r="R512" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:53.292238Z</t>
+        </is>
+      </c>
+      <c r="S512" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T512" s="2" t="inlineStr"/>
+      <c r="U512" s="2" t="inlineStr"/>
+      <c r="V512" s="2" t="inlineStr"/>
+      <c r="W512" s="2" t="inlineStr"/>
+      <c r="X512" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y512" s="2" t="inlineStr"/>
+      <c r="Z512" s="2" t="inlineStr"/>
+      <c r="AA512" s="2" t="inlineStr"/>
+      <c r="AB512" s="2" t="inlineStr"/>
+      <c r="AC512" s="2" t="inlineStr"/>
+      <c r="AD512" s="2" t="inlineStr"/>
+      <c r="AE512" s="2" t="inlineStr"/>
+      <c r="AF512" s="2" t="inlineStr"/>
+      <c r="AG512" s="2" t="inlineStr"/>
+      <c r="AH512" s="2" t="inlineStr"/>
+      <c r="AI512" s="2" t="inlineStr"/>
+      <c r="AJ512" s="2" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>6af4a0c81f7c4308</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>70533</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K513" s="2" t="inlineStr"/>
+      <c r="L513" s="2" t="inlineStr">
+        <is>
+          <t>0.509119</t>
+        </is>
+      </c>
+      <c r="M513" s="2" t="inlineStr"/>
+      <c r="N513" s="2" t="inlineStr"/>
+      <c r="O513" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P513" s="2" t="inlineStr"/>
+      <c r="Q513" s="2" t="inlineStr">
+        <is>
+          <t>-0.1106528631178707</t>
+        </is>
+      </c>
+      <c r="R513" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:54.329843Z</t>
+        </is>
+      </c>
+      <c r="S513" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T513" s="2" t="inlineStr"/>
+      <c r="U513" s="2" t="inlineStr"/>
+      <c r="V513" s="2" t="inlineStr"/>
+      <c r="W513" s="2" t="inlineStr"/>
+      <c r="X513" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y513" s="2" t="inlineStr"/>
+      <c r="Z513" s="2" t="inlineStr"/>
+      <c r="AA513" s="2" t="inlineStr"/>
+      <c r="AB513" s="2" t="inlineStr"/>
+      <c r="AC513" s="2" t="inlineStr"/>
+      <c r="AD513" s="2" t="inlineStr"/>
+      <c r="AE513" s="2" t="inlineStr"/>
+      <c r="AF513" s="2" t="inlineStr"/>
+      <c r="AG513" s="2" t="inlineStr"/>
+      <c r="AH513" s="2" t="inlineStr"/>
+      <c r="AI513" s="2" t="inlineStr"/>
+      <c r="AJ513" s="2" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>991128ebb6a048a4</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K514" s="2" t="inlineStr"/>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>0.674861</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="inlineStr"/>
+      <c r="N514" s="2" t="inlineStr"/>
+      <c r="O514" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P514" s="2" t="inlineStr"/>
+      <c r="Q514" s="2" t="inlineStr">
+        <is>
+          <t>0.08469706557377055</t>
+        </is>
+      </c>
+      <c r="R514" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:01:56.359942Z</t>
+        </is>
+      </c>
+      <c r="S514" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T514" s="2" t="inlineStr"/>
+      <c r="U514" s="2" t="inlineStr"/>
+      <c r="V514" s="2" t="inlineStr"/>
+      <c r="W514" s="2" t="inlineStr"/>
+      <c r="X514" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y514" s="2" t="inlineStr"/>
+      <c r="Z514" s="2" t="inlineStr"/>
+      <c r="AA514" s="2" t="inlineStr"/>
+      <c r="AB514" s="2" t="inlineStr"/>
+      <c r="AC514" s="2" t="inlineStr"/>
+      <c r="AD514" s="2" t="inlineStr"/>
+      <c r="AE514" s="2" t="inlineStr"/>
+      <c r="AF514" s="2" t="inlineStr"/>
+      <c r="AG514" s="2" t="inlineStr"/>
+      <c r="AH514" s="2" t="inlineStr"/>
+      <c r="AI514" s="2" t="inlineStr"/>
+      <c r="AJ514" s="2" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>1014cc2e520641af</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J515" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K515" s="2" t="inlineStr"/>
+      <c r="L515" s="2" t="inlineStr">
+        <is>
+          <t>0.614064</t>
+        </is>
+      </c>
+      <c r="M515" s="2" t="inlineStr"/>
+      <c r="N515" s="2" t="inlineStr"/>
+      <c r="O515" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P515" s="2" t="inlineStr"/>
+      <c r="Q515" s="2" t="inlineStr">
+        <is>
+          <t>0.023900065573770557</t>
+        </is>
+      </c>
+      <c r="R515" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:00.755213Z</t>
+        </is>
+      </c>
+      <c r="S515" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T515" s="2" t="inlineStr"/>
+      <c r="U515" s="2" t="inlineStr"/>
+      <c r="V515" s="2" t="inlineStr"/>
+      <c r="W515" s="2" t="inlineStr"/>
+      <c r="X515" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y515" s="2" t="inlineStr"/>
+      <c r="Z515" s="2" t="inlineStr"/>
+      <c r="AA515" s="2" t="inlineStr"/>
+      <c r="AB515" s="2" t="inlineStr"/>
+      <c r="AC515" s="2" t="inlineStr"/>
+      <c r="AD515" s="2" t="inlineStr"/>
+      <c r="AE515" s="2" t="inlineStr"/>
+      <c r="AF515" s="2" t="inlineStr"/>
+      <c r="AG515" s="2" t="inlineStr"/>
+      <c r="AH515" s="2" t="inlineStr"/>
+      <c r="AI515" s="2" t="inlineStr"/>
+      <c r="AJ515" s="2" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>8612fe55cb8341cf</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K516" s="2" t="inlineStr"/>
+      <c r="L516" s="2" t="inlineStr">
+        <is>
+          <t>0.556108</t>
+        </is>
+      </c>
+      <c r="M516" s="2" t="inlineStr"/>
+      <c r="N516" s="2" t="inlineStr"/>
+      <c r="O516" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P516" s="2" t="inlineStr"/>
+      <c r="Q516" s="2" t="inlineStr">
+        <is>
+          <t>0.036877230769230884</t>
+        </is>
+      </c>
+      <c r="R516" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:01.863539Z</t>
+        </is>
+      </c>
+      <c r="S516" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T516" s="2" t="inlineStr"/>
+      <c r="U516" s="2" t="inlineStr"/>
+      <c r="V516" s="2" t="inlineStr"/>
+      <c r="W516" s="2" t="inlineStr"/>
+      <c r="X516" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y516" s="2" t="inlineStr"/>
+      <c r="Z516" s="2" t="inlineStr"/>
+      <c r="AA516" s="2" t="inlineStr"/>
+      <c r="AB516" s="2" t="inlineStr"/>
+      <c r="AC516" s="2" t="inlineStr"/>
+      <c r="AD516" s="2" t="inlineStr"/>
+      <c r="AE516" s="2" t="inlineStr"/>
+      <c r="AF516" s="2" t="inlineStr"/>
+      <c r="AG516" s="2" t="inlineStr"/>
+      <c r="AH516" s="2" t="inlineStr"/>
+      <c r="AI516" s="2" t="inlineStr"/>
+      <c r="AJ516" s="2" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>efa8fd1dac624475</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J517" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K517" s="2" t="inlineStr"/>
+      <c r="L517" s="2" t="inlineStr">
+        <is>
+          <t>0.698282</t>
+        </is>
+      </c>
+      <c r="M517" s="2" t="inlineStr"/>
+      <c r="N517" s="2" t="inlineStr"/>
+      <c r="O517" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P517" s="2" t="inlineStr"/>
+      <c r="Q517" s="2" t="inlineStr">
+        <is>
+          <t>0.18847807843137254</t>
+        </is>
+      </c>
+      <c r="R517" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:03.034553Z</t>
+        </is>
+      </c>
+      <c r="S517" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T517" s="2" t="inlineStr"/>
+      <c r="U517" s="2" t="inlineStr"/>
+      <c r="V517" s="2" t="inlineStr"/>
+      <c r="W517" s="2" t="inlineStr"/>
+      <c r="X517" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y517" s="2" t="inlineStr"/>
+      <c r="Z517" s="2" t="inlineStr"/>
+      <c r="AA517" s="2" t="inlineStr"/>
+      <c r="AB517" s="2" t="inlineStr"/>
+      <c r="AC517" s="2" t="inlineStr"/>
+      <c r="AD517" s="2" t="inlineStr"/>
+      <c r="AE517" s="2" t="inlineStr"/>
+      <c r="AF517" s="2" t="inlineStr"/>
+      <c r="AG517" s="2" t="inlineStr"/>
+      <c r="AH517" s="2" t="inlineStr"/>
+      <c r="AI517" s="2" t="inlineStr"/>
+      <c r="AJ517" s="2" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>6ed0de190ac54c64</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K518" s="2" t="inlineStr"/>
+      <c r="L518" s="2" t="inlineStr">
+        <is>
+          <t>0.599172</t>
+        </is>
+      </c>
+      <c r="M518" s="2" t="inlineStr"/>
+      <c r="N518" s="2" t="inlineStr"/>
+      <c r="O518" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P518" s="2" t="inlineStr"/>
+      <c r="Q518" s="2" t="inlineStr">
+        <is>
+          <t>-0.020599863117870654</t>
+        </is>
+      </c>
+      <c r="R518" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:04.123815Z</t>
+        </is>
+      </c>
+      <c r="S518" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T518" s="2" t="inlineStr"/>
+      <c r="U518" s="2" t="inlineStr"/>
+      <c r="V518" s="2" t="inlineStr"/>
+      <c r="W518" s="2" t="inlineStr"/>
+      <c r="X518" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y518" s="2" t="inlineStr"/>
+      <c r="Z518" s="2" t="inlineStr"/>
+      <c r="AA518" s="2" t="inlineStr"/>
+      <c r="AB518" s="2" t="inlineStr"/>
+      <c r="AC518" s="2" t="inlineStr"/>
+      <c r="AD518" s="2" t="inlineStr"/>
+      <c r="AE518" s="2" t="inlineStr"/>
+      <c r="AF518" s="2" t="inlineStr"/>
+      <c r="AG518" s="2" t="inlineStr"/>
+      <c r="AH518" s="2" t="inlineStr"/>
+      <c r="AI518" s="2" t="inlineStr"/>
+      <c r="AJ518" s="2" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>4a6d56d669cc45c5</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K519" s="2" t="inlineStr"/>
+      <c r="L519" s="2" t="inlineStr">
+        <is>
+          <t>0.645957</t>
+        </is>
+      </c>
+      <c r="M519" s="2" t="inlineStr"/>
+      <c r="N519" s="2" t="inlineStr"/>
+      <c r="O519" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P519" s="2" t="inlineStr"/>
+      <c r="Q519" s="2" t="inlineStr">
+        <is>
+          <t>0.11544056807511738</t>
+        </is>
+      </c>
+      <c r="R519" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:05.325732Z</t>
+        </is>
+      </c>
+      <c r="S519" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T519" s="2" t="inlineStr"/>
+      <c r="U519" s="2" t="inlineStr"/>
+      <c r="V519" s="2" t="inlineStr"/>
+      <c r="W519" s="2" t="inlineStr"/>
+      <c r="X519" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y519" s="2" t="inlineStr"/>
+      <c r="Z519" s="2" t="inlineStr"/>
+      <c r="AA519" s="2" t="inlineStr"/>
+      <c r="AB519" s="2" t="inlineStr"/>
+      <c r="AC519" s="2" t="inlineStr"/>
+      <c r="AD519" s="2" t="inlineStr"/>
+      <c r="AE519" s="2" t="inlineStr"/>
+      <c r="AF519" s="2" t="inlineStr"/>
+      <c r="AG519" s="2" t="inlineStr"/>
+      <c r="AH519" s="2" t="inlineStr"/>
+      <c r="AI519" s="2" t="inlineStr"/>
+      <c r="AJ519" s="2" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>e3aee9e6a8b4401d</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>69510</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K520" s="2" t="inlineStr"/>
+      <c r="L520" s="2" t="inlineStr">
+        <is>
+          <t>0.51281</t>
+        </is>
+      </c>
+      <c r="M520" s="2" t="inlineStr"/>
+      <c r="N520" s="2" t="inlineStr"/>
+      <c r="O520" s="2" t="inlineStr">
+        <is>
+          <t>0.30959752321981426</t>
+        </is>
+      </c>
+      <c r="P520" s="2" t="inlineStr"/>
+      <c r="Q520" s="2" t="inlineStr">
+        <is>
+          <t>0.20321247678018572</t>
+        </is>
+      </c>
+      <c r="R520" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:10.395786Z</t>
+        </is>
+      </c>
+      <c r="S520" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T520" s="2" t="inlineStr"/>
+      <c r="U520" s="2" t="inlineStr"/>
+      <c r="V520" s="2" t="inlineStr"/>
+      <c r="W520" s="2" t="inlineStr"/>
+      <c r="X520" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y520" s="2" t="inlineStr"/>
+      <c r="Z520" s="2" t="inlineStr"/>
+      <c r="AA520" s="2" t="inlineStr"/>
+      <c r="AB520" s="2" t="inlineStr"/>
+      <c r="AC520" s="2" t="inlineStr"/>
+      <c r="AD520" s="2" t="inlineStr"/>
+      <c r="AE520" s="2" t="inlineStr"/>
+      <c r="AF520" s="2" t="inlineStr"/>
+      <c r="AG520" s="2" t="inlineStr"/>
+      <c r="AH520" s="2" t="inlineStr"/>
+      <c r="AI520" s="2" t="inlineStr"/>
+      <c r="AJ520" s="2" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>58f801692f0a4c3d</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>69537</t>
+        </is>
+      </c>
+      <c r="I521" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K521" s="2" t="inlineStr"/>
+      <c r="L521" s="2" t="inlineStr">
+        <is>
+          <t>0.536662</t>
+        </is>
+      </c>
+      <c r="M521" s="2" t="inlineStr"/>
+      <c r="N521" s="2" t="inlineStr"/>
+      <c r="O521" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P521" s="2" t="inlineStr"/>
+      <c r="Q521" s="2" t="inlineStr">
+        <is>
+          <t>0.10747745064377678</t>
+        </is>
+      </c>
+      <c r="R521" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:11.519418Z</t>
+        </is>
+      </c>
+      <c r="S521" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T521" s="2" t="inlineStr"/>
+      <c r="U521" s="2" t="inlineStr"/>
+      <c r="V521" s="2" t="inlineStr"/>
+      <c r="W521" s="2" t="inlineStr"/>
+      <c r="X521" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y521" s="2" t="inlineStr"/>
+      <c r="Z521" s="2" t="inlineStr"/>
+      <c r="AA521" s="2" t="inlineStr"/>
+      <c r="AB521" s="2" t="inlineStr"/>
+      <c r="AC521" s="2" t="inlineStr"/>
+      <c r="AD521" s="2" t="inlineStr"/>
+      <c r="AE521" s="2" t="inlineStr"/>
+      <c r="AF521" s="2" t="inlineStr"/>
+      <c r="AG521" s="2" t="inlineStr"/>
+      <c r="AH521" s="2" t="inlineStr"/>
+      <c r="AI521" s="2" t="inlineStr"/>
+      <c r="AJ521" s="2" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>72a0bb4132c54b8d</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>71199</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K522" s="2" t="inlineStr"/>
+      <c r="L522" s="2" t="inlineStr">
+        <is>
+          <t>0.506069</t>
+        </is>
+      </c>
+      <c r="M522" s="2" t="inlineStr"/>
+      <c r="N522" s="2" t="inlineStr"/>
+      <c r="O522" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P522" s="2" t="inlineStr"/>
+      <c r="Q522" s="2" t="inlineStr">
+        <is>
+          <t>0.06554036563876653</t>
+        </is>
+      </c>
+      <c r="R522" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:16.646106Z</t>
+        </is>
+      </c>
+      <c r="S522" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T522" s="2" t="inlineStr"/>
+      <c r="U522" s="2" t="inlineStr"/>
+      <c r="V522" s="2" t="inlineStr"/>
+      <c r="W522" s="2" t="inlineStr"/>
+      <c r="X522" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y522" s="2" t="inlineStr"/>
+      <c r="Z522" s="2" t="inlineStr"/>
+      <c r="AA522" s="2" t="inlineStr"/>
+      <c r="AB522" s="2" t="inlineStr"/>
+      <c r="AC522" s="2" t="inlineStr"/>
+      <c r="AD522" s="2" t="inlineStr"/>
+      <c r="AE522" s="2" t="inlineStr"/>
+      <c r="AF522" s="2" t="inlineStr"/>
+      <c r="AG522" s="2" t="inlineStr"/>
+      <c r="AH522" s="2" t="inlineStr"/>
+      <c r="AI522" s="2" t="inlineStr"/>
+      <c r="AJ522" s="2" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>ea4825ef528d4020</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="I523" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J523" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K523" s="2" t="inlineStr"/>
+      <c r="L523" s="2" t="inlineStr">
+        <is>
+          <t>0.526874</t>
+        </is>
+      </c>
+      <c r="M523" s="2" t="inlineStr"/>
+      <c r="N523" s="2" t="inlineStr"/>
+      <c r="O523" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P523" s="2" t="inlineStr"/>
+      <c r="Q523" s="2" t="inlineStr">
+        <is>
+          <t>-0.04394145064377686</t>
+        </is>
+      </c>
+      <c r="R523" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:17.714438Z</t>
+        </is>
+      </c>
+      <c r="S523" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T523" s="2" t="inlineStr"/>
+      <c r="U523" s="2" t="inlineStr"/>
+      <c r="V523" s="2" t="inlineStr"/>
+      <c r="W523" s="2" t="inlineStr"/>
+      <c r="X523" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y523" s="2" t="inlineStr"/>
+      <c r="Z523" s="2" t="inlineStr"/>
+      <c r="AA523" s="2" t="inlineStr"/>
+      <c r="AB523" s="2" t="inlineStr"/>
+      <c r="AC523" s="2" t="inlineStr"/>
+      <c r="AD523" s="2" t="inlineStr"/>
+      <c r="AE523" s="2" t="inlineStr"/>
+      <c r="AF523" s="2" t="inlineStr"/>
+      <c r="AG523" s="2" t="inlineStr"/>
+      <c r="AH523" s="2" t="inlineStr"/>
+      <c r="AI523" s="2" t="inlineStr"/>
+      <c r="AJ523" s="2" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>c8951270e0624b29</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K524" s="2" t="inlineStr"/>
+      <c r="L524" s="2" t="inlineStr">
+        <is>
+          <t>0.5377</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="inlineStr"/>
+      <c r="N524" s="2" t="inlineStr"/>
+      <c r="O524" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P524" s="2" t="inlineStr"/>
+      <c r="Q524" s="2" t="inlineStr">
+        <is>
+          <t>-0.033115450643776856</t>
+        </is>
+      </c>
+      <c r="R524" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:25.160499Z</t>
+        </is>
+      </c>
+      <c r="S524" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T524" s="2" t="inlineStr"/>
+      <c r="U524" s="2" t="inlineStr"/>
+      <c r="V524" s="2" t="inlineStr"/>
+      <c r="W524" s="2" t="inlineStr"/>
+      <c r="X524" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y524" s="2" t="inlineStr"/>
+      <c r="Z524" s="2" t="inlineStr"/>
+      <c r="AA524" s="2" t="inlineStr"/>
+      <c r="AB524" s="2" t="inlineStr"/>
+      <c r="AC524" s="2" t="inlineStr"/>
+      <c r="AD524" s="2" t="inlineStr"/>
+      <c r="AE524" s="2" t="inlineStr"/>
+      <c r="AF524" s="2" t="inlineStr"/>
+      <c r="AG524" s="2" t="inlineStr"/>
+      <c r="AH524" s="2" t="inlineStr"/>
+      <c r="AI524" s="2" t="inlineStr"/>
+      <c r="AJ524" s="2" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>aa011222d07a4cd6</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>70104</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J525" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K525" s="2" t="inlineStr"/>
+      <c r="L525" s="2" t="inlineStr">
+        <is>
+          <t>0.526178</t>
+        </is>
+      </c>
+      <c r="M525" s="2" t="inlineStr"/>
+      <c r="N525" s="2" t="inlineStr"/>
+      <c r="O525" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P525" s="2" t="inlineStr"/>
+      <c r="Q525" s="2" t="inlineStr">
+        <is>
+          <t>0.006947230769230872</t>
+        </is>
+      </c>
+      <c r="R525" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:02:30.113859Z</t>
+        </is>
+      </c>
+      <c r="S525" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T525" s="2" t="inlineStr"/>
+      <c r="U525" s="2" t="inlineStr"/>
+      <c r="V525" s="2" t="inlineStr"/>
+      <c r="W525" s="2" t="inlineStr"/>
+      <c r="X525" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y525" s="2" t="inlineStr"/>
+      <c r="Z525" s="2" t="inlineStr"/>
+      <c r="AA525" s="2" t="inlineStr"/>
+      <c r="AB525" s="2" t="inlineStr"/>
+      <c r="AC525" s="2" t="inlineStr"/>
+      <c r="AD525" s="2" t="inlineStr"/>
+      <c r="AE525" s="2" t="inlineStr"/>
+      <c r="AF525" s="2" t="inlineStr"/>
+      <c r="AG525" s="2" t="inlineStr"/>
+      <c r="AH525" s="2" t="inlineStr"/>
+      <c r="AI525" s="2" t="inlineStr"/>
+      <c r="AJ525" s="2" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>6de4cb7d300941fe</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>68562</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K526" s="2" t="inlineStr"/>
+      <c r="L526" s="2" t="inlineStr">
+        <is>
+          <t>0.526798</t>
+        </is>
+      </c>
+      <c r="M526" s="2" t="inlineStr"/>
+      <c r="N526" s="2" t="inlineStr"/>
+      <c r="O526" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P526" s="2" t="inlineStr"/>
+      <c r="Q526" s="2" t="inlineStr">
+        <is>
+          <t>-0.10283162962962955</t>
+        </is>
+      </c>
+      <c r="R526" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:05.955221Z</t>
+        </is>
+      </c>
+      <c r="S526" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T526" s="2" t="inlineStr"/>
+      <c r="U526" s="2" t="inlineStr"/>
+      <c r="V526" s="2" t="inlineStr"/>
+      <c r="W526" s="2" t="inlineStr"/>
+      <c r="X526" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y526" s="2" t="inlineStr"/>
+      <c r="Z526" s="2" t="inlineStr"/>
+      <c r="AA526" s="2" t="inlineStr"/>
+      <c r="AB526" s="2" t="inlineStr"/>
+      <c r="AC526" s="2" t="inlineStr"/>
+      <c r="AD526" s="2" t="inlineStr"/>
+      <c r="AE526" s="2" t="inlineStr"/>
+      <c r="AF526" s="2" t="inlineStr"/>
+      <c r="AG526" s="2" t="inlineStr"/>
+      <c r="AH526" s="2" t="inlineStr"/>
+      <c r="AI526" s="2" t="inlineStr"/>
+      <c r="AJ526" s="2" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>ef19da936b634b62</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>68563</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J527" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K527" s="2" t="inlineStr"/>
+      <c r="L527" s="2" t="inlineStr">
+        <is>
+          <t>0.526798</t>
+        </is>
+      </c>
+      <c r="M527" s="2" t="inlineStr"/>
+      <c r="N527" s="2" t="inlineStr"/>
+      <c r="O527" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P527" s="2" t="inlineStr"/>
+      <c r="Q527" s="2" t="inlineStr">
+        <is>
+          <t>-0.04401745064377682</t>
+        </is>
+      </c>
+      <c r="R527" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:06.519722Z</t>
+        </is>
+      </c>
+      <c r="S527" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T527" s="2" t="inlineStr"/>
+      <c r="U527" s="2" t="inlineStr"/>
+      <c r="V527" s="2" t="inlineStr"/>
+      <c r="W527" s="2" t="inlineStr"/>
+      <c r="X527" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y527" s="2" t="inlineStr"/>
+      <c r="Z527" s="2" t="inlineStr"/>
+      <c r="AA527" s="2" t="inlineStr"/>
+      <c r="AB527" s="2" t="inlineStr"/>
+      <c r="AC527" s="2" t="inlineStr"/>
+      <c r="AD527" s="2" t="inlineStr"/>
+      <c r="AE527" s="2" t="inlineStr"/>
+      <c r="AF527" s="2" t="inlineStr"/>
+      <c r="AG527" s="2" t="inlineStr"/>
+      <c r="AH527" s="2" t="inlineStr"/>
+      <c r="AI527" s="2" t="inlineStr"/>
+      <c r="AJ527" s="2" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>07e5fa10d9304a96</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>68565</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K528" s="2" t="inlineStr"/>
+      <c r="L528" s="2" t="inlineStr">
+        <is>
+          <t>0.589329</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="inlineStr"/>
+      <c r="N528" s="2" t="inlineStr"/>
+      <c r="O528" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P528" s="2" t="inlineStr"/>
+      <c r="Q528" s="2" t="inlineStr">
+        <is>
+          <t>-0.09118218210862616</t>
+        </is>
+      </c>
+      <c r="R528" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:07.130843Z</t>
+        </is>
+      </c>
+      <c r="S528" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T528" s="2" t="inlineStr"/>
+      <c r="U528" s="2" t="inlineStr"/>
+      <c r="V528" s="2" t="inlineStr"/>
+      <c r="W528" s="2" t="inlineStr"/>
+      <c r="X528" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y528" s="2" t="inlineStr"/>
+      <c r="Z528" s="2" t="inlineStr"/>
+      <c r="AA528" s="2" t="inlineStr"/>
+      <c r="AB528" s="2" t="inlineStr"/>
+      <c r="AC528" s="2" t="inlineStr"/>
+      <c r="AD528" s="2" t="inlineStr"/>
+      <c r="AE528" s="2" t="inlineStr"/>
+      <c r="AF528" s="2" t="inlineStr"/>
+      <c r="AG528" s="2" t="inlineStr"/>
+      <c r="AH528" s="2" t="inlineStr"/>
+      <c r="AI528" s="2" t="inlineStr"/>
+      <c r="AJ528" s="2" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>1b60754b1cc448be</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>68567</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J529" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K529" s="2" t="inlineStr"/>
+      <c r="L529" s="2" t="inlineStr">
+        <is>
+          <t>0.516198</t>
+        </is>
+      </c>
+      <c r="M529" s="2" t="inlineStr"/>
+      <c r="N529" s="2" t="inlineStr"/>
+      <c r="O529" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P529" s="2" t="inlineStr"/>
+      <c r="Q529" s="2" t="inlineStr">
+        <is>
+          <t>-0.04327336563876649</t>
+        </is>
+      </c>
+      <c r="R529" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:07.740231Z</t>
+        </is>
+      </c>
+      <c r="S529" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T529" s="2" t="inlineStr"/>
+      <c r="U529" s="2" t="inlineStr"/>
+      <c r="V529" s="2" t="inlineStr"/>
+      <c r="W529" s="2" t="inlineStr"/>
+      <c r="X529" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y529" s="2" t="inlineStr"/>
+      <c r="Z529" s="2" t="inlineStr"/>
+      <c r="AA529" s="2" t="inlineStr"/>
+      <c r="AB529" s="2" t="inlineStr"/>
+      <c r="AC529" s="2" t="inlineStr"/>
+      <c r="AD529" s="2" t="inlineStr"/>
+      <c r="AE529" s="2" t="inlineStr"/>
+      <c r="AF529" s="2" t="inlineStr"/>
+      <c r="AG529" s="2" t="inlineStr"/>
+      <c r="AH529" s="2" t="inlineStr"/>
+      <c r="AI529" s="2" t="inlineStr"/>
+      <c r="AJ529" s="2" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>be59143c41334ef2</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K530" s="2" t="inlineStr"/>
+      <c r="L530" s="2" t="inlineStr">
+        <is>
+          <t>0.571449</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="inlineStr"/>
+      <c r="N530" s="2" t="inlineStr"/>
+      <c r="O530" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P530" s="2" t="inlineStr"/>
+      <c r="Q530" s="2" t="inlineStr">
+        <is>
+          <t>0.021899450450450497</t>
+        </is>
+      </c>
+      <c r="R530" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:08.278263Z</t>
+        </is>
+      </c>
+      <c r="S530" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T530" s="2" t="inlineStr"/>
+      <c r="U530" s="2" t="inlineStr"/>
+      <c r="V530" s="2" t="inlineStr"/>
+      <c r="W530" s="2" t="inlineStr"/>
+      <c r="X530" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y530" s="2" t="inlineStr"/>
+      <c r="Z530" s="2" t="inlineStr"/>
+      <c r="AA530" s="2" t="inlineStr"/>
+      <c r="AB530" s="2" t="inlineStr"/>
+      <c r="AC530" s="2" t="inlineStr"/>
+      <c r="AD530" s="2" t="inlineStr"/>
+      <c r="AE530" s="2" t="inlineStr"/>
+      <c r="AF530" s="2" t="inlineStr"/>
+      <c r="AG530" s="2" t="inlineStr"/>
+      <c r="AH530" s="2" t="inlineStr"/>
+      <c r="AI530" s="2" t="inlineStr"/>
+      <c r="AJ530" s="2" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>743860af751e40d1</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G531" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="I531" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J531" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K531" s="2" t="inlineStr"/>
+      <c r="L531" s="2" t="inlineStr">
+        <is>
+          <t>0.500666</t>
+        </is>
+      </c>
+      <c r="M531" s="2" t="inlineStr"/>
+      <c r="N531" s="2" t="inlineStr"/>
+      <c r="O531" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P531" s="2" t="inlineStr"/>
+      <c r="Q531" s="2" t="inlineStr">
+        <is>
+          <t>0.0006660000000000554</t>
+        </is>
+      </c>
+      <c r="R531" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:08.955871Z</t>
+        </is>
+      </c>
+      <c r="S531" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T531" s="2" t="inlineStr"/>
+      <c r="U531" s="2" t="inlineStr"/>
+      <c r="V531" s="2" t="inlineStr"/>
+      <c r="W531" s="2" t="inlineStr"/>
+      <c r="X531" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y531" s="2" t="inlineStr"/>
+      <c r="Z531" s="2" t="inlineStr"/>
+      <c r="AA531" s="2" t="inlineStr"/>
+      <c r="AB531" s="2" t="inlineStr"/>
+      <c r="AC531" s="2" t="inlineStr"/>
+      <c r="AD531" s="2" t="inlineStr"/>
+      <c r="AE531" s="2" t="inlineStr"/>
+      <c r="AF531" s="2" t="inlineStr"/>
+      <c r="AG531" s="2" t="inlineStr"/>
+      <c r="AH531" s="2" t="inlineStr"/>
+      <c r="AI531" s="2" t="inlineStr"/>
+      <c r="AJ531" s="2" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>b3860cb826a145b9</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K532" s="2" t="inlineStr"/>
+      <c r="L532" s="2" t="inlineStr">
+        <is>
+          <t>0.681734</t>
+        </is>
+      </c>
+      <c r="M532" s="2" t="inlineStr"/>
+      <c r="N532" s="2" t="inlineStr"/>
+      <c r="O532" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P532" s="2" t="inlineStr"/>
+      <c r="Q532" s="2" t="inlineStr">
+        <is>
+          <t>0.011767003300329981</t>
+        </is>
+      </c>
+      <c r="R532" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:10.074450Z</t>
+        </is>
+      </c>
+      <c r="S532" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T532" s="2" t="inlineStr"/>
+      <c r="U532" s="2" t="inlineStr"/>
+      <c r="V532" s="2" t="inlineStr"/>
+      <c r="W532" s="2" t="inlineStr"/>
+      <c r="X532" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y532" s="2" t="inlineStr"/>
+      <c r="Z532" s="2" t="inlineStr"/>
+      <c r="AA532" s="2" t="inlineStr"/>
+      <c r="AB532" s="2" t="inlineStr"/>
+      <c r="AC532" s="2" t="inlineStr"/>
+      <c r="AD532" s="2" t="inlineStr"/>
+      <c r="AE532" s="2" t="inlineStr"/>
+      <c r="AF532" s="2" t="inlineStr"/>
+      <c r="AG532" s="2" t="inlineStr"/>
+      <c r="AH532" s="2" t="inlineStr"/>
+      <c r="AI532" s="2" t="inlineStr"/>
+      <c r="AJ532" s="2" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>49ec50e3f18d4441</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K533" s="2" t="inlineStr"/>
+      <c r="L533" s="2" t="inlineStr">
+        <is>
+          <t>0.67486</t>
+        </is>
+      </c>
+      <c r="M533" s="2" t="inlineStr"/>
+      <c r="N533" s="2" t="inlineStr"/>
+      <c r="O533" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P533" s="2" t="inlineStr"/>
+      <c r="Q533" s="2" t="inlineStr">
+        <is>
+          <t>0.08469606557377052</t>
+        </is>
+      </c>
+      <c r="R533" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:11.142800Z</t>
+        </is>
+      </c>
+      <c r="S533" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T533" s="2" t="inlineStr"/>
+      <c r="U533" s="2" t="inlineStr"/>
+      <c r="V533" s="2" t="inlineStr"/>
+      <c r="W533" s="2" t="inlineStr"/>
+      <c r="X533" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y533" s="2" t="inlineStr"/>
+      <c r="Z533" s="2" t="inlineStr"/>
+      <c r="AA533" s="2" t="inlineStr"/>
+      <c r="AB533" s="2" t="inlineStr"/>
+      <c r="AC533" s="2" t="inlineStr"/>
+      <c r="AD533" s="2" t="inlineStr"/>
+      <c r="AE533" s="2" t="inlineStr"/>
+      <c r="AF533" s="2" t="inlineStr"/>
+      <c r="AG533" s="2" t="inlineStr"/>
+      <c r="AH533" s="2" t="inlineStr"/>
+      <c r="AI533" s="2" t="inlineStr"/>
+      <c r="AJ533" s="2" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>66eb45d23abb4822</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>71341</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K534" s="2" t="inlineStr"/>
+      <c r="L534" s="2" t="inlineStr">
+        <is>
+          <t>0.505296</t>
+        </is>
+      </c>
+      <c r="M534" s="2" t="inlineStr"/>
+      <c r="N534" s="2" t="inlineStr"/>
+      <c r="O534" s="2" t="inlineStr">
+        <is>
+          <t>0.4807692307692307</t>
+        </is>
+      </c>
+      <c r="P534" s="2" t="inlineStr"/>
+      <c r="Q534" s="2" t="inlineStr">
+        <is>
+          <t>0.02452676923076924</t>
+        </is>
+      </c>
+      <c r="R534" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:11.634967Z</t>
+        </is>
+      </c>
+      <c r="S534" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T534" s="2" t="inlineStr"/>
+      <c r="U534" s="2" t="inlineStr"/>
+      <c r="V534" s="2" t="inlineStr"/>
+      <c r="W534" s="2" t="inlineStr"/>
+      <c r="X534" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y534" s="2" t="inlineStr"/>
+      <c r="Z534" s="2" t="inlineStr"/>
+      <c r="AA534" s="2" t="inlineStr"/>
+      <c r="AB534" s="2" t="inlineStr"/>
+      <c r="AC534" s="2" t="inlineStr"/>
+      <c r="AD534" s="2" t="inlineStr"/>
+      <c r="AE534" s="2" t="inlineStr"/>
+      <c r="AF534" s="2" t="inlineStr"/>
+      <c r="AG534" s="2" t="inlineStr"/>
+      <c r="AH534" s="2" t="inlineStr"/>
+      <c r="AI534" s="2" t="inlineStr"/>
+      <c r="AJ534" s="2" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>c30c8e0582574065</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K535" s="2" t="inlineStr"/>
+      <c r="L535" s="2" t="inlineStr">
+        <is>
+          <t>0.599257</t>
+        </is>
+      </c>
+      <c r="M535" s="2" t="inlineStr"/>
+      <c r="N535" s="2" t="inlineStr"/>
+      <c r="O535" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P535" s="2" t="inlineStr"/>
+      <c r="Q535" s="2" t="inlineStr">
+        <is>
+          <t>-0.020514863117870652</t>
+        </is>
+      </c>
+      <c r="R535" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:12.173847Z</t>
+        </is>
+      </c>
+      <c r="S535" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T535" s="2" t="inlineStr"/>
+      <c r="U535" s="2" t="inlineStr"/>
+      <c r="V535" s="2" t="inlineStr"/>
+      <c r="W535" s="2" t="inlineStr"/>
+      <c r="X535" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y535" s="2" t="inlineStr"/>
+      <c r="Z535" s="2" t="inlineStr"/>
+      <c r="AA535" s="2" t="inlineStr"/>
+      <c r="AB535" s="2" t="inlineStr"/>
+      <c r="AC535" s="2" t="inlineStr"/>
+      <c r="AD535" s="2" t="inlineStr"/>
+      <c r="AE535" s="2" t="inlineStr"/>
+      <c r="AF535" s="2" t="inlineStr"/>
+      <c r="AG535" s="2" t="inlineStr"/>
+      <c r="AH535" s="2" t="inlineStr"/>
+      <c r="AI535" s="2" t="inlineStr"/>
+      <c r="AJ535" s="2" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>18a4a2dd4c1645c3</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K536" s="2" t="inlineStr"/>
+      <c r="L536" s="2" t="inlineStr">
+        <is>
+          <t>0.645876</t>
+        </is>
+      </c>
+      <c r="M536" s="2" t="inlineStr"/>
+      <c r="N536" s="2" t="inlineStr"/>
+      <c r="O536" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P536" s="2" t="inlineStr"/>
+      <c r="Q536" s="2" t="inlineStr">
+        <is>
+          <t>0.1850465069124424</t>
+        </is>
+      </c>
+      <c r="R536" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:12.914229Z</t>
+        </is>
+      </c>
+      <c r="S536" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T536" s="2" t="inlineStr"/>
+      <c r="U536" s="2" t="inlineStr"/>
+      <c r="V536" s="2" t="inlineStr"/>
+      <c r="W536" s="2" t="inlineStr"/>
+      <c r="X536" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y536" s="2" t="inlineStr"/>
+      <c r="Z536" s="2" t="inlineStr"/>
+      <c r="AA536" s="2" t="inlineStr"/>
+      <c r="AB536" s="2" t="inlineStr"/>
+      <c r="AC536" s="2" t="inlineStr"/>
+      <c r="AD536" s="2" t="inlineStr"/>
+      <c r="AE536" s="2" t="inlineStr"/>
+      <c r="AF536" s="2" t="inlineStr"/>
+      <c r="AG536" s="2" t="inlineStr"/>
+      <c r="AH536" s="2" t="inlineStr"/>
+      <c r="AI536" s="2" t="inlineStr"/>
+      <c r="AJ536" s="2" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>408d07d1353e4a05</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K537" s="2" t="inlineStr"/>
+      <c r="L537" s="2" t="inlineStr">
+        <is>
+          <t>0.576143</t>
+        </is>
+      </c>
+      <c r="M537" s="2" t="inlineStr"/>
+      <c r="N537" s="2" t="inlineStr"/>
+      <c r="O537" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P537" s="2" t="inlineStr"/>
+      <c r="Q537" s="2" t="inlineStr">
+        <is>
+          <t>0.005327549356223149</t>
+        </is>
+      </c>
+      <c r="R537" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:13.493644Z</t>
+        </is>
+      </c>
+      <c r="S537" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T537" s="2" t="inlineStr"/>
+      <c r="U537" s="2" t="inlineStr"/>
+      <c r="V537" s="2" t="inlineStr"/>
+      <c r="W537" s="2" t="inlineStr"/>
+      <c r="X537" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y537" s="2" t="inlineStr"/>
+      <c r="Z537" s="2" t="inlineStr"/>
+      <c r="AA537" s="2" t="inlineStr"/>
+      <c r="AB537" s="2" t="inlineStr"/>
+      <c r="AC537" s="2" t="inlineStr"/>
+      <c r="AD537" s="2" t="inlineStr"/>
+      <c r="AE537" s="2" t="inlineStr"/>
+      <c r="AF537" s="2" t="inlineStr"/>
+      <c r="AG537" s="2" t="inlineStr"/>
+      <c r="AH537" s="2" t="inlineStr"/>
+      <c r="AI537" s="2" t="inlineStr"/>
+      <c r="AJ537" s="2" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>a7bd0adb730747b0</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K538" s="2" t="inlineStr"/>
+      <c r="L538" s="2" t="inlineStr">
+        <is>
+          <t>0.556024</t>
+        </is>
+      </c>
+      <c r="M538" s="2" t="inlineStr"/>
+      <c r="N538" s="2" t="inlineStr"/>
+      <c r="O538" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P538" s="2" t="inlineStr"/>
+      <c r="Q538" s="2" t="inlineStr">
+        <is>
+          <t>0.0367932307692308</t>
+        </is>
+      </c>
+      <c r="R538" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:14.595932Z</t>
+        </is>
+      </c>
+      <c r="S538" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T538" s="2" t="inlineStr"/>
+      <c r="U538" s="2" t="inlineStr"/>
+      <c r="V538" s="2" t="inlineStr"/>
+      <c r="W538" s="2" t="inlineStr"/>
+      <c r="X538" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y538" s="2" t="inlineStr"/>
+      <c r="Z538" s="2" t="inlineStr"/>
+      <c r="AA538" s="2" t="inlineStr"/>
+      <c r="AB538" s="2" t="inlineStr"/>
+      <c r="AC538" s="2" t="inlineStr"/>
+      <c r="AD538" s="2" t="inlineStr"/>
+      <c r="AE538" s="2" t="inlineStr"/>
+      <c r="AF538" s="2" t="inlineStr"/>
+      <c r="AG538" s="2" t="inlineStr"/>
+      <c r="AH538" s="2" t="inlineStr"/>
+      <c r="AI538" s="2" t="inlineStr"/>
+      <c r="AJ538" s="2" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>6df19e3286ca4ff7</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K539" s="2" t="inlineStr"/>
+      <c r="L539" s="2" t="inlineStr">
+        <is>
+          <t>0.698177</t>
+        </is>
+      </c>
+      <c r="M539" s="2" t="inlineStr"/>
+      <c r="N539" s="2" t="inlineStr"/>
+      <c r="O539" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P539" s="2" t="inlineStr"/>
+      <c r="Q539" s="2" t="inlineStr">
+        <is>
+          <t>0.18837307843137263</t>
+        </is>
+      </c>
+      <c r="R539" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:15.176846Z</t>
+        </is>
+      </c>
+      <c r="S539" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T539" s="2" t="inlineStr"/>
+      <c r="U539" s="2" t="inlineStr"/>
+      <c r="V539" s="2" t="inlineStr"/>
+      <c r="W539" s="2" t="inlineStr"/>
+      <c r="X539" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y539" s="2" t="inlineStr"/>
+      <c r="Z539" s="2" t="inlineStr"/>
+      <c r="AA539" s="2" t="inlineStr"/>
+      <c r="AB539" s="2" t="inlineStr"/>
+      <c r="AC539" s="2" t="inlineStr"/>
+      <c r="AD539" s="2" t="inlineStr"/>
+      <c r="AE539" s="2" t="inlineStr"/>
+      <c r="AF539" s="2" t="inlineStr"/>
+      <c r="AG539" s="2" t="inlineStr"/>
+      <c r="AH539" s="2" t="inlineStr"/>
+      <c r="AI539" s="2" t="inlineStr"/>
+      <c r="AJ539" s="2" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>68f966b7c91e41ac</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>70533</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K540" s="2" t="inlineStr"/>
+      <c r="L540" s="2" t="inlineStr">
+        <is>
+          <t>0.509047</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="inlineStr"/>
+      <c r="N540" s="2" t="inlineStr"/>
+      <c r="O540" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P540" s="2" t="inlineStr"/>
+      <c r="Q540" s="2" t="inlineStr">
+        <is>
+          <t>-0.11072486311787066</t>
+        </is>
+      </c>
+      <c r="R540" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:15.707146Z</t>
+        </is>
+      </c>
+      <c r="S540" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T540" s="2" t="inlineStr"/>
+      <c r="U540" s="2" t="inlineStr"/>
+      <c r="V540" s="2" t="inlineStr"/>
+      <c r="W540" s="2" t="inlineStr"/>
+      <c r="X540" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y540" s="2" t="inlineStr"/>
+      <c r="Z540" s="2" t="inlineStr"/>
+      <c r="AA540" s="2" t="inlineStr"/>
+      <c r="AB540" s="2" t="inlineStr"/>
+      <c r="AC540" s="2" t="inlineStr"/>
+      <c r="AD540" s="2" t="inlineStr"/>
+      <c r="AE540" s="2" t="inlineStr"/>
+      <c r="AF540" s="2" t="inlineStr"/>
+      <c r="AG540" s="2" t="inlineStr"/>
+      <c r="AH540" s="2" t="inlineStr"/>
+      <c r="AI540" s="2" t="inlineStr"/>
+      <c r="AJ540" s="2" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>7bcb1765eda24133</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K541" s="2" t="inlineStr"/>
+      <c r="L541" s="2" t="inlineStr">
+        <is>
+          <t>0.614141</t>
+        </is>
+      </c>
+      <c r="M541" s="2" t="inlineStr"/>
+      <c r="N541" s="2" t="inlineStr"/>
+      <c r="O541" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P541" s="2" t="inlineStr"/>
+      <c r="Q541" s="2" t="inlineStr">
+        <is>
+          <t>0.034309067226890866</t>
+        </is>
+      </c>
+      <c r="R541" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:16.265161Z</t>
+        </is>
+      </c>
+      <c r="S541" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T541" s="2" t="inlineStr"/>
+      <c r="U541" s="2" t="inlineStr"/>
+      <c r="V541" s="2" t="inlineStr"/>
+      <c r="W541" s="2" t="inlineStr"/>
+      <c r="X541" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y541" s="2" t="inlineStr"/>
+      <c r="Z541" s="2" t="inlineStr"/>
+      <c r="AA541" s="2" t="inlineStr"/>
+      <c r="AB541" s="2" t="inlineStr"/>
+      <c r="AC541" s="2" t="inlineStr"/>
+      <c r="AD541" s="2" t="inlineStr"/>
+      <c r="AE541" s="2" t="inlineStr"/>
+      <c r="AF541" s="2" t="inlineStr"/>
+      <c r="AG541" s="2" t="inlineStr"/>
+      <c r="AH541" s="2" t="inlineStr"/>
+      <c r="AI541" s="2" t="inlineStr"/>
+      <c r="AJ541" s="2" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>f356e37f63b84484</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>71386</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K542" s="2" t="inlineStr"/>
+      <c r="L542" s="2" t="inlineStr">
+        <is>
+          <t>0.60777</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="inlineStr"/>
+      <c r="N542" s="2" t="inlineStr"/>
+      <c r="O542" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P542" s="2" t="inlineStr"/>
+      <c r="Q542" s="2" t="inlineStr">
+        <is>
+          <t>-0.06219699669966994</t>
+        </is>
+      </c>
+      <c r="R542" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:16.895851Z</t>
+        </is>
+      </c>
+      <c r="S542" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T542" s="2" t="inlineStr"/>
+      <c r="U542" s="2" t="inlineStr"/>
+      <c r="V542" s="2" t="inlineStr"/>
+      <c r="W542" s="2" t="inlineStr"/>
+      <c r="X542" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y542" s="2" t="inlineStr"/>
+      <c r="Z542" s="2" t="inlineStr"/>
+      <c r="AA542" s="2" t="inlineStr"/>
+      <c r="AB542" s="2" t="inlineStr"/>
+      <c r="AC542" s="2" t="inlineStr"/>
+      <c r="AD542" s="2" t="inlineStr"/>
+      <c r="AE542" s="2" t="inlineStr"/>
+      <c r="AF542" s="2" t="inlineStr"/>
+      <c r="AG542" s="2" t="inlineStr"/>
+      <c r="AH542" s="2" t="inlineStr"/>
+      <c r="AI542" s="2" t="inlineStr"/>
+      <c r="AJ542" s="2" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>29bfade4a7be4f67</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>71727</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K543" s="2" t="inlineStr"/>
+      <c r="L543" s="2" t="inlineStr">
+        <is>
+          <t>0.655018</t>
+        </is>
+      </c>
+      <c r="M543" s="2" t="inlineStr"/>
+      <c r="N543" s="2" t="inlineStr"/>
+      <c r="O543" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P543" s="2" t="inlineStr"/>
+      <c r="Q543" s="2" t="inlineStr">
+        <is>
+          <t>0.07518606722689081</t>
+        </is>
+      </c>
+      <c r="R543" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:18.645513Z</t>
+        </is>
+      </c>
+      <c r="S543" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="T543" s="2" t="inlineStr"/>
+      <c r="U543" s="2" t="inlineStr"/>
+      <c r="V543" s="2" t="inlineStr"/>
+      <c r="W543" s="2" t="inlineStr"/>
+      <c r="X543" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y543" s="2" t="inlineStr"/>
+      <c r="Z543" s="2" t="inlineStr"/>
+      <c r="AA543" s="2" t="inlineStr"/>
+      <c r="AB543" s="2" t="inlineStr"/>
+      <c r="AC543" s="2" t="inlineStr"/>
+      <c r="AD543" s="2" t="inlineStr"/>
+      <c r="AE543" s="2" t="inlineStr"/>
+      <c r="AF543" s="2" t="inlineStr"/>
+      <c r="AG543" s="2" t="inlineStr"/>
+      <c r="AH543" s="2" t="inlineStr"/>
+      <c r="AI543" s="2" t="inlineStr"/>
+      <c r="AJ543" s="2" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>8fb619c165fd4380</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>69537</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K544" s="2" t="inlineStr"/>
+      <c r="L544" s="2" t="inlineStr">
+        <is>
+          <t>0.536585</t>
+        </is>
+      </c>
+      <c r="M544" s="2" t="inlineStr"/>
+      <c r="N544" s="2" t="inlineStr"/>
+      <c r="O544" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P544" s="2" t="inlineStr"/>
+      <c r="Q544" s="2" t="inlineStr">
+        <is>
+          <t>0.10740045064377679</t>
+        </is>
+      </c>
+      <c r="R544" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:21.650580Z</t>
+        </is>
+      </c>
+      <c r="S544" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T544" s="2" t="inlineStr"/>
+      <c r="U544" s="2" t="inlineStr"/>
+      <c r="V544" s="2" t="inlineStr"/>
+      <c r="W544" s="2" t="inlineStr"/>
+      <c r="X544" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y544" s="2" t="inlineStr"/>
+      <c r="Z544" s="2" t="inlineStr"/>
+      <c r="AA544" s="2" t="inlineStr"/>
+      <c r="AB544" s="2" t="inlineStr"/>
+      <c r="AC544" s="2" t="inlineStr"/>
+      <c r="AD544" s="2" t="inlineStr"/>
+      <c r="AE544" s="2" t="inlineStr"/>
+      <c r="AF544" s="2" t="inlineStr"/>
+      <c r="AG544" s="2" t="inlineStr"/>
+      <c r="AH544" s="2" t="inlineStr"/>
+      <c r="AI544" s="2" t="inlineStr"/>
+      <c r="AJ544" s="2" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>c3d300ca624b41d3</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>71199</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K545" s="2" t="inlineStr"/>
+      <c r="L545" s="2" t="inlineStr">
+        <is>
+          <t>0.50612</t>
+        </is>
+      </c>
+      <c r="M545" s="2" t="inlineStr"/>
+      <c r="N545" s="2" t="inlineStr"/>
+      <c r="O545" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P545" s="2" t="inlineStr"/>
+      <c r="Q545" s="2" t="inlineStr">
+        <is>
+          <t>0.06559136563876655</t>
+        </is>
+      </c>
+      <c r="R545" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:23.410197Z</t>
+        </is>
+      </c>
+      <c r="S545" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T545" s="2" t="inlineStr"/>
+      <c r="U545" s="2" t="inlineStr"/>
+      <c r="V545" s="2" t="inlineStr"/>
+      <c r="W545" s="2" t="inlineStr"/>
+      <c r="X545" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y545" s="2" t="inlineStr"/>
+      <c r="Z545" s="2" t="inlineStr"/>
+      <c r="AA545" s="2" t="inlineStr"/>
+      <c r="AB545" s="2" t="inlineStr"/>
+      <c r="AC545" s="2" t="inlineStr"/>
+      <c r="AD545" s="2" t="inlineStr"/>
+      <c r="AE545" s="2" t="inlineStr"/>
+      <c r="AF545" s="2" t="inlineStr"/>
+      <c r="AG545" s="2" t="inlineStr"/>
+      <c r="AH545" s="2" t="inlineStr"/>
+      <c r="AI545" s="2" t="inlineStr"/>
+      <c r="AJ545" s="2" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>491d44d71a064bc3</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>69553</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K546" s="2" t="inlineStr"/>
+      <c r="L546" s="2" t="inlineStr">
+        <is>
+          <t>0.585628</t>
+        </is>
+      </c>
+      <c r="M546" s="2" t="inlineStr"/>
+      <c r="N546" s="2" t="inlineStr"/>
+      <c r="O546" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P546" s="2" t="inlineStr"/>
+      <c r="Q546" s="2" t="inlineStr">
+        <is>
+          <t>-0.11407169969969966</t>
+        </is>
+      </c>
+      <c r="R546" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:24.015231Z</t>
+        </is>
+      </c>
+      <c r="S546" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T546" s="2" t="inlineStr"/>
+      <c r="U546" s="2" t="inlineStr"/>
+      <c r="V546" s="2" t="inlineStr"/>
+      <c r="W546" s="2" t="inlineStr"/>
+      <c r="X546" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y546" s="2" t="inlineStr"/>
+      <c r="Z546" s="2" t="inlineStr"/>
+      <c r="AA546" s="2" t="inlineStr"/>
+      <c r="AB546" s="2" t="inlineStr"/>
+      <c r="AC546" s="2" t="inlineStr"/>
+      <c r="AD546" s="2" t="inlineStr"/>
+      <c r="AE546" s="2" t="inlineStr"/>
+      <c r="AF546" s="2" t="inlineStr"/>
+      <c r="AG546" s="2" t="inlineStr"/>
+      <c r="AH546" s="2" t="inlineStr"/>
+      <c r="AI546" s="2" t="inlineStr"/>
+      <c r="AJ546" s="2" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>5c14752f268441b1</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K547" s="2" t="inlineStr"/>
+      <c r="L547" s="2" t="inlineStr">
+        <is>
+          <t>0.526798</t>
+        </is>
+      </c>
+      <c r="M547" s="2" t="inlineStr"/>
+      <c r="N547" s="2" t="inlineStr"/>
+      <c r="O547" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P547" s="2" t="inlineStr"/>
+      <c r="Q547" s="2" t="inlineStr">
+        <is>
+          <t>-0.04401745064377682</t>
+        </is>
+      </c>
+      <c r="R547" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:25.294415Z</t>
+        </is>
+      </c>
+      <c r="S547" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T547" s="2" t="inlineStr"/>
+      <c r="U547" s="2" t="inlineStr"/>
+      <c r="V547" s="2" t="inlineStr"/>
+      <c r="W547" s="2" t="inlineStr"/>
+      <c r="X547" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y547" s="2" t="inlineStr"/>
+      <c r="Z547" s="2" t="inlineStr"/>
+      <c r="AA547" s="2" t="inlineStr"/>
+      <c r="AB547" s="2" t="inlineStr"/>
+      <c r="AC547" s="2" t="inlineStr"/>
+      <c r="AD547" s="2" t="inlineStr"/>
+      <c r="AE547" s="2" t="inlineStr"/>
+      <c r="AF547" s="2" t="inlineStr"/>
+      <c r="AG547" s="2" t="inlineStr"/>
+      <c r="AH547" s="2" t="inlineStr"/>
+      <c r="AI547" s="2" t="inlineStr"/>
+      <c r="AJ547" s="2" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>ffe47996f21f4bd3</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>475f364a096b07d854cb14593fbd6a49f4aa1a09e613dca77e6698a4185512cf</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K548" s="2" t="inlineStr"/>
+      <c r="L548" s="2" t="inlineStr">
+        <is>
+          <t>0.537718</t>
+        </is>
+      </c>
+      <c r="M548" s="2" t="inlineStr"/>
+      <c r="N548" s="2" t="inlineStr"/>
+      <c r="O548" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P548" s="2" t="inlineStr"/>
+      <c r="Q548" s="2" t="inlineStr">
+        <is>
+          <t>-0.02175336563876651</t>
+        </is>
+      </c>
+      <c r="R548" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:07:26.978469Z</t>
+        </is>
+      </c>
+      <c r="S548" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T548" s="2" t="inlineStr"/>
+      <c r="U548" s="2" t="inlineStr"/>
+      <c r="V548" s="2" t="inlineStr"/>
+      <c r="W548" s="2" t="inlineStr"/>
+      <c r="X548" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y548" s="2" t="inlineStr"/>
+      <c r="Z548" s="2" t="inlineStr"/>
+      <c r="AA548" s="2" t="inlineStr"/>
+      <c r="AB548" s="2" t="inlineStr"/>
+      <c r="AC548" s="2" t="inlineStr"/>
+      <c r="AD548" s="2" t="inlineStr"/>
+      <c r="AE548" s="2" t="inlineStr"/>
+      <c r="AF548" s="2" t="inlineStr"/>
+      <c r="AG548" s="2" t="inlineStr"/>
+      <c r="AH548" s="2" t="inlineStr"/>
+      <c r="AI548" s="2" t="inlineStr"/>
+      <c r="AJ548" s="2" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>9418d49d0410466a</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>68562</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K549" s="2" t="inlineStr"/>
+      <c r="L549" s="2" t="inlineStr">
+        <is>
+          <t>0.526798</t>
+        </is>
+      </c>
+      <c r="M549" s="2" t="inlineStr"/>
+      <c r="N549" s="2" t="inlineStr"/>
+      <c r="O549" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P549" s="2" t="inlineStr"/>
+      <c r="Q549" s="2" t="inlineStr">
+        <is>
+          <t>-0.10283162962962955</t>
+        </is>
+      </c>
+      <c r="R549" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:40.094577Z</t>
+        </is>
+      </c>
+      <c r="S549" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T549" s="2" t="inlineStr"/>
+      <c r="U549" s="2" t="inlineStr"/>
+      <c r="V549" s="2" t="inlineStr"/>
+      <c r="W549" s="2" t="inlineStr"/>
+      <c r="X549" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y549" s="2" t="inlineStr"/>
+      <c r="Z549" s="2" t="inlineStr"/>
+      <c r="AA549" s="2" t="inlineStr"/>
+      <c r="AB549" s="2" t="inlineStr"/>
+      <c r="AC549" s="2" t="inlineStr"/>
+      <c r="AD549" s="2" t="inlineStr"/>
+      <c r="AE549" s="2" t="inlineStr"/>
+      <c r="AF549" s="2" t="inlineStr"/>
+      <c r="AG549" s="2" t="inlineStr"/>
+      <c r="AH549" s="2" t="inlineStr"/>
+      <c r="AI549" s="2" t="inlineStr"/>
+      <c r="AJ549" s="2" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>017ea24372224afb</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>68563</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K550" s="2" t="inlineStr"/>
+      <c r="L550" s="2" t="inlineStr">
+        <is>
+          <t>0.526798</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="inlineStr"/>
+      <c r="N550" s="2" t="inlineStr"/>
+      <c r="O550" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P550" s="2" t="inlineStr"/>
+      <c r="Q550" s="2" t="inlineStr">
+        <is>
+          <t>-0.04401745064377682</t>
+        </is>
+      </c>
+      <c r="R550" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:40.578112Z</t>
+        </is>
+      </c>
+      <c r="S550" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="T550" s="2" t="inlineStr"/>
+      <c r="U550" s="2" t="inlineStr"/>
+      <c r="V550" s="2" t="inlineStr"/>
+      <c r="W550" s="2" t="inlineStr"/>
+      <c r="X550" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y550" s="2" t="inlineStr"/>
+      <c r="Z550" s="2" t="inlineStr"/>
+      <c r="AA550" s="2" t="inlineStr"/>
+      <c r="AB550" s="2" t="inlineStr"/>
+      <c r="AC550" s="2" t="inlineStr"/>
+      <c r="AD550" s="2" t="inlineStr"/>
+      <c r="AE550" s="2" t="inlineStr"/>
+      <c r="AF550" s="2" t="inlineStr"/>
+      <c r="AG550" s="2" t="inlineStr"/>
+      <c r="AH550" s="2" t="inlineStr"/>
+      <c r="AI550" s="2" t="inlineStr"/>
+      <c r="AJ550" s="2" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>d07fd229256448aa</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>68565</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K551" s="2" t="inlineStr"/>
+      <c r="L551" s="2" t="inlineStr">
+        <is>
+          <t>0.589329</t>
+        </is>
+      </c>
+      <c r="M551" s="2" t="inlineStr"/>
+      <c r="N551" s="2" t="inlineStr"/>
+      <c r="O551" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P551" s="2" t="inlineStr"/>
+      <c r="Q551" s="2" t="inlineStr">
+        <is>
+          <t>-0.09118218210862616</t>
+        </is>
+      </c>
+      <c r="R551" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:41.052332Z</t>
+        </is>
+      </c>
+      <c r="S551" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T551" s="2" t="inlineStr"/>
+      <c r="U551" s="2" t="inlineStr"/>
+      <c r="V551" s="2" t="inlineStr"/>
+      <c r="W551" s="2" t="inlineStr"/>
+      <c r="X551" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y551" s="2" t="inlineStr"/>
+      <c r="Z551" s="2" t="inlineStr"/>
+      <c r="AA551" s="2" t="inlineStr"/>
+      <c r="AB551" s="2" t="inlineStr"/>
+      <c r="AC551" s="2" t="inlineStr"/>
+      <c r="AD551" s="2" t="inlineStr"/>
+      <c r="AE551" s="2" t="inlineStr"/>
+      <c r="AF551" s="2" t="inlineStr"/>
+      <c r="AG551" s="2" t="inlineStr"/>
+      <c r="AH551" s="2" t="inlineStr"/>
+      <c r="AI551" s="2" t="inlineStr"/>
+      <c r="AJ551" s="2" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>7999ea44b9a941b3</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>68567</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K552" s="2" t="inlineStr"/>
+      <c r="L552" s="2" t="inlineStr">
+        <is>
+          <t>0.516198</t>
+        </is>
+      </c>
+      <c r="M552" s="2" t="inlineStr"/>
+      <c r="N552" s="2" t="inlineStr"/>
+      <c r="O552" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P552" s="2" t="inlineStr"/>
+      <c r="Q552" s="2" t="inlineStr">
+        <is>
+          <t>-0.04327336563876649</t>
+        </is>
+      </c>
+      <c r="R552" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:41.781184Z</t>
+        </is>
+      </c>
+      <c r="S552" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T552" s="2" t="inlineStr"/>
+      <c r="U552" s="2" t="inlineStr"/>
+      <c r="V552" s="2" t="inlineStr"/>
+      <c r="W552" s="2" t="inlineStr"/>
+      <c r="X552" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y552" s="2" t="inlineStr"/>
+      <c r="Z552" s="2" t="inlineStr"/>
+      <c r="AA552" s="2" t="inlineStr"/>
+      <c r="AB552" s="2" t="inlineStr"/>
+      <c r="AC552" s="2" t="inlineStr"/>
+      <c r="AD552" s="2" t="inlineStr"/>
+      <c r="AE552" s="2" t="inlineStr"/>
+      <c r="AF552" s="2" t="inlineStr"/>
+      <c r="AG552" s="2" t="inlineStr"/>
+      <c r="AH552" s="2" t="inlineStr"/>
+      <c r="AI552" s="2" t="inlineStr"/>
+      <c r="AJ552" s="2" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>e872bf59f493483a</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>71337</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K553" s="2" t="inlineStr"/>
+      <c r="L553" s="2" t="inlineStr">
+        <is>
+          <t>0.571449</t>
+        </is>
+      </c>
+      <c r="M553" s="2" t="inlineStr"/>
+      <c r="N553" s="2" t="inlineStr"/>
+      <c r="O553" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P553" s="2" t="inlineStr"/>
+      <c r="Q553" s="2" t="inlineStr">
+        <is>
+          <t>0.021899450450450497</t>
+        </is>
+      </c>
+      <c r="R553" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:42.351782Z</t>
+        </is>
+      </c>
+      <c r="S553" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T553" s="2" t="inlineStr"/>
+      <c r="U553" s="2" t="inlineStr"/>
+      <c r="V553" s="2" t="inlineStr"/>
+      <c r="W553" s="2" t="inlineStr"/>
+      <c r="X553" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y553" s="2" t="inlineStr"/>
+      <c r="Z553" s="2" t="inlineStr"/>
+      <c r="AA553" s="2" t="inlineStr"/>
+      <c r="AB553" s="2" t="inlineStr"/>
+      <c r="AC553" s="2" t="inlineStr"/>
+      <c r="AD553" s="2" t="inlineStr"/>
+      <c r="AE553" s="2" t="inlineStr"/>
+      <c r="AF553" s="2" t="inlineStr"/>
+      <c r="AG553" s="2" t="inlineStr"/>
+      <c r="AH553" s="2" t="inlineStr"/>
+      <c r="AI553" s="2" t="inlineStr"/>
+      <c r="AJ553" s="2" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>e1385fc03a584caa</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K554" s="2" t="inlineStr"/>
+      <c r="L554" s="2" t="inlineStr">
+        <is>
+          <t>0.500666</t>
+        </is>
+      </c>
+      <c r="M554" s="2" t="inlineStr"/>
+      <c r="N554" s="2" t="inlineStr"/>
+      <c r="O554" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P554" s="2" t="inlineStr"/>
+      <c r="Q554" s="2" t="inlineStr">
+        <is>
+          <t>0.0006660000000000554</t>
+        </is>
+      </c>
+      <c r="R554" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:42.942188Z</t>
+        </is>
+      </c>
+      <c r="S554" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T554" s="2" t="inlineStr"/>
+      <c r="U554" s="2" t="inlineStr"/>
+      <c r="V554" s="2" t="inlineStr"/>
+      <c r="W554" s="2" t="inlineStr"/>
+      <c r="X554" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y554" s="2" t="inlineStr"/>
+      <c r="Z554" s="2" t="inlineStr"/>
+      <c r="AA554" s="2" t="inlineStr"/>
+      <c r="AB554" s="2" t="inlineStr"/>
+      <c r="AC554" s="2" t="inlineStr"/>
+      <c r="AD554" s="2" t="inlineStr"/>
+      <c r="AE554" s="2" t="inlineStr"/>
+      <c r="AF554" s="2" t="inlineStr"/>
+      <c r="AG554" s="2" t="inlineStr"/>
+      <c r="AH554" s="2" t="inlineStr"/>
+      <c r="AI554" s="2" t="inlineStr"/>
+      <c r="AJ554" s="2" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>1993812020294926</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>71339</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K555" s="2" t="inlineStr"/>
+      <c r="L555" s="2" t="inlineStr">
+        <is>
+          <t>0.681734</t>
+        </is>
+      </c>
+      <c r="M555" s="2" t="inlineStr"/>
+      <c r="N555" s="2" t="inlineStr"/>
+      <c r="O555" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P555" s="2" t="inlineStr"/>
+      <c r="Q555" s="2" t="inlineStr">
+        <is>
+          <t>0.011767003300329981</t>
+        </is>
+      </c>
+      <c r="R555" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:44.028305Z</t>
+        </is>
+      </c>
+      <c r="S555" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:15:00Z</t>
+        </is>
+      </c>
+      <c r="T555" s="2" t="inlineStr"/>
+      <c r="U555" s="2" t="inlineStr"/>
+      <c r="V555" s="2" t="inlineStr"/>
+      <c r="W555" s="2" t="inlineStr"/>
+      <c r="X555" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y555" s="2" t="inlineStr"/>
+      <c r="Z555" s="2" t="inlineStr"/>
+      <c r="AA555" s="2" t="inlineStr"/>
+      <c r="AB555" s="2" t="inlineStr"/>
+      <c r="AC555" s="2" t="inlineStr"/>
+      <c r="AD555" s="2" t="inlineStr"/>
+      <c r="AE555" s="2" t="inlineStr"/>
+      <c r="AF555" s="2" t="inlineStr"/>
+      <c r="AG555" s="2" t="inlineStr"/>
+      <c r="AH555" s="2" t="inlineStr"/>
+      <c r="AI555" s="2" t="inlineStr"/>
+      <c r="AJ555" s="2" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>b2002b232aeb463e</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K556" s="2" t="inlineStr"/>
+      <c r="L556" s="2" t="inlineStr">
+        <is>
+          <t>0.67486</t>
+        </is>
+      </c>
+      <c r="M556" s="2" t="inlineStr"/>
+      <c r="N556" s="2" t="inlineStr"/>
+      <c r="O556" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P556" s="2" t="inlineStr"/>
+      <c r="Q556" s="2" t="inlineStr">
+        <is>
+          <t>0.08469606557377052</t>
+        </is>
+      </c>
+      <c r="R556" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:45.147234Z</t>
+        </is>
+      </c>
+      <c r="S556" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T556" s="2" t="inlineStr"/>
+      <c r="U556" s="2" t="inlineStr"/>
+      <c r="V556" s="2" t="inlineStr"/>
+      <c r="W556" s="2" t="inlineStr"/>
+      <c r="X556" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y556" s="2" t="inlineStr"/>
+      <c r="Z556" s="2" t="inlineStr"/>
+      <c r="AA556" s="2" t="inlineStr"/>
+      <c r="AB556" s="2" t="inlineStr"/>
+      <c r="AC556" s="2" t="inlineStr"/>
+      <c r="AD556" s="2" t="inlineStr"/>
+      <c r="AE556" s="2" t="inlineStr"/>
+      <c r="AF556" s="2" t="inlineStr"/>
+      <c r="AG556" s="2" t="inlineStr"/>
+      <c r="AH556" s="2" t="inlineStr"/>
+      <c r="AI556" s="2" t="inlineStr"/>
+      <c r="AJ556" s="2" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>fc5b6751088747bb</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>71341</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K557" s="2" t="inlineStr"/>
+      <c r="L557" s="2" t="inlineStr">
+        <is>
+          <t>0.505296</t>
+        </is>
+      </c>
+      <c r="M557" s="2" t="inlineStr"/>
+      <c r="N557" s="2" t="inlineStr"/>
+      <c r="O557" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P557" s="2" t="inlineStr"/>
+      <c r="Q557" s="2" t="inlineStr">
+        <is>
+          <t>0.005295999999999967</t>
+        </is>
+      </c>
+      <c r="R557" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:45.726436Z</t>
+        </is>
+      </c>
+      <c r="S557" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T557" s="2" t="inlineStr"/>
+      <c r="U557" s="2" t="inlineStr"/>
+      <c r="V557" s="2" t="inlineStr"/>
+      <c r="W557" s="2" t="inlineStr"/>
+      <c r="X557" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y557" s="2" t="inlineStr"/>
+      <c r="Z557" s="2" t="inlineStr"/>
+      <c r="AA557" s="2" t="inlineStr"/>
+      <c r="AB557" s="2" t="inlineStr"/>
+      <c r="AC557" s="2" t="inlineStr"/>
+      <c r="AD557" s="2" t="inlineStr"/>
+      <c r="AE557" s="2" t="inlineStr"/>
+      <c r="AF557" s="2" t="inlineStr"/>
+      <c r="AG557" s="2" t="inlineStr"/>
+      <c r="AH557" s="2" t="inlineStr"/>
+      <c r="AI557" s="2" t="inlineStr"/>
+      <c r="AJ557" s="2" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>22db873f43fe4783</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K558" s="2" t="inlineStr"/>
+      <c r="L558" s="2" t="inlineStr">
+        <is>
+          <t>0.599257</t>
+        </is>
+      </c>
+      <c r="M558" s="2" t="inlineStr"/>
+      <c r="N558" s="2" t="inlineStr"/>
+      <c r="O558" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P558" s="2" t="inlineStr"/>
+      <c r="Q558" s="2" t="inlineStr">
+        <is>
+          <t>-0.020514863117870652</t>
+        </is>
+      </c>
+      <c r="R558" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:46.262059Z</t>
+        </is>
+      </c>
+      <c r="S558" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T558" s="2" t="inlineStr"/>
+      <c r="U558" s="2" t="inlineStr"/>
+      <c r="V558" s="2" t="inlineStr"/>
+      <c r="W558" s="2" t="inlineStr"/>
+      <c r="X558" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y558" s="2" t="inlineStr"/>
+      <c r="Z558" s="2" t="inlineStr"/>
+      <c r="AA558" s="2" t="inlineStr"/>
+      <c r="AB558" s="2" t="inlineStr"/>
+      <c r="AC558" s="2" t="inlineStr"/>
+      <c r="AD558" s="2" t="inlineStr"/>
+      <c r="AE558" s="2" t="inlineStr"/>
+      <c r="AF558" s="2" t="inlineStr"/>
+      <c r="AG558" s="2" t="inlineStr"/>
+      <c r="AH558" s="2" t="inlineStr"/>
+      <c r="AI558" s="2" t="inlineStr"/>
+      <c r="AJ558" s="2" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>e2e4200bbda044ea</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>71391</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K559" s="2" t="inlineStr"/>
+      <c r="L559" s="2" t="inlineStr">
+        <is>
+          <t>0.645876</t>
+        </is>
+      </c>
+      <c r="M559" s="2" t="inlineStr"/>
+      <c r="N559" s="2" t="inlineStr"/>
+      <c r="O559" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P559" s="2" t="inlineStr"/>
+      <c r="Q559" s="2" t="inlineStr">
+        <is>
+          <t>0.145876</t>
+        </is>
+      </c>
+      <c r="R559" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:46.831301Z</t>
+        </is>
+      </c>
+      <c r="S559" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T559" s="2" t="inlineStr"/>
+      <c r="U559" s="2" t="inlineStr"/>
+      <c r="V559" s="2" t="inlineStr"/>
+      <c r="W559" s="2" t="inlineStr"/>
+      <c r="X559" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y559" s="2" t="inlineStr"/>
+      <c r="Z559" s="2" t="inlineStr"/>
+      <c r="AA559" s="2" t="inlineStr"/>
+      <c r="AB559" s="2" t="inlineStr"/>
+      <c r="AC559" s="2" t="inlineStr"/>
+      <c r="AD559" s="2" t="inlineStr"/>
+      <c r="AE559" s="2" t="inlineStr"/>
+      <c r="AF559" s="2" t="inlineStr"/>
+      <c r="AG559" s="2" t="inlineStr"/>
+      <c r="AH559" s="2" t="inlineStr"/>
+      <c r="AI559" s="2" t="inlineStr"/>
+      <c r="AJ559" s="2" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>eeffb95a6a674992</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>71385</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K560" s="2" t="inlineStr"/>
+      <c r="L560" s="2" t="inlineStr">
+        <is>
+          <t>0.576143</t>
+        </is>
+      </c>
+      <c r="M560" s="2" t="inlineStr"/>
+      <c r="N560" s="2" t="inlineStr"/>
+      <c r="O560" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P560" s="2" t="inlineStr"/>
+      <c r="Q560" s="2" t="inlineStr">
+        <is>
+          <t>0.005327549356223149</t>
+        </is>
+      </c>
+      <c r="R560" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:47.526137Z</t>
+        </is>
+      </c>
+      <c r="S560" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T560" s="2" t="inlineStr"/>
+      <c r="U560" s="2" t="inlineStr"/>
+      <c r="V560" s="2" t="inlineStr"/>
+      <c r="W560" s="2" t="inlineStr"/>
+      <c r="X560" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y560" s="2" t="inlineStr"/>
+      <c r="Z560" s="2" t="inlineStr"/>
+      <c r="AA560" s="2" t="inlineStr"/>
+      <c r="AB560" s="2" t="inlineStr"/>
+      <c r="AC560" s="2" t="inlineStr"/>
+      <c r="AD560" s="2" t="inlineStr"/>
+      <c r="AE560" s="2" t="inlineStr"/>
+      <c r="AF560" s="2" t="inlineStr"/>
+      <c r="AG560" s="2" t="inlineStr"/>
+      <c r="AH560" s="2" t="inlineStr"/>
+      <c r="AI560" s="2" t="inlineStr"/>
+      <c r="AJ560" s="2" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>c6871c7441814f81</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>71384</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K561" s="2" t="inlineStr"/>
+      <c r="L561" s="2" t="inlineStr">
+        <is>
+          <t>0.507111</t>
+        </is>
+      </c>
+      <c r="M561" s="2" t="inlineStr"/>
+      <c r="N561" s="2" t="inlineStr"/>
+      <c r="O561" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P561" s="2" t="inlineStr"/>
+      <c r="Q561" s="2" t="inlineStr">
+        <is>
+          <t>0.0071109999999999784</t>
+        </is>
+      </c>
+      <c r="R561" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:48.003203Z</t>
+        </is>
+      </c>
+      <c r="S561" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T561" s="2" t="inlineStr"/>
+      <c r="U561" s="2" t="inlineStr"/>
+      <c r="V561" s="2" t="inlineStr"/>
+      <c r="W561" s="2" t="inlineStr"/>
+      <c r="X561" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y561" s="2" t="inlineStr"/>
+      <c r="Z561" s="2" t="inlineStr"/>
+      <c r="AA561" s="2" t="inlineStr"/>
+      <c r="AB561" s="2" t="inlineStr"/>
+      <c r="AC561" s="2" t="inlineStr"/>
+      <c r="AD561" s="2" t="inlineStr"/>
+      <c r="AE561" s="2" t="inlineStr"/>
+      <c r="AF561" s="2" t="inlineStr"/>
+      <c r="AG561" s="2" t="inlineStr"/>
+      <c r="AH561" s="2" t="inlineStr"/>
+      <c r="AI561" s="2" t="inlineStr"/>
+      <c r="AJ561" s="2" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>cbfdee05ce654c00</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K562" s="2" t="inlineStr"/>
+      <c r="L562" s="2" t="inlineStr">
+        <is>
+          <t>0.556024</t>
+        </is>
+      </c>
+      <c r="M562" s="2" t="inlineStr"/>
+      <c r="N562" s="2" t="inlineStr"/>
+      <c r="O562" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P562" s="2" t="inlineStr"/>
+      <c r="Q562" s="2" t="inlineStr">
+        <is>
+          <t>0.0367932307692308</t>
+        </is>
+      </c>
+      <c r="R562" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:48.498248Z</t>
+        </is>
+      </c>
+      <c r="S562" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T562" s="2" t="inlineStr"/>
+      <c r="U562" s="2" t="inlineStr"/>
+      <c r="V562" s="2" t="inlineStr"/>
+      <c r="W562" s="2" t="inlineStr"/>
+      <c r="X562" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y562" s="2" t="inlineStr"/>
+      <c r="Z562" s="2" t="inlineStr"/>
+      <c r="AA562" s="2" t="inlineStr"/>
+      <c r="AB562" s="2" t="inlineStr"/>
+      <c r="AC562" s="2" t="inlineStr"/>
+      <c r="AD562" s="2" t="inlineStr"/>
+      <c r="AE562" s="2" t="inlineStr"/>
+      <c r="AF562" s="2" t="inlineStr"/>
+      <c r="AG562" s="2" t="inlineStr"/>
+      <c r="AH562" s="2" t="inlineStr"/>
+      <c r="AI562" s="2" t="inlineStr"/>
+      <c r="AJ562" s="2" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>c20e95700d2b49c3</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>71389</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J563" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K563" s="2" t="inlineStr"/>
+      <c r="L563" s="2" t="inlineStr">
+        <is>
+          <t>0.698177</t>
+        </is>
+      </c>
+      <c r="M563" s="2" t="inlineStr"/>
+      <c r="N563" s="2" t="inlineStr"/>
+      <c r="O563" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P563" s="2" t="inlineStr"/>
+      <c r="Q563" s="2" t="inlineStr">
+        <is>
+          <t>0.19817700000000005</t>
+        </is>
+      </c>
+      <c r="R563" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:49.093007Z</t>
+        </is>
+      </c>
+      <c r="S563" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T563" s="2" t="inlineStr"/>
+      <c r="U563" s="2" t="inlineStr"/>
+      <c r="V563" s="2" t="inlineStr"/>
+      <c r="W563" s="2" t="inlineStr"/>
+      <c r="X563" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y563" s="2" t="inlineStr"/>
+      <c r="Z563" s="2" t="inlineStr"/>
+      <c r="AA563" s="2" t="inlineStr"/>
+      <c r="AB563" s="2" t="inlineStr"/>
+      <c r="AC563" s="2" t="inlineStr"/>
+      <c r="AD563" s="2" t="inlineStr"/>
+      <c r="AE563" s="2" t="inlineStr"/>
+      <c r="AF563" s="2" t="inlineStr"/>
+      <c r="AG563" s="2" t="inlineStr"/>
+      <c r="AH563" s="2" t="inlineStr"/>
+      <c r="AI563" s="2" t="inlineStr"/>
+      <c r="AJ563" s="2" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>fef34d302e9c433f</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>70533</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K564" s="2" t="inlineStr"/>
+      <c r="L564" s="2" t="inlineStr">
+        <is>
+          <t>0.509047</t>
+        </is>
+      </c>
+      <c r="M564" s="2" t="inlineStr"/>
+      <c r="N564" s="2" t="inlineStr"/>
+      <c r="O564" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P564" s="2" t="inlineStr"/>
+      <c r="Q564" s="2" t="inlineStr">
+        <is>
+          <t>-0.11072486311787066</t>
+        </is>
+      </c>
+      <c r="R564" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:49.650275Z</t>
+        </is>
+      </c>
+      <c r="S564" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T564" s="2" t="inlineStr"/>
+      <c r="U564" s="2" t="inlineStr"/>
+      <c r="V564" s="2" t="inlineStr"/>
+      <c r="W564" s="2" t="inlineStr"/>
+      <c r="X564" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y564" s="2" t="inlineStr"/>
+      <c r="Z564" s="2" t="inlineStr"/>
+      <c r="AA564" s="2" t="inlineStr"/>
+      <c r="AB564" s="2" t="inlineStr"/>
+      <c r="AC564" s="2" t="inlineStr"/>
+      <c r="AD564" s="2" t="inlineStr"/>
+      <c r="AE564" s="2" t="inlineStr"/>
+      <c r="AF564" s="2" t="inlineStr"/>
+      <c r="AG564" s="2" t="inlineStr"/>
+      <c r="AH564" s="2" t="inlineStr"/>
+      <c r="AI564" s="2" t="inlineStr"/>
+      <c r="AJ564" s="2" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>b3e3cc06fe324e7b</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K565" s="2" t="inlineStr"/>
+      <c r="L565" s="2" t="inlineStr">
+        <is>
+          <t>0.614141</t>
+        </is>
+      </c>
+      <c r="M565" s="2" t="inlineStr"/>
+      <c r="N565" s="2" t="inlineStr"/>
+      <c r="O565" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P565" s="2" t="inlineStr"/>
+      <c r="Q565" s="2" t="inlineStr">
+        <is>
+          <t>0.034309067226890866</t>
+        </is>
+      </c>
+      <c r="R565" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:50.211130Z</t>
+        </is>
+      </c>
+      <c r="S565" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T565" s="2" t="inlineStr"/>
+      <c r="U565" s="2" t="inlineStr"/>
+      <c r="V565" s="2" t="inlineStr"/>
+      <c r="W565" s="2" t="inlineStr"/>
+      <c r="X565" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y565" s="2" t="inlineStr"/>
+      <c r="Z565" s="2" t="inlineStr"/>
+      <c r="AA565" s="2" t="inlineStr"/>
+      <c r="AB565" s="2" t="inlineStr"/>
+      <c r="AC565" s="2" t="inlineStr"/>
+      <c r="AD565" s="2" t="inlineStr"/>
+      <c r="AE565" s="2" t="inlineStr"/>
+      <c r="AF565" s="2" t="inlineStr"/>
+      <c r="AG565" s="2" t="inlineStr"/>
+      <c r="AH565" s="2" t="inlineStr"/>
+      <c r="AI565" s="2" t="inlineStr"/>
+      <c r="AJ565" s="2" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>244cfbebd19e4d65</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>71386</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K566" s="2" t="inlineStr"/>
+      <c r="L566" s="2" t="inlineStr">
+        <is>
+          <t>0.60777</t>
+        </is>
+      </c>
+      <c r="M566" s="2" t="inlineStr"/>
+      <c r="N566" s="2" t="inlineStr"/>
+      <c r="O566" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P566" s="2" t="inlineStr"/>
+      <c r="Q566" s="2" t="inlineStr">
+        <is>
+          <t>-0.06219699669966994</t>
+        </is>
+      </c>
+      <c r="R566" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:50.832408Z</t>
+        </is>
+      </c>
+      <c r="S566" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="T566" s="2" t="inlineStr"/>
+      <c r="U566" s="2" t="inlineStr"/>
+      <c r="V566" s="2" t="inlineStr"/>
+      <c r="W566" s="2" t="inlineStr"/>
+      <c r="X566" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y566" s="2" t="inlineStr"/>
+      <c r="Z566" s="2" t="inlineStr"/>
+      <c r="AA566" s="2" t="inlineStr"/>
+      <c r="AB566" s="2" t="inlineStr"/>
+      <c r="AC566" s="2" t="inlineStr"/>
+      <c r="AD566" s="2" t="inlineStr"/>
+      <c r="AE566" s="2" t="inlineStr"/>
+      <c r="AF566" s="2" t="inlineStr"/>
+      <c r="AG566" s="2" t="inlineStr"/>
+      <c r="AH566" s="2" t="inlineStr"/>
+      <c r="AI566" s="2" t="inlineStr"/>
+      <c r="AJ566" s="2" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>93378011b9194add</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>69537</t>
+        </is>
+      </c>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K567" s="2" t="inlineStr"/>
+      <c r="L567" s="2" t="inlineStr">
+        <is>
+          <t>0.536585</t>
+        </is>
+      </c>
+      <c r="M567" s="2" t="inlineStr"/>
+      <c r="N567" s="2" t="inlineStr"/>
+      <c r="O567" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P567" s="2" t="inlineStr"/>
+      <c r="Q567" s="2" t="inlineStr">
+        <is>
+          <t>0.10740045064377679</t>
+        </is>
+      </c>
+      <c r="R567" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:55.432557Z</t>
+        </is>
+      </c>
+      <c r="S567" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="T567" s="2" t="inlineStr"/>
+      <c r="U567" s="2" t="inlineStr"/>
+      <c r="V567" s="2" t="inlineStr"/>
+      <c r="W567" s="2" t="inlineStr"/>
+      <c r="X567" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y567" s="2" t="inlineStr"/>
+      <c r="Z567" s="2" t="inlineStr"/>
+      <c r="AA567" s="2" t="inlineStr"/>
+      <c r="AB567" s="2" t="inlineStr"/>
+      <c r="AC567" s="2" t="inlineStr"/>
+      <c r="AD567" s="2" t="inlineStr"/>
+      <c r="AE567" s="2" t="inlineStr"/>
+      <c r="AF567" s="2" t="inlineStr"/>
+      <c r="AG567" s="2" t="inlineStr"/>
+      <c r="AH567" s="2" t="inlineStr"/>
+      <c r="AI567" s="2" t="inlineStr"/>
+      <c r="AJ567" s="2" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>2cbdc1e128634b67</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K568" s="2" t="inlineStr"/>
+      <c r="L568" s="2" t="inlineStr">
+        <is>
+          <t>0.526798</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="inlineStr"/>
+      <c r="N568" s="2" t="inlineStr"/>
+      <c r="O568" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P568" s="2" t="inlineStr"/>
+      <c r="Q568" s="2" t="inlineStr">
+        <is>
+          <t>-0.04401745064377682</t>
+        </is>
+      </c>
+      <c r="R568" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:26:58.665259Z</t>
+        </is>
+      </c>
+      <c r="S568" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T568" s="2" t="inlineStr"/>
+      <c r="U568" s="2" t="inlineStr"/>
+      <c r="V568" s="2" t="inlineStr"/>
+      <c r="W568" s="2" t="inlineStr"/>
+      <c r="X568" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y568" s="2" t="inlineStr"/>
+      <c r="Z568" s="2" t="inlineStr"/>
+      <c r="AA568" s="2" t="inlineStr"/>
+      <c r="AB568" s="2" t="inlineStr"/>
+      <c r="AC568" s="2" t="inlineStr"/>
+      <c r="AD568" s="2" t="inlineStr"/>
+      <c r="AE568" s="2" t="inlineStr"/>
+      <c r="AF568" s="2" t="inlineStr"/>
+      <c r="AG568" s="2" t="inlineStr"/>
+      <c r="AH568" s="2" t="inlineStr"/>
+      <c r="AI568" s="2" t="inlineStr"/>
+      <c r="AJ568" s="2" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>9e5b40372f8146ac</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K569" s="2" t="inlineStr"/>
+      <c r="L569" s="2" t="inlineStr">
+        <is>
+          <t>0.537718</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="inlineStr"/>
+      <c r="N569" s="2" t="inlineStr"/>
+      <c r="O569" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P569" s="2" t="inlineStr"/>
+      <c r="Q569" s="2" t="inlineStr">
+        <is>
+          <t>-0.03309745064377678</t>
+        </is>
+      </c>
+      <c r="R569" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:00.540243Z</t>
+        </is>
+      </c>
+      <c r="S569" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T569" s="2" t="inlineStr"/>
+      <c r="U569" s="2" t="inlineStr"/>
+      <c r="V569" s="2" t="inlineStr"/>
+      <c r="W569" s="2" t="inlineStr"/>
+      <c r="X569" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y569" s="2" t="inlineStr"/>
+      <c r="Z569" s="2" t="inlineStr"/>
+      <c r="AA569" s="2" t="inlineStr"/>
+      <c r="AB569" s="2" t="inlineStr"/>
+      <c r="AC569" s="2" t="inlineStr"/>
+      <c r="AD569" s="2" t="inlineStr"/>
+      <c r="AE569" s="2" t="inlineStr"/>
+      <c r="AF569" s="2" t="inlineStr"/>
+      <c r="AG569" s="2" t="inlineStr"/>
+      <c r="AH569" s="2" t="inlineStr"/>
+      <c r="AI569" s="2" t="inlineStr"/>
+      <c r="AJ569" s="2" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>8e4cd77a618141d4</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>70104</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K570" s="2" t="inlineStr"/>
+      <c r="L570" s="2" t="inlineStr">
+        <is>
+          <t>0.526241</t>
+        </is>
+      </c>
+      <c r="M570" s="2" t="inlineStr"/>
+      <c r="N570" s="2" t="inlineStr"/>
+      <c r="O570" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P570" s="2" t="inlineStr"/>
+      <c r="Q570" s="2" t="inlineStr">
+        <is>
+          <t>0.007010230769230796</t>
+        </is>
+      </c>
+      <c r="R570" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:27:03.198013Z</t>
+        </is>
+      </c>
+      <c r="S570" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="T570" s="2" t="inlineStr"/>
+      <c r="U570" s="2" t="inlineStr"/>
+      <c r="V570" s="2" t="inlineStr"/>
+      <c r="W570" s="2" t="inlineStr"/>
+      <c r="X570" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y570" s="2" t="inlineStr"/>
+      <c r="Z570" s="2" t="inlineStr"/>
+      <c r="AA570" s="2" t="inlineStr"/>
+      <c r="AB570" s="2" t="inlineStr"/>
+      <c r="AC570" s="2" t="inlineStr"/>
+      <c r="AD570" s="2" t="inlineStr"/>
+      <c r="AE570" s="2" t="inlineStr"/>
+      <c r="AF570" s="2" t="inlineStr"/>
+      <c r="AG570" s="2" t="inlineStr"/>
+      <c r="AH570" s="2" t="inlineStr"/>
+      <c r="AI570" s="2" t="inlineStr"/>
+      <c r="AJ570" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ498"/>
+  <autoFilter ref="A1:AJ570"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>